--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="237">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -614,6 +614,12 @@
     <t>2000</t>
   </si>
   <si>
+    <t>15300</t>
+  </si>
+  <si>
+    <t>16000</t>
+  </si>
+  <si>
     <t>13000</t>
   </si>
   <si>
@@ -629,9 +635,6 @@
     <t>21000</t>
   </si>
   <si>
-    <t>16000</t>
-  </si>
-  <si>
     <t>10000</t>
   </si>
   <si>
@@ -653,7 +656,10 @@
     <t>78720</t>
   </si>
   <si>
-    <t>21308</t>
+    <t>23972</t>
+  </si>
+  <si>
+    <t>24000</t>
   </si>
   <si>
     <t>21700</t>
@@ -2818,10 +2824,10 @@
         <v>117</v>
       </c>
       <c r="E2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2841,7 +2847,7 @@
         <v>117</v>
       </c>
       <c r="F3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2858,10 +2864,10 @@
         <v>117</v>
       </c>
       <c r="E4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2878,10 +2884,10 @@
         <v>117</v>
       </c>
       <c r="E5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2898,10 +2904,10 @@
         <v>117</v>
       </c>
       <c r="E6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2918,10 +2924,10 @@
         <v>198</v>
       </c>
       <c r="E7" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F7" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2935,13 +2941,13 @@
         <v>188</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>199</v>
       </c>
       <c r="E8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F8" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2955,13 +2961,13 @@
         <v>189</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>200</v>
       </c>
       <c r="E9" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="F9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2975,13 +2981,13 @@
         <v>190</v>
       </c>
       <c r="D10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2995,13 +3001,13 @@
         <v>191</v>
       </c>
       <c r="D11" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E11" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F11" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3015,13 +3021,13 @@
         <v>192</v>
       </c>
       <c r="D12" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E12" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F12" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3038,10 +3044,10 @@
         <v>198</v>
       </c>
       <c r="E13" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F13" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -3055,13 +3061,13 @@
         <v>193</v>
       </c>
       <c r="D14" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E14" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F14" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -3075,13 +3081,13 @@
         <v>184</v>
       </c>
       <c r="D15" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E15" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F15" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -3095,13 +3101,13 @@
         <v>194</v>
       </c>
       <c r="D16" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E16" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F16" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -3115,13 +3121,13 @@
         <v>195</v>
       </c>
       <c r="D17" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E17" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F17" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -3135,13 +3141,13 @@
         <v>196</v>
       </c>
       <c r="D18" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E18" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F18" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -3158,10 +3164,10 @@
         <v>198</v>
       </c>
       <c r="E19" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F19" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -3178,10 +3184,10 @@
         <v>198</v>
       </c>
       <c r="E20" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F20" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -3195,13 +3201,13 @@
         <v>197</v>
       </c>
       <c r="D21" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E21" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F21" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="242">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -92,6 +92,9 @@
     <t>주요제품</t>
   </si>
   <si>
+    <t>2024-07-23</t>
+  </si>
+  <si>
     <t>2024-07-15</t>
   </si>
   <si>
@@ -140,6 +143,9 @@
     <t>2024-05-23</t>
   </si>
   <si>
+    <t>2024-07-29</t>
+  </si>
+  <si>
     <t>2024-07-19</t>
   </si>
   <si>
@@ -164,15 +170,15 @@
     <t>2024-05-29</t>
   </si>
   <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
     <t>2024-08-06</t>
   </si>
   <si>
     <t>2024-07-26</t>
   </si>
   <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
     <t>2024-07-12</t>
   </si>
   <si>
@@ -200,6 +206,9 @@
     <t>2024-07-01</t>
   </si>
   <si>
+    <t>미래</t>
+  </si>
+  <si>
     <t>삼성</t>
   </si>
   <si>
@@ -218,9 +227,6 @@
     <t>엘에스</t>
   </si>
   <si>
-    <t>미래</t>
-  </si>
-  <si>
     <t>한국</t>
   </si>
   <si>
@@ -236,6 +242,9 @@
     <t>신한, 한국</t>
   </si>
   <si>
+    <t>뱅크웨어글로벌</t>
+  </si>
+  <si>
     <t>아이빔테크놀로지</t>
   </si>
   <si>
@@ -299,6 +308,9 @@
     <t>신한글로벌액티브리츠</t>
   </si>
   <si>
+    <t>155.74:1</t>
+  </si>
+  <si>
     <t>1011.50:1</t>
   </si>
   <si>
@@ -362,6 +374,9 @@
     <t>38.7:1</t>
   </si>
   <si>
+    <t>1.52%</t>
+  </si>
+  <si>
     <t>0.49%</t>
   </si>
   <si>
@@ -398,6 +413,9 @@
     <t>0.95%</t>
   </si>
   <si>
+    <t>국내외 은행 및 금융기업 대상 코어뱅킹 소프트웨어</t>
+  </si>
+  <si>
     <t>생체현미경, CRO 서비스</t>
   </si>
   <si>
@@ -504,9 +522,6 @@
   </si>
   <si>
     <t>유라클</t>
-  </si>
-  <si>
-    <t>뱅크웨어글로벌</t>
   </si>
   <si>
     <t>NH스팩31호</t>
@@ -1083,7 +1098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y22"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1168,76 +1183,76 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F2">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="G2">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>7300</v>
+        <v>16000</v>
       </c>
       <c r="J2">
-        <v>8500</v>
+        <v>19000</v>
       </c>
       <c r="K2">
-        <v>14965620</v>
+        <v>10000988</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="N2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="O2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="P2">
-        <v>1337894447</v>
+        <v>72895458363</v>
       </c>
       <c r="Q2">
-        <v>4495088983</v>
+        <v>72913766913</v>
       </c>
       <c r="R2">
-        <v>99398351</v>
+        <v>11230711680</v>
       </c>
       <c r="S2">
-        <v>-3330678562</v>
+        <v>-6524077412</v>
       </c>
       <c r="T2">
-        <v>-2905069801</v>
+        <v>-4556157069</v>
       </c>
       <c r="U2">
-        <v>-1314068310</v>
+        <v>-3633759729</v>
       </c>
       <c r="V2">
-        <v>-9735376868</v>
+        <v>-11528915410</v>
       </c>
       <c r="W2">
-        <v>-5043515600</v>
+        <v>-7978634776</v>
       </c>
       <c r="X2">
-        <v>-1257080998</v>
+        <v>-3801868433</v>
       </c>
       <c r="Y2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1245,76 +1260,76 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F3">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="G3">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>14000</v>
+        <v>7300</v>
       </c>
       <c r="J3">
-        <v>17000</v>
+        <v>8500</v>
       </c>
       <c r="K3">
-        <v>6471740</v>
+        <v>14965620</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="N3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="O3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="P3">
-        <v>5214628820</v>
+        <v>1337894447</v>
       </c>
       <c r="Q3">
-        <v>6009352447</v>
+        <v>4495088983</v>
       </c>
       <c r="R3">
-        <v>965797975</v>
+        <v>99398351</v>
       </c>
       <c r="S3">
-        <v>2015081728</v>
+        <v>-3330678562</v>
       </c>
       <c r="T3">
-        <v>1319755337</v>
+        <v>-2905069801</v>
       </c>
       <c r="U3">
-        <v>-44547594</v>
+        <v>-1314068310</v>
       </c>
       <c r="V3">
-        <v>1503069100</v>
+        <v>-9735376868</v>
       </c>
       <c r="W3">
-        <v>1410469786</v>
+        <v>-5043515600</v>
       </c>
       <c r="X3">
-        <v>24178632</v>
+        <v>-1257080998</v>
       </c>
       <c r="Y3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1322,99 +1337,99 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F4">
-        <v>6000000</v>
+        <v>1350000</v>
       </c>
       <c r="G4">
-        <v>6000000</v>
+        <v>1350000</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>2000</v>
+        <v>14000</v>
       </c>
       <c r="J4">
-        <v>2000</v>
+        <v>17000</v>
       </c>
       <c r="K4">
-        <v>6345000</v>
+        <v>6471740</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>2000</v>
+        <v>22000</v>
       </c>
       <c r="N4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="O4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>5214628820</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>6009352447</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>965797975</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>2015081728</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>1319755337</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>-44547594</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1503069100</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1410469786</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>24178632</v>
       </c>
       <c r="Y4" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F5">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="G5">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1426,7 +1441,7 @@
         <v>2000</v>
       </c>
       <c r="K5">
-        <v>4420000</v>
+        <v>6345000</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1435,10 +1450,10 @@
         <v>2000</v>
       </c>
       <c r="N5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="O5" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1468,7 +1483,7 @@
         <v>0</v>
       </c>
       <c r="Y5" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1476,46 +1491,46 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F6">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="G6">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>6200</v>
+        <v>2000</v>
       </c>
       <c r="J6">
-        <v>7700</v>
+        <v>2000</v>
       </c>
       <c r="K6">
-        <v>10830212</v>
+        <v>4420000</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="N6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="O6" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1545,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1553,46 +1568,46 @@
         <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F7">
-        <v>4000000</v>
+        <v>1618000</v>
       </c>
       <c r="G7">
-        <v>4000000</v>
+        <v>1618000</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>2000</v>
+        <v>6200</v>
       </c>
       <c r="J7">
-        <v>2000</v>
+        <v>7700</v>
       </c>
       <c r="K7">
-        <v>5020000</v>
+        <v>10830212</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="N7" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="O7" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1622,7 +1637,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1630,76 +1645,76 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F8">
-        <v>1810000</v>
+        <v>4000000</v>
       </c>
       <c r="G8">
-        <v>1810000</v>
+        <v>4000000</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="J8">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="K8">
-        <v>7836009</v>
+        <v>5020000</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N8" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="O8" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="P8">
-        <v>12596039842</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>14910346438</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>16039074617</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>1732604466</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>2893667787</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>1613779678</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1558081149</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>2643467726</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>1795726428</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1707,76 +1722,76 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F9">
-        <v>1330000</v>
+        <v>1810000</v>
       </c>
       <c r="G9">
-        <v>1330000</v>
+        <v>1810000</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>36400</v>
+        <v>9000</v>
       </c>
       <c r="J9">
-        <v>43300</v>
+        <v>12000</v>
       </c>
       <c r="K9">
-        <v>9375694</v>
+        <v>7836009</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>43300</v>
+        <v>16000</v>
       </c>
       <c r="N9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="O9" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="P9">
-        <v>103267682</v>
+        <v>12596039842</v>
       </c>
       <c r="Q9">
-        <v>342201581</v>
+        <v>14910346438</v>
       </c>
       <c r="R9">
-        <v>231425455</v>
+        <v>16039074617</v>
       </c>
       <c r="S9">
-        <v>-7598692896</v>
+        <v>1732604466</v>
       </c>
       <c r="T9">
-        <v>-25822444575</v>
+        <v>2893667787</v>
       </c>
       <c r="U9">
-        <v>-15929213281</v>
+        <v>1613779678</v>
       </c>
       <c r="V9">
-        <v>-6973258680</v>
+        <v>1558081149</v>
       </c>
       <c r="W9">
-        <v>-48433907514</v>
+        <v>2643467726</v>
       </c>
       <c r="X9">
-        <v>-83246975113</v>
+        <v>1795726428</v>
       </c>
       <c r="Y9" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1784,76 +1799,76 @@
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F10">
-        <v>3400000</v>
+        <v>1330000</v>
       </c>
       <c r="G10">
-        <v>3400000</v>
+        <v>1330000</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>4500</v>
+        <v>36400</v>
       </c>
       <c r="J10">
-        <v>5500</v>
+        <v>43300</v>
       </c>
       <c r="K10">
-        <v>30888000</v>
+        <v>9375694</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>7000</v>
+        <v>43300</v>
       </c>
       <c r="N10" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="O10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="P10">
-        <v>85187882584</v>
+        <v>103267682</v>
       </c>
       <c r="Q10">
-        <v>87525689695</v>
+        <v>342201581</v>
       </c>
       <c r="R10">
-        <v>77247394706</v>
+        <v>231425455</v>
       </c>
       <c r="S10">
-        <v>2205797752</v>
+        <v>-7598692896</v>
       </c>
       <c r="T10">
-        <v>4920387020</v>
+        <v>-25822444575</v>
       </c>
       <c r="U10">
-        <v>4336496285</v>
+        <v>-15929213281</v>
       </c>
       <c r="V10">
-        <v>1613954566</v>
+        <v>-6973258680</v>
       </c>
       <c r="W10">
-        <v>3980493669</v>
+        <v>-48433907514</v>
       </c>
       <c r="X10">
-        <v>2646634321</v>
+        <v>-83246975113</v>
       </c>
       <c r="Y10" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1864,73 +1879,73 @@
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F11">
-        <v>6250000</v>
+        <v>3400000</v>
       </c>
       <c r="G11">
-        <v>6250000</v>
+        <v>3400000</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>2000</v>
+        <v>4500</v>
       </c>
       <c r="J11">
-        <v>2000</v>
+        <v>5500</v>
       </c>
       <c r="K11">
-        <v>6870000</v>
+        <v>30888000</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="N11" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="O11" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>85187882584</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>87525689695</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>77247394706</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>2205797752</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>4920387020</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>4336496285</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1613954566</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>3980493669</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>2646634321</v>
       </c>
       <c r="Y11" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1938,43 +1953,43 @@
         <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F12">
-        <v>2000000</v>
+        <v>6250000</v>
       </c>
       <c r="G12">
-        <v>2000000</v>
+        <v>6250000</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>7500</v>
+        <v>2000</v>
       </c>
       <c r="J12">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="K12">
-        <v>17529140</v>
+        <v>6870000</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <v>11500</v>
+        <v>2000</v>
       </c>
       <c r="N12" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="O12" t="s">
         <v>122</v>
@@ -2007,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -2015,46 +2030,46 @@
         <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F13">
-        <v>6450000</v>
+        <v>2000000</v>
       </c>
       <c r="G13">
-        <v>6450000</v>
+        <v>2000000</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>2000</v>
+        <v>7500</v>
       </c>
       <c r="J13">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="K13">
-        <v>6930000</v>
+        <v>17529140</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>2000</v>
+        <v>11500</v>
       </c>
       <c r="N13" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="O13" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -2084,7 +2099,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -2092,22 +2107,22 @@
         <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F14">
-        <v>6000000</v>
+        <v>6450000</v>
       </c>
       <c r="G14">
-        <v>6000000</v>
+        <v>6450000</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -2119,7 +2134,7 @@
         <v>2000</v>
       </c>
       <c r="K14">
-        <v>6220000</v>
+        <v>6930000</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -2128,10 +2143,10 @@
         <v>2000</v>
       </c>
       <c r="N14" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="O14" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -2161,30 +2176,30 @@
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
         <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F15">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="G15">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -2196,7 +2211,7 @@
         <v>2000</v>
       </c>
       <c r="K15">
-        <v>4810000</v>
+        <v>6220000</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -2205,10 +2220,10 @@
         <v>2000</v>
       </c>
       <c r="N15" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="O15" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -2238,30 +2253,30 @@
         <v>0</v>
       </c>
       <c r="Y15" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:25">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E16" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F16">
-        <v>4750000</v>
+        <v>4000000</v>
       </c>
       <c r="G16">
-        <v>4750000</v>
+        <v>4000000</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -2273,7 +2288,7 @@
         <v>2000</v>
       </c>
       <c r="K16">
-        <v>5480000</v>
+        <v>4810000</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -2282,10 +2297,10 @@
         <v>2000</v>
       </c>
       <c r="N16" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="O16" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -2315,84 +2330,84 @@
         <v>0</v>
       </c>
       <c r="Y16" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:25">
       <c r="A17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" t="s">
         <v>37</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>47</v>
       </c>
-      <c r="C17" t="s">
-        <v>45</v>
-      </c>
       <c r="D17" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F17">
-        <v>1300000</v>
+        <v>4750000</v>
       </c>
       <c r="G17">
-        <v>1300000</v>
+        <v>4750000</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>10500</v>
+        <v>2000</v>
       </c>
       <c r="J17">
-        <v>14000</v>
+        <v>2000</v>
       </c>
       <c r="K17">
-        <v>12293880</v>
+        <v>5480000</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <v>17000</v>
+        <v>2000</v>
       </c>
       <c r="N17" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="O17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P17">
-        <v>1386123525</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>1152944128</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>1885010467</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>-4388824706</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>-7990287699</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>-9803411085</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>-4430563401</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>-7988275689</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <v>-9916946238</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2400,230 +2415,230 @@
         <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
         <v>70</v>
       </c>
       <c r="E18" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F18">
-        <v>1600000</v>
+        <v>1300000</v>
       </c>
       <c r="G18">
-        <v>1600000</v>
+        <v>1300000</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>20000</v>
+        <v>10500</v>
       </c>
       <c r="J18">
-        <v>23500</v>
+        <v>14000</v>
       </c>
       <c r="K18">
-        <v>8751446</v>
+        <v>12293880</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>30000</v>
+        <v>17000</v>
       </c>
       <c r="N18" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="O18" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>1386123525</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>1152944128</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1885010467</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>-4388824706</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>-7990287699</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>-9803411085</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>-4430563401</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>-7988275689</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>-9916946238</v>
       </c>
       <c r="Y18" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:25">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D19" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E19" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F19">
-        <v>1298000</v>
+        <v>1600000</v>
       </c>
       <c r="G19">
-        <v>1298000</v>
+        <v>1600000</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>10400</v>
+        <v>20000</v>
       </c>
       <c r="J19">
-        <v>12700</v>
+        <v>23500</v>
       </c>
       <c r="K19">
-        <v>8650735</v>
+        <v>8751446</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>16000</v>
+        <v>30000</v>
       </c>
       <c r="N19" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="O19" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="P19">
-        <v>2055746777</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>2918221978</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>979078233</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>-3343774083</v>
+        <v>0</v>
       </c>
       <c r="T19">
-        <v>-3525649863</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>-1713494359</v>
+        <v>0</v>
       </c>
       <c r="V19">
-        <v>-4430074915</v>
+        <v>0</v>
       </c>
       <c r="W19">
-        <v>-8304699942</v>
+        <v>0</v>
       </c>
       <c r="X19">
-        <v>-1627684107</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:25">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" t="s">
         <v>48</v>
       </c>
-      <c r="C20" t="s">
-        <v>58</v>
-      </c>
       <c r="D20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E20" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F20">
-        <v>5000000</v>
+        <v>1298000</v>
       </c>
       <c r="G20">
-        <v>5000000</v>
+        <v>1298000</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>2000</v>
+        <v>10400</v>
       </c>
       <c r="J20">
-        <v>2000</v>
+        <v>12700</v>
       </c>
       <c r="K20">
-        <v>5840000</v>
+        <v>8650735</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>2000</v>
+        <v>16000</v>
       </c>
       <c r="N20" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="O20" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2055746777</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2918221978</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>979078233</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>-3343774083</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>-3525649863</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>-1713494359</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>-4430074915</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>-8304699942</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>-1627684107</v>
       </c>
       <c r="Y20" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2631,46 +2646,46 @@
         <v>40</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D21" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="E21" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F21">
-        <v>1400000</v>
+        <v>5000000</v>
       </c>
       <c r="G21">
-        <v>1400000</v>
+        <v>5000000</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21">
-        <v>34000</v>
+        <v>2000</v>
       </c>
       <c r="J21">
-        <v>40000</v>
+        <v>2000</v>
       </c>
       <c r="K21">
-        <v>7942750</v>
+        <v>5840000</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>40000</v>
+        <v>2000</v>
       </c>
       <c r="N21" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="O21" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -2700,84 +2715,161 @@
         <v>0</v>
       </c>
       <c r="Y21" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" spans="1:25">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" t="s">
+        <v>95</v>
+      </c>
+      <c r="F22">
+        <v>1400000</v>
+      </c>
+      <c r="G22">
+        <v>1400000</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>34000</v>
+      </c>
+      <c r="J22">
+        <v>40000</v>
+      </c>
+      <c r="K22">
+        <v>7942750</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>40000</v>
+      </c>
+      <c r="N22" t="s">
+        <v>117</v>
+      </c>
+      <c r="O22" t="s">
+        <v>131</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25">
+      <c r="A23" t="s">
         <v>35</v>
       </c>
-      <c r="C22" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" t="s">
-        <v>72</v>
-      </c>
-      <c r="E22" t="s">
-        <v>93</v>
-      </c>
-      <c r="F22">
+      <c r="B23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" t="s">
+        <v>74</v>
+      </c>
+      <c r="E23" t="s">
+        <v>96</v>
+      </c>
+      <c r="F23">
         <v>23333334</v>
       </c>
-      <c r="G22">
+      <c r="G23">
         <v>23333334</v>
       </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
         <v>3000</v>
       </c>
-      <c r="J22">
+      <c r="J23">
         <v>3800</v>
       </c>
-      <c r="K22">
+      <c r="K23">
         <v>43477664</v>
       </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
         <v>3000</v>
       </c>
-      <c r="N22" t="s">
-        <v>114</v>
-      </c>
-      <c r="O22" t="s">
-        <v>117</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>0</v>
-      </c>
-      <c r="V22">
-        <v>0</v>
-      </c>
-      <c r="W22">
-        <v>0</v>
-      </c>
-      <c r="X22">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>142</v>
+      <c r="N23" t="s">
+        <v>118</v>
+      </c>
+      <c r="O23" t="s">
+        <v>122</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -2792,422 +2884,422 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B2" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C2" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="F2" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F3" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B4" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C4" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D4" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E4" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F4" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B5" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C5" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D5" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E5" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F5" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B6" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C6" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D6" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E6" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F6" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B7" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C7" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D7" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E7" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F7" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B8" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C8" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="D8" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="E8" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="F8" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B9" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C9" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D9" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="E9" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="F9" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B10" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C10" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D10" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="E10" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F10" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B11" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C11" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D11" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E11" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="F11" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B12" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C12" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D12" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E12" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F12" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C13" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D13" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E13" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="F13" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C14" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D14" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E14" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="F14" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C15" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D15" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E15" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="F15" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>163</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C16" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="D16" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="E16" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="F16" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B17" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C17" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="D17" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E17" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F17" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B18" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C18" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D18" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E18" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F18" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B19" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C19" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D19" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E19" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="F19" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B20" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C20" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D20" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E20" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="F20" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B21" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C21" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="D21" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E21" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="F21" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="247">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -92,6 +92,9 @@
     <t>주요제품</t>
   </si>
   <si>
+    <t>2024-07-29</t>
+  </si>
+  <si>
     <t>2024-07-23</t>
   </si>
   <si>
@@ -143,7 +146,7 @@
     <t>2024-05-23</t>
   </si>
   <si>
-    <t>2024-07-29</t>
+    <t>2024-07-30</t>
   </si>
   <si>
     <t>2024-07-19</t>
@@ -170,6 +173,9 @@
     <t>2024-05-29</t>
   </si>
   <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
     <t>2024-07-25</t>
   </si>
   <si>
@@ -206,6 +212,9 @@
     <t>2024-07-01</t>
   </si>
   <si>
+    <t>교보</t>
+  </si>
+  <si>
     <t>미래</t>
   </si>
   <si>
@@ -242,6 +251,9 @@
     <t>신한, 한국</t>
   </si>
   <si>
+    <t>교보16호스팩</t>
+  </si>
+  <si>
     <t>뱅크웨어글로벌</t>
   </si>
   <si>
@@ -308,6 +320,9 @@
     <t>신한글로벌액티브리츠</t>
   </si>
   <si>
+    <t>1085.71:1</t>
+  </si>
+  <si>
     <t>155.74:1</t>
   </si>
   <si>
@@ -374,6 +389,9 @@
     <t>38.7:1</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>1.52%</t>
   </si>
   <si>
@@ -383,9 +401,6 @@
     <t>5.60%</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>4.50%</t>
   </si>
   <si>
@@ -413,6 +428,9 @@
     <t>0.95%</t>
   </si>
   <si>
+    <t>기업인수합병</t>
+  </si>
+  <si>
     <t>국내외 은행 및 금융기업 대상 코어뱅킹 소프트웨어</t>
   </si>
   <si>
@@ -438,9 +456,6 @@
   </si>
   <si>
     <t>전동기 및 발전기 (범용모터, 서보모터)</t>
-  </si>
-  <si>
-    <t>기업인수합병</t>
   </si>
   <si>
     <t>산업용 및 차량용 라이다(LiDAR)</t>
@@ -1098,7 +1113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y23"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1183,76 +1198,76 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F2">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="G2">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="J2">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="K2">
-        <v>10000988</v>
+        <v>6100000</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="O2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="P2">
-        <v>72895458363</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>72913766913</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>11230711680</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>-6524077412</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>-4556157069</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>-3633759729</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>-11528915410</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>-7978634776</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>-3801868433</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1260,76 +1275,76 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F3">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="G3">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>7300</v>
+        <v>16000</v>
       </c>
       <c r="J3">
-        <v>8500</v>
+        <v>19000</v>
       </c>
       <c r="K3">
-        <v>14965620</v>
+        <v>10000988</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="N3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="O3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="P3">
-        <v>1337894447</v>
+        <v>72895458363</v>
       </c>
       <c r="Q3">
-        <v>4495088983</v>
+        <v>72913766913</v>
       </c>
       <c r="R3">
-        <v>99398351</v>
+        <v>11230711680</v>
       </c>
       <c r="S3">
-        <v>-3330678562</v>
+        <v>-6524077412</v>
       </c>
       <c r="T3">
-        <v>-2905069801</v>
+        <v>-4556157069</v>
       </c>
       <c r="U3">
-        <v>-1314068310</v>
+        <v>-3633759729</v>
       </c>
       <c r="V3">
-        <v>-9735376868</v>
+        <v>-11528915410</v>
       </c>
       <c r="W3">
-        <v>-5043515600</v>
+        <v>-7978634776</v>
       </c>
       <c r="X3">
-        <v>-1257080998</v>
+        <v>-3801868433</v>
       </c>
       <c r="Y3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1340,73 +1355,73 @@
         <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F4">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="G4">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>14000</v>
+        <v>7300</v>
       </c>
       <c r="J4">
-        <v>17000</v>
+        <v>8500</v>
       </c>
       <c r="K4">
-        <v>6471740</v>
+        <v>14965620</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="N4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="O4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="P4">
-        <v>5214628820</v>
+        <v>1337894447</v>
       </c>
       <c r="Q4">
-        <v>6009352447</v>
+        <v>4495088983</v>
       </c>
       <c r="R4">
-        <v>965797975</v>
+        <v>99398351</v>
       </c>
       <c r="S4">
-        <v>2015081728</v>
+        <v>-3330678562</v>
       </c>
       <c r="T4">
-        <v>1319755337</v>
+        <v>-2905069801</v>
       </c>
       <c r="U4">
-        <v>-44547594</v>
+        <v>-1314068310</v>
       </c>
       <c r="V4">
-        <v>1503069100</v>
+        <v>-9735376868</v>
       </c>
       <c r="W4">
-        <v>1410469786</v>
+        <v>-5043515600</v>
       </c>
       <c r="X4">
-        <v>24178632</v>
+        <v>-1257080998</v>
       </c>
       <c r="Y4" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1417,96 +1432,96 @@
         <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F5">
-        <v>6000000</v>
+        <v>1350000</v>
       </c>
       <c r="G5">
-        <v>6000000</v>
+        <v>1350000</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>2000</v>
+        <v>14000</v>
       </c>
       <c r="J5">
-        <v>2000</v>
+        <v>17000</v>
       </c>
       <c r="K5">
-        <v>6345000</v>
+        <v>6471740</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>2000</v>
+        <v>22000</v>
       </c>
       <c r="N5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="O5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>5214628820</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>6009352447</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>965797975</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>2015081728</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1319755337</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>-44547594</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1503069100</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1410469786</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>24178632</v>
       </c>
       <c r="Y5" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:25">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F6">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="G6">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1518,7 +1533,7 @@
         <v>2000</v>
       </c>
       <c r="K6">
-        <v>4420000</v>
+        <v>6345000</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1527,10 +1542,10 @@
         <v>2000</v>
       </c>
       <c r="N6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="O6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1560,7 +1575,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1571,43 +1586,43 @@
         <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F7">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="G7">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>6200</v>
+        <v>2000</v>
       </c>
       <c r="J7">
-        <v>7700</v>
+        <v>2000</v>
       </c>
       <c r="K7">
-        <v>10830212</v>
+        <v>4420000</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="N7" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1637,7 +1652,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1645,46 +1660,46 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F8">
-        <v>4000000</v>
+        <v>1618000</v>
       </c>
       <c r="G8">
-        <v>4000000</v>
+        <v>1618000</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>2000</v>
+        <v>6200</v>
       </c>
       <c r="J8">
-        <v>2000</v>
+        <v>7700</v>
       </c>
       <c r="K8">
-        <v>5020000</v>
+        <v>10830212</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="N8" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="O8" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1714,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1725,73 +1740,73 @@
         <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F9">
-        <v>1810000</v>
+        <v>4000000</v>
       </c>
       <c r="G9">
-        <v>1810000</v>
+        <v>4000000</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="J9">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="K9">
-        <v>7836009</v>
+        <v>5020000</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N9" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="O9" t="s">
         <v>124</v>
       </c>
       <c r="P9">
-        <v>12596039842</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>14910346438</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>16039074617</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>1732604466</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>2893667787</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>1613779678</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>1558081149</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>2643467726</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>1795726428</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1802,73 +1817,73 @@
         <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F10">
-        <v>1330000</v>
+        <v>1810000</v>
       </c>
       <c r="G10">
-        <v>1330000</v>
+        <v>1810000</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>36400</v>
+        <v>9000</v>
       </c>
       <c r="J10">
-        <v>43300</v>
+        <v>12000</v>
       </c>
       <c r="K10">
-        <v>9375694</v>
+        <v>7836009</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>43300</v>
+        <v>16000</v>
       </c>
       <c r="N10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="O10" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="P10">
-        <v>103267682</v>
+        <v>12596039842</v>
       </c>
       <c r="Q10">
-        <v>342201581</v>
+        <v>14910346438</v>
       </c>
       <c r="R10">
-        <v>231425455</v>
+        <v>16039074617</v>
       </c>
       <c r="S10">
-        <v>-7598692896</v>
+        <v>1732604466</v>
       </c>
       <c r="T10">
-        <v>-25822444575</v>
+        <v>2893667787</v>
       </c>
       <c r="U10">
-        <v>-15929213281</v>
+        <v>1613779678</v>
       </c>
       <c r="V10">
-        <v>-6973258680</v>
+        <v>1558081149</v>
       </c>
       <c r="W10">
-        <v>-48433907514</v>
+        <v>2643467726</v>
       </c>
       <c r="X10">
-        <v>-83246975113</v>
+        <v>1795726428</v>
       </c>
       <c r="Y10" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1876,76 +1891,76 @@
         <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F11">
-        <v>3400000</v>
+        <v>1330000</v>
       </c>
       <c r="G11">
-        <v>3400000</v>
+        <v>1330000</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>4500</v>
+        <v>36400</v>
       </c>
       <c r="J11">
-        <v>5500</v>
+        <v>43300</v>
       </c>
       <c r="K11">
-        <v>30888000</v>
+        <v>9375694</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>7000</v>
+        <v>43300</v>
       </c>
       <c r="N11" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="O11" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="P11">
-        <v>85187882584</v>
+        <v>103267682</v>
       </c>
       <c r="Q11">
-        <v>87525689695</v>
+        <v>342201581</v>
       </c>
       <c r="R11">
-        <v>77247394706</v>
+        <v>231425455</v>
       </c>
       <c r="S11">
-        <v>2205797752</v>
+        <v>-7598692896</v>
       </c>
       <c r="T11">
-        <v>4920387020</v>
+        <v>-25822444575</v>
       </c>
       <c r="U11">
-        <v>4336496285</v>
+        <v>-15929213281</v>
       </c>
       <c r="V11">
-        <v>1613954566</v>
+        <v>-6973258680</v>
       </c>
       <c r="W11">
-        <v>3980493669</v>
+        <v>-48433907514</v>
       </c>
       <c r="X11">
-        <v>2646634321</v>
+        <v>-83246975113</v>
       </c>
       <c r="Y11" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1956,73 +1971,73 @@
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E12" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F12">
-        <v>6250000</v>
+        <v>3400000</v>
       </c>
       <c r="G12">
-        <v>6250000</v>
+        <v>3400000</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>2000</v>
+        <v>4500</v>
       </c>
       <c r="J12">
-        <v>2000</v>
+        <v>5500</v>
       </c>
       <c r="K12">
-        <v>6870000</v>
+        <v>30888000</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="N12" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="O12" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>85187882584</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>87525689695</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>77247394706</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>2205797752</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>4920387020</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>4336496285</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1613954566</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>3980493669</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>2646634321</v>
       </c>
       <c r="Y12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -2030,46 +2045,46 @@
         <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E13" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F13">
-        <v>2000000</v>
+        <v>6250000</v>
       </c>
       <c r="G13">
-        <v>2000000</v>
+        <v>6250000</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>7500</v>
+        <v>2000</v>
       </c>
       <c r="J13">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="K13">
-        <v>17529140</v>
+        <v>6870000</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>11500</v>
+        <v>2000</v>
       </c>
       <c r="N13" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O13" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -2099,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -2107,46 +2122,46 @@
         <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E14" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F14">
-        <v>6450000</v>
+        <v>2000000</v>
       </c>
       <c r="G14">
-        <v>6450000</v>
+        <v>2000000</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>2000</v>
+        <v>7500</v>
       </c>
       <c r="J14">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="K14">
-        <v>6930000</v>
+        <v>17529140</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>2000</v>
+        <v>11500</v>
       </c>
       <c r="N14" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="O14" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -2176,7 +2191,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -2184,22 +2199,22 @@
         <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F15">
-        <v>6000000</v>
+        <v>6450000</v>
       </c>
       <c r="G15">
-        <v>6000000</v>
+        <v>6450000</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -2211,7 +2226,7 @@
         <v>2000</v>
       </c>
       <c r="K15">
-        <v>6220000</v>
+        <v>6930000</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -2220,10 +2235,10 @@
         <v>2000</v>
       </c>
       <c r="N15" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="O15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -2253,30 +2268,30 @@
         <v>0</v>
       </c>
       <c r="Y15" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" spans="1:25">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
         <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F16">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="G16">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -2288,7 +2303,7 @@
         <v>2000</v>
       </c>
       <c r="K16">
-        <v>4810000</v>
+        <v>6220000</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -2297,10 +2312,10 @@
         <v>2000</v>
       </c>
       <c r="N16" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="O16" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -2330,30 +2345,30 @@
         <v>0</v>
       </c>
       <c r="Y16" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:25">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E17" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F17">
-        <v>4750000</v>
+        <v>4000000</v>
       </c>
       <c r="G17">
-        <v>4750000</v>
+        <v>4000000</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -2365,7 +2380,7 @@
         <v>2000</v>
       </c>
       <c r="K17">
-        <v>5480000</v>
+        <v>4810000</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -2374,10 +2389,10 @@
         <v>2000</v>
       </c>
       <c r="N17" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="O17" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -2407,84 +2422,84 @@
         <v>0</v>
       </c>
       <c r="Y17" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" spans="1:25">
       <c r="A18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" t="s">
         <v>38</v>
       </c>
-      <c r="B18" t="s">
-        <v>49</v>
-      </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E18" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F18">
-        <v>1300000</v>
+        <v>4750000</v>
       </c>
       <c r="G18">
-        <v>1300000</v>
+        <v>4750000</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>10500</v>
+        <v>2000</v>
       </c>
       <c r="J18">
-        <v>14000</v>
+        <v>2000</v>
       </c>
       <c r="K18">
-        <v>12293880</v>
+        <v>5480000</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>17000</v>
+        <v>2000</v>
       </c>
       <c r="N18" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="O18" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="P18">
-        <v>1386123525</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>1152944128</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>1885010467</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>-4388824706</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>-7990287699</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>-9803411085</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>-4430563401</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>-7988275689</v>
+        <v>0</v>
       </c>
       <c r="X18">
-        <v>-9916946238</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2492,230 +2507,230 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="D19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E19" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F19">
-        <v>1600000</v>
+        <v>1300000</v>
       </c>
       <c r="G19">
-        <v>1600000</v>
+        <v>1300000</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>20000</v>
+        <v>10500</v>
       </c>
       <c r="J19">
-        <v>23500</v>
+        <v>14000</v>
       </c>
       <c r="K19">
-        <v>8751446</v>
+        <v>12293880</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>30000</v>
+        <v>17000</v>
       </c>
       <c r="N19" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="O19" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>1386123525</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>1152944128</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1885010467</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>-4388824706</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>-7990287699</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>-9803411085</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>-4430563401</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>-7988275689</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>-9916946238</v>
       </c>
       <c r="Y19" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:25">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F20">
-        <v>1298000</v>
+        <v>1600000</v>
       </c>
       <c r="G20">
-        <v>1298000</v>
+        <v>1600000</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>10400</v>
+        <v>20000</v>
       </c>
       <c r="J20">
-        <v>12700</v>
+        <v>23500</v>
       </c>
       <c r="K20">
-        <v>8650735</v>
+        <v>8751446</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>16000</v>
+        <v>30000</v>
       </c>
       <c r="N20" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="O20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="P20">
-        <v>2055746777</v>
+        <v>0</v>
       </c>
       <c r="Q20">
-        <v>2918221978</v>
+        <v>0</v>
       </c>
       <c r="R20">
-        <v>979078233</v>
+        <v>0</v>
       </c>
       <c r="S20">
-        <v>-3343774083</v>
+        <v>0</v>
       </c>
       <c r="T20">
-        <v>-3525649863</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>-1713494359</v>
+        <v>0</v>
       </c>
       <c r="V20">
-        <v>-4430074915</v>
+        <v>0</v>
       </c>
       <c r="W20">
-        <v>-8304699942</v>
+        <v>0</v>
       </c>
       <c r="X20">
-        <v>-1627684107</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:25">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B21" t="s">
         <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E21" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F21">
-        <v>5000000</v>
+        <v>1298000</v>
       </c>
       <c r="G21">
-        <v>5000000</v>
+        <v>1298000</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21">
-        <v>2000</v>
+        <v>10400</v>
       </c>
       <c r="J21">
-        <v>2000</v>
+        <v>12700</v>
       </c>
       <c r="K21">
-        <v>5840000</v>
+        <v>8650735</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>2000</v>
+        <v>16000</v>
       </c>
       <c r="N21" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O21" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2055746777</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2918221978</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>979078233</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>-3343774083</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>-3525649863</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>-1713494359</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>-4430074915</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>-8304699942</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>-1627684107</v>
       </c>
       <c r="Y21" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2723,46 +2738,46 @@
         <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D22" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="E22" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F22">
-        <v>1400000</v>
+        <v>5000000</v>
       </c>
       <c r="G22">
-        <v>1400000</v>
+        <v>5000000</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
       <c r="I22">
-        <v>34000</v>
+        <v>2000</v>
       </c>
       <c r="J22">
-        <v>40000</v>
+        <v>2000</v>
       </c>
       <c r="K22">
-        <v>7942750</v>
+        <v>5840000</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22">
-        <v>40000</v>
+        <v>2000</v>
       </c>
       <c r="N22" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="O22" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -2792,84 +2807,161 @@
         <v>0</v>
       </c>
       <c r="Y22" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:25">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B23" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" t="s">
+        <v>67</v>
+      </c>
+      <c r="E23" t="s">
+        <v>99</v>
+      </c>
+      <c r="F23">
+        <v>1400000</v>
+      </c>
+      <c r="G23">
+        <v>1400000</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>34000</v>
+      </c>
+      <c r="J23">
+        <v>40000</v>
+      </c>
+      <c r="K23">
+        <v>7942750</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>40000</v>
+      </c>
+      <c r="N23" t="s">
+        <v>122</v>
+      </c>
+      <c r="O23" t="s">
+        <v>136</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
+      <c r="A24" t="s">
         <v>36</v>
       </c>
-      <c r="C23" t="s">
-        <v>62</v>
-      </c>
-      <c r="D23" t="s">
-        <v>74</v>
-      </c>
-      <c r="E23" t="s">
-        <v>96</v>
-      </c>
-      <c r="F23">
+      <c r="B24" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" t="s">
+        <v>100</v>
+      </c>
+      <c r="F24">
         <v>23333334</v>
       </c>
-      <c r="G23">
+      <c r="G24">
         <v>23333334</v>
       </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
         <v>3000</v>
       </c>
-      <c r="J23">
+      <c r="J24">
         <v>3800</v>
       </c>
-      <c r="K23">
+      <c r="K24">
         <v>43477664</v>
       </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
         <v>3000</v>
       </c>
-      <c r="N23" t="s">
-        <v>118</v>
-      </c>
-      <c r="O23" t="s">
-        <v>122</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>0</v>
-      </c>
-      <c r="V23">
-        <v>0</v>
-      </c>
-      <c r="W23">
-        <v>0</v>
-      </c>
-      <c r="X23">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>148</v>
+      <c r="N24" t="s">
+        <v>123</v>
+      </c>
+      <c r="O24" t="s">
+        <v>124</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -2884,422 +2976,422 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B2" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E2" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="F2" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B3" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C3" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F3" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B4" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C4" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E4" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="F4" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B5" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C5" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E5" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F5" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B6" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C6" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E6" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="F6" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B7" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C7" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D7" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E7" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F7" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B8" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C8" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D8" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E8" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="F8" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B9" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C9" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="D9" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E9" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="F9" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B10" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C10" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="D10" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E10" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F10" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B11" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C11" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D11" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E11" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F11" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B12" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C12" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="D12" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E12" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F12" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B13" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C13" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D13" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E13" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="F13" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C14" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D14" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E14" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="F14" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C15" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D15" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="E15" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="F15" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B16" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C16" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D16" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E16" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="F16" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B17" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C17" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="D17" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E17" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F17" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B18" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C18" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D18" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="E18" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="F18" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B19" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C19" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D19" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E19" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="F19" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B20" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C20" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D20" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E20" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="F20" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B21" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C21" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D21" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E21" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F21" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="241">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -143,9 +143,6 @@
     <t>2024-05-28</t>
   </si>
   <si>
-    <t>2024-05-23</t>
-  </si>
-  <si>
     <t>2024-07-30</t>
   </si>
   <si>
@@ -206,9 +203,6 @@
     <t>2024-06-18</t>
   </si>
   <si>
-    <t>2024-06-14</t>
-  </si>
-  <si>
     <t>2024-07-01</t>
   </si>
   <si>
@@ -314,9 +308,6 @@
     <t>디비금융스팩12호</t>
   </si>
   <si>
-    <t>그리드위즈</t>
-  </si>
-  <si>
     <t>신한글로벌액티브리츠</t>
   </si>
   <si>
@@ -383,9 +374,6 @@
     <t>1141.40:1</t>
   </si>
   <si>
-    <t>124.60:1</t>
-  </si>
-  <si>
     <t>38.7:1</t>
   </si>
   <si>
@@ -425,9 +413,6 @@
     <t>9.93%</t>
   </si>
   <si>
-    <t>0.95%</t>
-  </si>
-  <si>
     <t>기업인수합병</t>
   </si>
   <si>
@@ -471,9 +456,6 @@
   </si>
   <si>
     <t>기업인수 및 합병</t>
-  </si>
-  <si>
-    <t>수요관리 서비스, 전기차 충전기 모뎀 등</t>
   </si>
   <si>
     <t>신탁 및 집합투자</t>
@@ -1113,7 +1095,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y24"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1198,16 +1180,16 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F2">
         <v>5800000</v>
@@ -1234,10 +1216,10 @@
         <v>2000</v>
       </c>
       <c r="N2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -1267,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="Y2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1278,13 +1260,13 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F3">
         <v>1400000</v>
@@ -1311,10 +1293,10 @@
         <v>16000</v>
       </c>
       <c r="N3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="O3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="P3">
         <v>72895458363</v>
@@ -1344,7 +1326,7 @@
         <v>-3801868433</v>
       </c>
       <c r="Y3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1352,16 +1334,16 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F4">
         <v>2234000</v>
@@ -1388,10 +1370,10 @@
         <v>10000</v>
       </c>
       <c r="N4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="O4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="P4">
         <v>1337894447</v>
@@ -1421,7 +1403,7 @@
         <v>-1257080998</v>
       </c>
       <c r="Y4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1429,16 +1411,16 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F5">
         <v>1350000</v>
@@ -1465,10 +1447,10 @@
         <v>22000</v>
       </c>
       <c r="N5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="P5">
         <v>5214628820</v>
@@ -1498,7 +1480,7 @@
         <v>24178632</v>
       </c>
       <c r="Y5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1506,16 +1488,16 @@
         <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F6">
         <v>6000000</v>
@@ -1542,10 +1524,10 @@
         <v>2000</v>
       </c>
       <c r="N6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="O6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1575,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1583,16 +1565,16 @@
         <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F7">
         <v>4000000</v>
@@ -1619,10 +1601,10 @@
         <v>2000</v>
       </c>
       <c r="N7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1652,7 +1634,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1660,16 +1642,16 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
         <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F8">
         <v>1618000</v>
@@ -1696,10 +1678,10 @@
         <v>10000</v>
       </c>
       <c r="N8" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="O8" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1729,7 +1711,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1737,16 +1719,16 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F9">
         <v>4000000</v>
@@ -1773,10 +1755,10 @@
         <v>2000</v>
       </c>
       <c r="N9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="O9" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1806,7 +1788,7 @@
         <v>0</v>
       </c>
       <c r="Y9" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1814,16 +1796,16 @@
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F10">
         <v>1810000</v>
@@ -1850,10 +1832,10 @@
         <v>16000</v>
       </c>
       <c r="N10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="O10" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="P10">
         <v>12596039842</v>
@@ -1883,7 +1865,7 @@
         <v>1795726428</v>
       </c>
       <c r="Y10" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1891,16 +1873,16 @@
         <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F11">
         <v>1330000</v>
@@ -1927,10 +1909,10 @@
         <v>43300</v>
       </c>
       <c r="N11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="O11" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="P11">
         <v>103267682</v>
@@ -1960,7 +1942,7 @@
         <v>-83246975113</v>
       </c>
       <c r="Y11" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1974,10 +1956,10 @@
         <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F12">
         <v>3400000</v>
@@ -2004,10 +1986,10 @@
         <v>7000</v>
       </c>
       <c r="N12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="O12" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="P12">
         <v>85187882584</v>
@@ -2037,7 +2019,7 @@
         <v>2646634321</v>
       </c>
       <c r="Y12" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -2048,13 +2030,13 @@
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F13">
         <v>6250000</v>
@@ -2081,10 +2063,10 @@
         <v>2000</v>
       </c>
       <c r="N13" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="O13" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -2114,7 +2096,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -2125,13 +2107,13 @@
         <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E14" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F14">
         <v>2000000</v>
@@ -2158,10 +2140,10 @@
         <v>11500</v>
       </c>
       <c r="N14" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="O14" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -2191,7 +2173,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -2205,10 +2187,10 @@
         <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F15">
         <v>6450000</v>
@@ -2235,10 +2217,10 @@
         <v>2000</v>
       </c>
       <c r="N15" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="O15" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -2268,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="Y15" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -2279,13 +2261,13 @@
         <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F16">
         <v>6000000</v>
@@ -2312,10 +2294,10 @@
         <v>2000</v>
       </c>
       <c r="N16" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="O16" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -2345,7 +2327,7 @@
         <v>0</v>
       </c>
       <c r="Y16" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2356,13 +2338,13 @@
         <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F17">
         <v>4000000</v>
@@ -2389,10 +2371,10 @@
         <v>2000</v>
       </c>
       <c r="N17" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="O17" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -2422,7 +2404,7 @@
         <v>0</v>
       </c>
       <c r="Y17" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2433,13 +2415,13 @@
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E18" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F18">
         <v>4750000</v>
@@ -2466,10 +2448,10 @@
         <v>2000</v>
       </c>
       <c r="N18" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="O18" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -2499,7 +2481,7 @@
         <v>0</v>
       </c>
       <c r="Y18" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2507,16 +2489,16 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D19" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E19" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F19">
         <v>1300000</v>
@@ -2543,10 +2525,10 @@
         <v>17000</v>
       </c>
       <c r="N19" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="O19" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="P19">
         <v>1386123525</v>
@@ -2576,7 +2558,7 @@
         <v>-9916946238</v>
       </c>
       <c r="Y19" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2590,10 +2572,10 @@
         <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E20" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F20">
         <v>1600000</v>
@@ -2620,10 +2602,10 @@
         <v>30000</v>
       </c>
       <c r="N20" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O20" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -2653,7 +2635,7 @@
         <v>0</v>
       </c>
       <c r="Y20" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2661,16 +2643,16 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D21" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E21" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F21">
         <v>1298000</v>
@@ -2697,10 +2679,10 @@
         <v>16000</v>
       </c>
       <c r="N21" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O21" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="P21">
         <v>2055746777</v>
@@ -2730,7 +2712,7 @@
         <v>-1627684107</v>
       </c>
       <c r="Y21" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2738,16 +2720,16 @@
         <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F22">
         <v>5000000</v>
@@ -2774,10 +2756,10 @@
         <v>2000</v>
       </c>
       <c r="N22" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="O22" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -2807,54 +2789,54 @@
         <v>0</v>
       </c>
       <c r="Y22" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="23" spans="1:25">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="E23" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F23">
-        <v>1400000</v>
+        <v>23333334</v>
       </c>
       <c r="G23">
-        <v>1400000</v>
+        <v>23333334</v>
       </c>
       <c r="H23">
         <v>0</v>
       </c>
       <c r="I23">
-        <v>34000</v>
+        <v>3000</v>
       </c>
       <c r="J23">
-        <v>40000</v>
+        <v>3800</v>
       </c>
       <c r="K23">
-        <v>7942750</v>
+        <v>43477664</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23">
-        <v>40000</v>
+        <v>3000</v>
       </c>
       <c r="N23" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O23" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -2884,84 +2866,7 @@
         <v>0</v>
       </c>
       <c r="Y23" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25">
-      <c r="A24" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" t="s">
-        <v>64</v>
-      </c>
-      <c r="D24" t="s">
-        <v>77</v>
-      </c>
-      <c r="E24" t="s">
-        <v>100</v>
-      </c>
-      <c r="F24">
-        <v>23333334</v>
-      </c>
-      <c r="G24">
-        <v>23333334</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>3000</v>
-      </c>
-      <c r="J24">
-        <v>3800</v>
-      </c>
-      <c r="K24">
-        <v>43477664</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>3000</v>
-      </c>
-      <c r="N24" t="s">
-        <v>123</v>
-      </c>
-      <c r="O24" t="s">
-        <v>124</v>
-      </c>
-      <c r="P24">
-        <v>0</v>
-      </c>
-      <c r="Q24">
-        <v>0</v>
-      </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
-      <c r="U24">
-        <v>0</v>
-      </c>
-      <c r="V24">
-        <v>0</v>
-      </c>
-      <c r="W24">
-        <v>0</v>
-      </c>
-      <c r="X24">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -2976,422 +2881,422 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B2" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E2" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="F2" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C3" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F3" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C4" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E4" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="F4" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B5" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C5" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E5" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="F5" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B6" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C6" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E6" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="F6" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B7" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C7" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D7" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="E7" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="F7" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B8" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C8" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D8" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="E8" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="F8" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B9" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C9" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D9" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E9" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="F9" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B10" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C10" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D10" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="E10" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="F10" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B11" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C11" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D11" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="E11" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="F11" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B12" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C12" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D12" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="E12" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="F12" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C13" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D13" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="E13" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="F13" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C14" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D14" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="E14" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="F14" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s">
+        <v>182</v>
+      </c>
+      <c r="C15" t="s">
         <v>188</v>
       </c>
-      <c r="C15" t="s">
-        <v>194</v>
-      </c>
       <c r="D15" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="E15" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="F15" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B16" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C16" t="s">
+        <v>198</v>
+      </c>
+      <c r="D16" t="s">
         <v>204</v>
       </c>
-      <c r="D16" t="s">
-        <v>210</v>
-      </c>
       <c r="E16" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="F16" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B17" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C17" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D17" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="E17" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="F17" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B18" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C18" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D18" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E18" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F18" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B19" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C19" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D19" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="E19" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="F19" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B20" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C20" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D20" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="E20" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="F20" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B21" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C21" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D21" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="E21" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="F21" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -479,15 +479,15 @@
     <t>주간사</t>
   </si>
   <si>
+    <t>아이언디바이스</t>
+  </si>
+  <si>
     <t>에이치이엠파마(구.에이치이엠)</t>
   </si>
   <si>
     <t>미래에셋비전스팩7호</t>
   </si>
   <si>
-    <t>아이언디바이스</t>
-  </si>
-  <si>
     <t>키움스팩9호</t>
   </si>
   <si>
@@ -530,15 +530,15 @@
     <t>산일전기(유가)</t>
   </si>
   <si>
+    <t>2024.08.30~09.05</t>
+  </si>
+  <si>
     <t>2024.08.26~08.30</t>
   </si>
   <si>
     <t>2024.08.26~08.27</t>
   </si>
   <si>
-    <t>2024.08.19~08.23</t>
-  </si>
-  <si>
     <t>2024.08.13~08.14</t>
   </si>
   <si>
@@ -581,15 +581,15 @@
     <t>2024.07.09~07.15</t>
   </si>
   <si>
+    <t>4,900~5,700</t>
+  </si>
+  <si>
     <t>18,000~21,000</t>
   </si>
   <si>
     <t>2,000~2,000</t>
   </si>
   <si>
-    <t>4,900~5,700</t>
-  </si>
-  <si>
     <t>32,000~40,200</t>
   </si>
   <si>
@@ -656,12 +656,12 @@
     <t>35000</t>
   </si>
   <si>
+    <t>14700</t>
+  </si>
+  <si>
     <t>12546</t>
   </si>
   <si>
-    <t>14700</t>
-  </si>
-  <si>
     <t>6000</t>
   </si>
   <si>
@@ -704,13 +704,13 @@
     <t>266000</t>
   </si>
   <si>
+    <t>대신증권</t>
+  </si>
+  <si>
     <t>신한투자증권</t>
   </si>
   <si>
     <t>미래에셋증권</t>
-  </si>
-  <si>
-    <t>대신증권</t>
   </si>
   <si>
     <t>키움증권</t>
@@ -2933,7 +2933,7 @@
         <v>120</v>
       </c>
       <c r="E3" t="s">
-        <v>120</v>
+        <v>214</v>
       </c>
       <c r="F3" t="s">
         <v>230</v>
@@ -2953,7 +2953,7 @@
         <v>120</v>
       </c>
       <c r="E4" t="s">
-        <v>214</v>
+        <v>120</v>
       </c>
       <c r="F4" t="s">
         <v>231</v>
@@ -2967,7 +2967,7 @@
         <v>174</v>
       </c>
       <c r="C5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D5" t="s">
         <v>120</v>
@@ -3007,7 +3007,7 @@
         <v>176</v>
       </c>
       <c r="C7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D7" t="s">
         <v>202</v>
@@ -3016,7 +3016,7 @@
         <v>205</v>
       </c>
       <c r="F7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3116,7 +3116,7 @@
         <v>220</v>
       </c>
       <c r="F12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3127,7 +3127,7 @@
         <v>181</v>
       </c>
       <c r="C13" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D13" t="s">
         <v>202</v>
@@ -3167,7 +3167,7 @@
         <v>182</v>
       </c>
       <c r="C15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D15" t="s">
         <v>209</v>
@@ -3196,7 +3196,7 @@
         <v>223</v>
       </c>
       <c r="F16" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -3247,7 +3247,7 @@
         <v>186</v>
       </c>
       <c r="C19" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D19" t="s">
         <v>202</v>
@@ -3267,7 +3267,7 @@
         <v>186</v>
       </c>
       <c r="C20" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D20" t="s">
         <v>202</v>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="246">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -143,6 +143,9 @@
     <t>2024-05-28</t>
   </si>
   <si>
+    <t>2024-08-02</t>
+  </si>
+  <si>
     <t>2024-07-30</t>
   </si>
   <si>
@@ -170,6 +173,9 @@
     <t>2024-05-29</t>
   </si>
   <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
     <t>2024-08-13</t>
   </si>
   <si>
@@ -206,6 +212,9 @@
     <t>2024-07-01</t>
   </si>
   <si>
+    <t>키움</t>
+  </si>
+  <si>
     <t>교보</t>
   </si>
   <si>
@@ -215,9 +224,6 @@
     <t>삼성</t>
   </si>
   <si>
-    <t>키움</t>
-  </si>
-  <si>
     <t>NH</t>
   </si>
   <si>
@@ -245,6 +251,9 @@
     <t>신한, 한국</t>
   </si>
   <si>
+    <t>유라클</t>
+  </si>
+  <si>
     <t>교보16호스팩</t>
   </si>
   <si>
@@ -311,6 +320,9 @@
     <t>신한글로벌액티브리츠</t>
   </si>
   <si>
+    <t>1065.86:1</t>
+  </si>
+  <si>
     <t>1085.71:1</t>
   </si>
   <si>
@@ -377,6 +389,9 @@
     <t>38.7:1</t>
   </si>
   <si>
+    <t>0.55%</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
@@ -413,6 +428,9 @@
     <t>9.93%</t>
   </si>
   <si>
+    <t>모바일 앱 개발 플랫폼</t>
+  </si>
+  <si>
     <t>기업인수합병</t>
   </si>
   <si>
@@ -516,9 +534,6 @@
   </si>
   <si>
     <t>넥스트바이오메디컬</t>
-  </si>
-  <si>
-    <t>유라클</t>
   </si>
   <si>
     <t>NH스팩31호</t>
@@ -1095,7 +1110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y23"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1183,43 +1198,43 @@
         <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F2">
-        <v>5800000</v>
+        <v>751000</v>
       </c>
       <c r="G2">
-        <v>5800000</v>
+        <v>203700</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>547300</v>
       </c>
       <c r="I2">
-        <v>2000</v>
+        <v>18000</v>
       </c>
       <c r="J2">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="K2">
-        <v>6100000</v>
+        <v>4330068</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="N2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="O2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -1249,315 +1264,315 @@
         <v>0</v>
       </c>
       <c r="Y2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:25">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F3">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="G3">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="J3">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="K3">
-        <v>10000988</v>
+        <v>6100000</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="O3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="P3">
-        <v>72895458363</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>72913766913</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>11230711680</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>-6524077412</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>-4556157069</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>-3633759729</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>-11528915410</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>-7978634776</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>-3801868433</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:25">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F4">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="G4">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>7300</v>
+        <v>16000</v>
       </c>
       <c r="J4">
-        <v>8500</v>
+        <v>19000</v>
       </c>
       <c r="K4">
-        <v>14965620</v>
+        <v>10000988</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="N4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="O4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="P4">
-        <v>1337894447</v>
+        <v>72895458363</v>
       </c>
       <c r="Q4">
-        <v>4495088983</v>
+        <v>72913766913</v>
       </c>
       <c r="R4">
-        <v>99398351</v>
+        <v>11230711680</v>
       </c>
       <c r="S4">
-        <v>-3330678562</v>
+        <v>-6524077412</v>
       </c>
       <c r="T4">
-        <v>-2905069801</v>
+        <v>-4556157069</v>
       </c>
       <c r="U4">
-        <v>-1314068310</v>
+        <v>-3633759729</v>
       </c>
       <c r="V4">
-        <v>-9735376868</v>
+        <v>-11528915410</v>
       </c>
       <c r="W4">
-        <v>-5043515600</v>
+        <v>-7978634776</v>
       </c>
       <c r="X4">
-        <v>-1257080998</v>
+        <v>-3801868433</v>
       </c>
       <c r="Y4" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
         <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F5">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="G5">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>14000</v>
+        <v>7300</v>
       </c>
       <c r="J5">
-        <v>17000</v>
+        <v>8500</v>
       </c>
       <c r="K5">
-        <v>6471740</v>
+        <v>14965620</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="N5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="O5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="P5">
-        <v>5214628820</v>
+        <v>1337894447</v>
       </c>
       <c r="Q5">
-        <v>6009352447</v>
+        <v>4495088983</v>
       </c>
       <c r="R5">
-        <v>965797975</v>
+        <v>99398351</v>
       </c>
       <c r="S5">
-        <v>2015081728</v>
+        <v>-3330678562</v>
       </c>
       <c r="T5">
-        <v>1319755337</v>
+        <v>-2905069801</v>
       </c>
       <c r="U5">
-        <v>-44547594</v>
+        <v>-1314068310</v>
       </c>
       <c r="V5">
-        <v>1503069100</v>
+        <v>-9735376868</v>
       </c>
       <c r="W5">
-        <v>1410469786</v>
+        <v>-5043515600</v>
       </c>
       <c r="X5">
-        <v>24178632</v>
+        <v>-1257080998</v>
       </c>
       <c r="Y5" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:25">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
         <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F6">
-        <v>6000000</v>
+        <v>1350000</v>
       </c>
       <c r="G6">
-        <v>6000000</v>
+        <v>1350000</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>2000</v>
+        <v>14000</v>
       </c>
       <c r="J6">
-        <v>2000</v>
+        <v>17000</v>
       </c>
       <c r="K6">
-        <v>6345000</v>
+        <v>6471740</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>2000</v>
+        <v>22000</v>
       </c>
       <c r="N6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="O6" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>5214628820</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>6009352447</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>965797975</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>2015081728</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1319755337</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>-44547594</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1503069100</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1410469786</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>24178632</v>
       </c>
       <c r="Y6" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1565,22 +1580,22 @@
         <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F7">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="G7">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1592,7 +1607,7 @@
         <v>2000</v>
       </c>
       <c r="K7">
-        <v>4420000</v>
+        <v>6345000</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1601,10 +1616,10 @@
         <v>2000</v>
       </c>
       <c r="N7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="O7" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1634,54 +1649,54 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
         <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F8">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="G8">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>6200</v>
+        <v>2000</v>
       </c>
       <c r="J8">
-        <v>7700</v>
+        <v>2000</v>
       </c>
       <c r="K8">
-        <v>10830212</v>
+        <v>4420000</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="N8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="O8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1711,54 +1726,54 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F9">
-        <v>4000000</v>
+        <v>1618000</v>
       </c>
       <c r="G9">
-        <v>4000000</v>
+        <v>1618000</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>2000</v>
+        <v>6200</v>
       </c>
       <c r="J9">
-        <v>2000</v>
+        <v>7700</v>
       </c>
       <c r="K9">
-        <v>5020000</v>
+        <v>10830212</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="N9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="O9" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1788,362 +1803,362 @@
         <v>0</v>
       </c>
       <c r="Y9" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
         <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F10">
-        <v>1810000</v>
+        <v>4000000</v>
       </c>
       <c r="G10">
-        <v>1810000</v>
+        <v>4000000</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="J10">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="K10">
-        <v>7836009</v>
+        <v>5020000</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="O10" t="s">
         <v>125</v>
       </c>
       <c r="P10">
-        <v>12596039842</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>14910346438</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>16039074617</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>1732604466</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>2893667787</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>1613779678</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>1558081149</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>2643467726</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>1795726428</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:25">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
         <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F11">
-        <v>1330000</v>
+        <v>1810000</v>
       </c>
       <c r="G11">
-        <v>1330000</v>
+        <v>1810000</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>36400</v>
+        <v>9000</v>
       </c>
       <c r="J11">
-        <v>43300</v>
+        <v>12000</v>
       </c>
       <c r="K11">
-        <v>9375694</v>
+        <v>7836009</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>43300</v>
+        <v>16000</v>
       </c>
       <c r="N11" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="O11" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="P11">
-        <v>103267682</v>
+        <v>12596039842</v>
       </c>
       <c r="Q11">
-        <v>342201581</v>
+        <v>14910346438</v>
       </c>
       <c r="R11">
-        <v>231425455</v>
+        <v>16039074617</v>
       </c>
       <c r="S11">
-        <v>-7598692896</v>
+        <v>1732604466</v>
       </c>
       <c r="T11">
-        <v>-25822444575</v>
+        <v>2893667787</v>
       </c>
       <c r="U11">
-        <v>-15929213281</v>
+        <v>1613779678</v>
       </c>
       <c r="V11">
-        <v>-6973258680</v>
+        <v>1558081149</v>
       </c>
       <c r="W11">
-        <v>-48433907514</v>
+        <v>2643467726</v>
       </c>
       <c r="X11">
-        <v>-83246975113</v>
+        <v>1795726428</v>
       </c>
       <c r="Y11" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:25">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F12">
-        <v>3400000</v>
+        <v>1330000</v>
       </c>
       <c r="G12">
-        <v>3400000</v>
+        <v>1330000</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>4500</v>
+        <v>36400</v>
       </c>
       <c r="J12">
-        <v>5500</v>
+        <v>43300</v>
       </c>
       <c r="K12">
-        <v>30888000</v>
+        <v>9375694</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <v>7000</v>
+        <v>43300</v>
       </c>
       <c r="N12" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="O12" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="P12">
-        <v>85187882584</v>
+        <v>103267682</v>
       </c>
       <c r="Q12">
-        <v>87525689695</v>
+        <v>342201581</v>
       </c>
       <c r="R12">
-        <v>77247394706</v>
+        <v>231425455</v>
       </c>
       <c r="S12">
-        <v>2205797752</v>
+        <v>-7598692896</v>
       </c>
       <c r="T12">
-        <v>4920387020</v>
+        <v>-25822444575</v>
       </c>
       <c r="U12">
-        <v>4336496285</v>
+        <v>-15929213281</v>
       </c>
       <c r="V12">
-        <v>1613954566</v>
+        <v>-6973258680</v>
       </c>
       <c r="W12">
-        <v>3980493669</v>
+        <v>-48433907514</v>
       </c>
       <c r="X12">
-        <v>2646634321</v>
+        <v>-83246975113</v>
       </c>
       <c r="Y12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:25">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F13">
-        <v>6250000</v>
+        <v>3400000</v>
       </c>
       <c r="G13">
-        <v>6250000</v>
+        <v>3400000</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>2000</v>
+        <v>4500</v>
       </c>
       <c r="J13">
-        <v>2000</v>
+        <v>5500</v>
       </c>
       <c r="K13">
-        <v>6870000</v>
+        <v>30888000</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="N13" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="O13" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>85187882584</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>87525689695</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>77247394706</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>2205797752</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>4920387020</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>4336496285</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1613954566</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>3980493669</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>2646634321</v>
       </c>
       <c r="Y13" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:25">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F14">
-        <v>2000000</v>
+        <v>6250000</v>
       </c>
       <c r="G14">
-        <v>2000000</v>
+        <v>6250000</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>7500</v>
+        <v>2000</v>
       </c>
       <c r="J14">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="K14">
-        <v>17529140</v>
+        <v>6870000</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>11500</v>
+        <v>2000</v>
       </c>
       <c r="N14" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="O14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -2173,54 +2188,54 @@
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:25">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F15">
-        <v>6450000</v>
+        <v>2000000</v>
       </c>
       <c r="G15">
-        <v>6450000</v>
+        <v>2000000</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>2000</v>
+        <v>7500</v>
       </c>
       <c r="J15">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="K15">
-        <v>6930000</v>
+        <v>17529140</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15">
-        <v>2000</v>
+        <v>11500</v>
       </c>
       <c r="N15" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="O15" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -2250,30 +2265,30 @@
         <v>0</v>
       </c>
       <c r="Y15" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:25">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F16">
-        <v>6000000</v>
+        <v>6450000</v>
       </c>
       <c r="G16">
-        <v>6000000</v>
+        <v>6450000</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -2285,7 +2300,7 @@
         <v>2000</v>
       </c>
       <c r="K16">
-        <v>6220000</v>
+        <v>6930000</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -2294,10 +2309,10 @@
         <v>2000</v>
       </c>
       <c r="N16" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="O16" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -2327,30 +2342,30 @@
         <v>0</v>
       </c>
       <c r="Y16" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:25">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F17">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="G17">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -2362,7 +2377,7 @@
         <v>2000</v>
       </c>
       <c r="K17">
-        <v>4810000</v>
+        <v>6220000</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -2371,10 +2386,10 @@
         <v>2000</v>
       </c>
       <c r="N17" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="O17" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -2404,7 +2419,7 @@
         <v>0</v>
       </c>
       <c r="Y17" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2415,19 +2430,19 @@
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D18" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F18">
-        <v>4750000</v>
+        <v>4000000</v>
       </c>
       <c r="G18">
-        <v>4750000</v>
+        <v>4000000</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -2439,7 +2454,7 @@
         <v>2000</v>
       </c>
       <c r="K18">
-        <v>5480000</v>
+        <v>4810000</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -2448,10 +2463,10 @@
         <v>2000</v>
       </c>
       <c r="N18" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="O18" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -2481,392 +2496,469 @@
         <v>0</v>
       </c>
       <c r="Y18" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:25">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F19">
-        <v>1300000</v>
+        <v>4750000</v>
       </c>
       <c r="G19">
-        <v>1300000</v>
+        <v>4750000</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>10500</v>
+        <v>2000</v>
       </c>
       <c r="J19">
-        <v>14000</v>
+        <v>2000</v>
       </c>
       <c r="K19">
-        <v>12293880</v>
+        <v>5480000</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>17000</v>
+        <v>2000</v>
       </c>
       <c r="N19" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="O19" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="P19">
-        <v>1386123525</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>1152944128</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>1885010467</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>-4388824706</v>
+        <v>0</v>
       </c>
       <c r="T19">
-        <v>-7990287699</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>-9803411085</v>
+        <v>0</v>
       </c>
       <c r="V19">
-        <v>-4430563401</v>
+        <v>0</v>
       </c>
       <c r="W19">
-        <v>-7988275689</v>
+        <v>0</v>
       </c>
       <c r="X19">
-        <v>-9916946238</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" spans="1:25">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="D20" t="s">
         <v>73</v>
       </c>
       <c r="E20" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F20">
-        <v>1600000</v>
+        <v>1300000</v>
       </c>
       <c r="G20">
-        <v>1600000</v>
+        <v>1300000</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>20000</v>
+        <v>10500</v>
       </c>
       <c r="J20">
-        <v>23500</v>
+        <v>14000</v>
       </c>
       <c r="K20">
-        <v>8751446</v>
+        <v>12293880</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>30000</v>
+        <v>17000</v>
       </c>
       <c r="N20" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="O20" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>1386123525</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>1152944128</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1885010467</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>-4388824706</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>-7990287699</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>-9803411085</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>-4430563401</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>-7988275689</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>-9916946238</v>
       </c>
       <c r="Y20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:25">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E21" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F21">
-        <v>1298000</v>
+        <v>1600000</v>
       </c>
       <c r="G21">
-        <v>1298000</v>
+        <v>1600000</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21">
-        <v>10400</v>
+        <v>20000</v>
       </c>
       <c r="J21">
-        <v>12700</v>
+        <v>23500</v>
       </c>
       <c r="K21">
-        <v>8650735</v>
+        <v>8751446</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>16000</v>
+        <v>30000</v>
       </c>
       <c r="N21" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="O21" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="P21">
-        <v>2055746777</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>2918221978</v>
+        <v>0</v>
       </c>
       <c r="R21">
-        <v>979078233</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>-3343774083</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>-3525649863</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>-1713494359</v>
+        <v>0</v>
       </c>
       <c r="V21">
-        <v>-4430074915</v>
+        <v>0</v>
       </c>
       <c r="W21">
-        <v>-8304699942</v>
+        <v>0</v>
       </c>
       <c r="X21">
-        <v>-1627684107</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:25">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B22" t="s">
         <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D22" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E22" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F22">
-        <v>5000000</v>
+        <v>1298000</v>
       </c>
       <c r="G22">
-        <v>5000000</v>
+        <v>1298000</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
       <c r="I22">
-        <v>2000</v>
+        <v>10400</v>
       </c>
       <c r="J22">
-        <v>2000</v>
+        <v>12700</v>
       </c>
       <c r="K22">
-        <v>5840000</v>
+        <v>8650735</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22">
-        <v>2000</v>
+        <v>16000</v>
       </c>
       <c r="N22" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="O22" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2055746777</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2918221978</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>979078233</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>-3343774083</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>-3525649863</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>-1713494359</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>-4430074915</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>-8304699942</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>-1627684107</v>
       </c>
       <c r="Y22" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:25">
       <c r="A23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" t="s">
+        <v>99</v>
+      </c>
+      <c r="F23">
+        <v>5000000</v>
+      </c>
+      <c r="G23">
+        <v>5000000</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>2000</v>
+      </c>
+      <c r="J23">
+        <v>2000</v>
+      </c>
+      <c r="K23">
+        <v>5840000</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>2000</v>
+      </c>
+      <c r="N23" t="s">
+        <v>122</v>
+      </c>
+      <c r="O23" t="s">
+        <v>125</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
+      <c r="A24" t="s">
         <v>36</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B24" t="s">
         <v>37</v>
       </c>
-      <c r="C23" t="s">
-        <v>62</v>
-      </c>
-      <c r="D23" t="s">
-        <v>75</v>
-      </c>
-      <c r="E23" t="s">
-        <v>97</v>
-      </c>
-      <c r="F23">
+      <c r="C24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" t="s">
+        <v>100</v>
+      </c>
+      <c r="F24">
         <v>23333334</v>
       </c>
-      <c r="G23">
+      <c r="G24">
         <v>23333334</v>
       </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
         <v>3000</v>
       </c>
-      <c r="J23">
+      <c r="J24">
         <v>3800</v>
       </c>
-      <c r="K23">
+      <c r="K24">
         <v>43477664</v>
       </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
         <v>3000</v>
       </c>
-      <c r="N23" t="s">
-        <v>119</v>
-      </c>
-      <c r="O23" t="s">
-        <v>120</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>0</v>
-      </c>
-      <c r="V23">
-        <v>0</v>
-      </c>
-      <c r="W23">
-        <v>0</v>
-      </c>
-      <c r="X23">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>147</v>
+      <c r="N24" t="s">
+        <v>123</v>
+      </c>
+      <c r="O24" t="s">
+        <v>125</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -2881,422 +2973,422 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B2" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C2" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="F2" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C3" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E3" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="F3" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B4" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D4" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E4" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F4" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B5" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C5" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D5" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E5" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="F5" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B6" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C6" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E6" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F6" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B7" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C7" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D7" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E7" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="F7" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B8" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C8" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D8" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E8" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="F8" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B9" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C9" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D9" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E9" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="F9" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B10" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C10" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="D10" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E10" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="F10" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B11" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C11" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="D11" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E11" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="F11" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B12" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C12" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D12" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E12" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F12" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B13" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C13" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D13" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E13" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F13" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C14" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="D14" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E14" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F14" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="B15" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C15" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D15" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E15" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="F15" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B16" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C16" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D16" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E16" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="F16" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B17" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C17" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D17" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="E17" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="F17" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B18" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C18" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="D18" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E18" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F18" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B19" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C19" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D19" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E19" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="F19" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B20" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C20" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D20" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E20" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="F20" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B21" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C21" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D21" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="E21" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="F21" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="240">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -95,6 +95,9 @@
     <t>2024-07-31</t>
   </si>
   <si>
+    <t>2024-08-05</t>
+  </si>
+  <si>
     <t>2024-07-30</t>
   </si>
   <si>
@@ -143,9 +146,6 @@
     <t>2024-08-06</t>
   </si>
   <si>
-    <t>2024-08-05</t>
-  </si>
-  <si>
     <t>2024-08-02</t>
   </si>
   <si>
@@ -170,6 +170,9 @@
     <t>2024-08-21</t>
   </si>
   <si>
+    <t>2024-08-22</t>
+  </si>
+  <si>
     <t>2024-08-20</t>
   </si>
   <si>
@@ -206,6 +209,9 @@
     <t>한국</t>
   </si>
   <si>
+    <t>대신</t>
+  </si>
+  <si>
     <t>하나</t>
   </si>
   <si>
@@ -227,9 +233,6 @@
     <t>SK</t>
   </si>
   <si>
-    <t>대신</t>
-  </si>
-  <si>
     <t>엘에스</t>
   </si>
   <si>
@@ -242,6 +245,9 @@
     <t>티디에스팜</t>
   </si>
   <si>
+    <t>대신밸런스제18호스팩</t>
+  </si>
+  <si>
     <t>케이쓰리아이</t>
   </si>
   <si>
@@ -302,6 +308,9 @@
     <t>1331.20:1</t>
   </si>
   <si>
+    <t>1069.96:1</t>
+  </si>
+  <si>
     <t>239.23:1</t>
   </si>
   <si>
@@ -362,6 +371,9 @@
     <t>4.23%</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>1.03%</t>
   </si>
   <si>
@@ -371,9 +383,6 @@
     <t>0.55%</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>1.52%</t>
   </si>
   <si>
@@ -404,6 +413,9 @@
     <t>경피약물전달시스템(습포제, 첩부제)</t>
   </si>
   <si>
+    <t>금융 지원 서비스업</t>
+  </si>
+  <si>
     <t>XR 실감형콘텐츠</t>
   </si>
   <si>
@@ -485,6 +497,9 @@
     <t>제닉스</t>
   </si>
   <si>
+    <t>셀비온</t>
+  </si>
+  <si>
     <t>키움스팩9호</t>
   </si>
   <si>
@@ -584,6 +599,9 @@
     <t>28,000~34,000</t>
   </si>
   <si>
+    <t>10,000~12,200</t>
+  </si>
+  <si>
     <t>8,000~10,000</t>
   </si>
   <si>
@@ -638,9 +656,6 @@
     <t>29000</t>
   </si>
   <si>
-    <t>21000</t>
-  </si>
-  <si>
     <t>49500</t>
   </si>
   <si>
@@ -683,9 +698,6 @@
     <t>11600</t>
   </si>
   <si>
-    <t>15771</t>
-  </si>
-  <si>
     <t>NH투자증권</t>
   </si>
   <si>
@@ -698,13 +710,13 @@
     <t>신영증권,케이비증권</t>
   </si>
   <si>
+    <t>대신증권</t>
+  </si>
+  <si>
     <t>키움증권</t>
   </si>
   <si>
     <t>한국투자증권</t>
-  </si>
-  <si>
-    <t>대신증권</t>
   </si>
   <si>
     <t>신한투자증권</t>
@@ -1080,7 +1092,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y21"/>
+  <dimension ref="A1:Y22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1165,16 +1177,16 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
         <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F2">
         <v>1000000</v>
@@ -1201,10 +1213,10 @@
         <v>13000</v>
       </c>
       <c r="N2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="O2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="P2">
         <v>25588</v>
@@ -1234,7 +1246,7 @@
         <v>809</v>
       </c>
       <c r="Y2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1248,70 +1260,70 @@
         <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F3">
-        <v>1400000</v>
+        <v>6500000</v>
       </c>
       <c r="G3">
-        <v>1400000</v>
+        <v>6500000</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>12500</v>
+        <v>2000</v>
       </c>
       <c r="J3">
-        <v>15500</v>
+        <v>2000</v>
       </c>
       <c r="K3">
-        <v>7486442</v>
+        <v>7910000</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>15500</v>
+        <v>2000</v>
       </c>
       <c r="N3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="O3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="P3">
-        <v>10740898602</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>13058877126</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>3506428302</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>1748628548</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>1115790858</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>191527654</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>1491084554</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>1185231988</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>219774608</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1319,123 +1331,123 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F4">
-        <v>1000000</v>
+        <v>1400000</v>
       </c>
       <c r="G4">
-        <v>1000000</v>
+        <v>1400000</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>24000</v>
+        <v>12500</v>
       </c>
       <c r="J4">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="K4">
-        <v>8008066</v>
+        <v>7486442</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="N4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>10740898602</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>13058877126</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>3506428302</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1748628548</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>1115790858</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>191527654</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1491084554</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1185231988</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>219774608</v>
       </c>
       <c r="Y4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
         <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F5">
-        <v>751000</v>
+        <v>1000000</v>
       </c>
       <c r="G5">
-        <v>203700</v>
+        <v>1000000</v>
       </c>
       <c r="H5">
-        <v>547300</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>18000</v>
+        <v>24000</v>
       </c>
       <c r="J5">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="K5">
-        <v>4330068</v>
+        <v>8008066</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="N5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="O5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1465,54 +1477,54 @@
         <v>0</v>
       </c>
       <c r="Y5" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:25">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s">
         <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F6">
-        <v>5800000</v>
+        <v>751000</v>
       </c>
       <c r="G6">
-        <v>5800000</v>
+        <v>203700</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>547300</v>
       </c>
       <c r="I6">
-        <v>2000</v>
+        <v>18000</v>
       </c>
       <c r="J6">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="K6">
-        <v>6100000</v>
+        <v>4330068</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="N6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="O6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1542,7 +1554,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1556,70 +1568,70 @@
         <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F7">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="G7">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="J7">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="K7">
-        <v>10000988</v>
+        <v>6100000</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="O7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P7">
-        <v>72895458363</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>72913766913</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>11230711680</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>-6524077412</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>-4556157069</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>-3633759729</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>-11528915410</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>-7978634776</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>-3801868433</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1627,76 +1639,76 @@
         <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F8">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="G8">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>7300</v>
+        <v>16000</v>
       </c>
       <c r="J8">
-        <v>8500</v>
+        <v>19000</v>
       </c>
       <c r="K8">
-        <v>14965620</v>
+        <v>10000988</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="N8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="O8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="P8">
-        <v>1337894447</v>
+        <v>72895458363</v>
       </c>
       <c r="Q8">
-        <v>4495088983</v>
+        <v>72913766913</v>
       </c>
       <c r="R8">
-        <v>99398351</v>
+        <v>11230711680</v>
       </c>
       <c r="S8">
-        <v>-3330678562</v>
+        <v>-6524077412</v>
       </c>
       <c r="T8">
-        <v>-2905069801</v>
+        <v>-4556157069</v>
       </c>
       <c r="U8">
-        <v>-1314068310</v>
+        <v>-3633759729</v>
       </c>
       <c r="V8">
-        <v>-9735376868</v>
+        <v>-11528915410</v>
       </c>
       <c r="W8">
-        <v>-5043515600</v>
+        <v>-7978634776</v>
       </c>
       <c r="X8">
-        <v>-1257080998</v>
+        <v>-3801868433</v>
       </c>
       <c r="Y8" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1704,76 +1716,76 @@
         <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F9">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="G9">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>14000</v>
+        <v>7300</v>
       </c>
       <c r="J9">
-        <v>17000</v>
+        <v>8500</v>
       </c>
       <c r="K9">
-        <v>6471740</v>
+        <v>14965620</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="N9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="P9">
-        <v>5214628820</v>
+        <v>1337894447</v>
       </c>
       <c r="Q9">
-        <v>6009352447</v>
+        <v>4495088983</v>
       </c>
       <c r="R9">
-        <v>965797975</v>
+        <v>99398351</v>
       </c>
       <c r="S9">
-        <v>2015081728</v>
+        <v>-3330678562</v>
       </c>
       <c r="T9">
-        <v>1319755337</v>
+        <v>-2905069801</v>
       </c>
       <c r="U9">
-        <v>-44547594</v>
+        <v>-1314068310</v>
       </c>
       <c r="V9">
-        <v>1503069100</v>
+        <v>-9735376868</v>
       </c>
       <c r="W9">
-        <v>1410469786</v>
+        <v>-5043515600</v>
       </c>
       <c r="X9">
-        <v>24178632</v>
+        <v>-1257080998</v>
       </c>
       <c r="Y9" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1781,99 +1793,99 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F10">
-        <v>6000000</v>
+        <v>1350000</v>
       </c>
       <c r="G10">
-        <v>6000000</v>
+        <v>1350000</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>2000</v>
+        <v>14000</v>
       </c>
       <c r="J10">
-        <v>2000</v>
+        <v>17000</v>
       </c>
       <c r="K10">
-        <v>6345000</v>
+        <v>6471740</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>2000</v>
+        <v>22000</v>
       </c>
       <c r="N10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="O10" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>5214628820</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>6009352447</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>965797975</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>2015081728</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1319755337</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>-44547594</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1503069100</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1410469786</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>24178632</v>
       </c>
       <c r="Y10" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:25">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
         <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F11">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="G11">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -1885,7 +1897,7 @@
         <v>2000</v>
       </c>
       <c r="K11">
-        <v>4420000</v>
+        <v>6345000</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1894,7 +1906,7 @@
         <v>2000</v>
       </c>
       <c r="N11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="O11" t="s">
         <v>118</v>
@@ -1927,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="Y11" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1935,46 +1947,46 @@
         <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F12">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="G12">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>6200</v>
+        <v>2000</v>
       </c>
       <c r="J12">
-        <v>7700</v>
+        <v>2000</v>
       </c>
       <c r="K12">
-        <v>10830212</v>
+        <v>4420000</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="N12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="O12" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -2004,7 +2016,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -2015,43 +2027,43 @@
         <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F13">
-        <v>4000000</v>
+        <v>1618000</v>
       </c>
       <c r="G13">
-        <v>4000000</v>
+        <v>1618000</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>2000</v>
+        <v>6200</v>
       </c>
       <c r="J13">
-        <v>2000</v>
+        <v>7700</v>
       </c>
       <c r="K13">
-        <v>5020000</v>
+        <v>10830212</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="N13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O13" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -2081,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -2089,76 +2101,76 @@
         <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s">
         <v>57</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F14">
-        <v>1810000</v>
+        <v>4000000</v>
       </c>
       <c r="G14">
-        <v>1810000</v>
+        <v>4000000</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="J14">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="K14">
-        <v>7836009</v>
+        <v>5020000</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N14" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O14" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="P14">
-        <v>12596039842</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>14910346438</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>16039074617</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>1732604466</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>2893667787</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>1613779678</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1558081149</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>2643467726</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>1795726428</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -2166,76 +2178,76 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
         <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F15">
-        <v>1330000</v>
+        <v>1810000</v>
       </c>
       <c r="G15">
-        <v>1330000</v>
+        <v>1810000</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>36400</v>
+        <v>9000</v>
       </c>
       <c r="J15">
-        <v>43300</v>
+        <v>12000</v>
       </c>
       <c r="K15">
-        <v>9375694</v>
+        <v>7836009</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15">
-        <v>43300</v>
+        <v>16000</v>
       </c>
       <c r="N15" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="O15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="P15">
-        <v>103267682</v>
+        <v>12596039842</v>
       </c>
       <c r="Q15">
-        <v>342201581</v>
+        <v>14910346438</v>
       </c>
       <c r="R15">
-        <v>231425455</v>
+        <v>16039074617</v>
       </c>
       <c r="S15">
-        <v>-7598692896</v>
+        <v>1732604466</v>
       </c>
       <c r="T15">
-        <v>-25822444575</v>
+        <v>2893667787</v>
       </c>
       <c r="U15">
-        <v>-15929213281</v>
+        <v>1613779678</v>
       </c>
       <c r="V15">
-        <v>-6973258680</v>
+        <v>1558081149</v>
       </c>
       <c r="W15">
-        <v>-48433907514</v>
+        <v>2643467726</v>
       </c>
       <c r="X15">
-        <v>-83246975113</v>
+        <v>1795726428</v>
       </c>
       <c r="Y15" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -2243,76 +2255,76 @@
         <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F16">
-        <v>3400000</v>
+        <v>1330000</v>
       </c>
       <c r="G16">
-        <v>3400000</v>
+        <v>1330000</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16">
-        <v>4500</v>
+        <v>36400</v>
       </c>
       <c r="J16">
-        <v>5500</v>
+        <v>43300</v>
       </c>
       <c r="K16">
-        <v>30888000</v>
+        <v>9375694</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <v>7000</v>
+        <v>43300</v>
       </c>
       <c r="N16" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O16" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="P16">
-        <v>85187882584</v>
+        <v>103267682</v>
       </c>
       <c r="Q16">
-        <v>87525689695</v>
+        <v>342201581</v>
       </c>
       <c r="R16">
-        <v>77247394706</v>
+        <v>231425455</v>
       </c>
       <c r="S16">
-        <v>2205797752</v>
+        <v>-7598692896</v>
       </c>
       <c r="T16">
-        <v>4920387020</v>
+        <v>-25822444575</v>
       </c>
       <c r="U16">
-        <v>4336496285</v>
+        <v>-15929213281</v>
       </c>
       <c r="V16">
-        <v>1613954566</v>
+        <v>-6973258680</v>
       </c>
       <c r="W16">
-        <v>3980493669</v>
+        <v>-48433907514</v>
       </c>
       <c r="X16">
-        <v>2646634321</v>
+        <v>-83246975113</v>
       </c>
       <c r="Y16" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2323,73 +2335,73 @@
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F17">
-        <v>6250000</v>
+        <v>3400000</v>
       </c>
       <c r="G17">
-        <v>6250000</v>
+        <v>3400000</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>2000</v>
+        <v>4500</v>
       </c>
       <c r="J17">
-        <v>2000</v>
+        <v>5500</v>
       </c>
       <c r="K17">
-        <v>6870000</v>
+        <v>30888000</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="N17" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O17" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>85187882584</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>87525689695</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>77247394706</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>2205797752</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>4920387020</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>4336496285</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1613954566</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>3980493669</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>2646634321</v>
       </c>
       <c r="Y17" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2397,46 +2409,46 @@
         <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
         <v>60</v>
       </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F18">
-        <v>2000000</v>
+        <v>6250000</v>
       </c>
       <c r="G18">
-        <v>2000000</v>
+        <v>6250000</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>7500</v>
+        <v>2000</v>
       </c>
       <c r="J18">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="K18">
-        <v>17529140</v>
+        <v>6870000</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>11500</v>
+        <v>2000</v>
       </c>
       <c r="N18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="O18" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -2466,7 +2478,7 @@
         <v>0</v>
       </c>
       <c r="Y18" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2474,46 +2486,46 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F19">
-        <v>6450000</v>
+        <v>2000000</v>
       </c>
       <c r="G19">
-        <v>6450000</v>
+        <v>2000000</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>2000</v>
+        <v>7500</v>
       </c>
       <c r="J19">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="K19">
-        <v>6930000</v>
+        <v>17529140</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>2000</v>
+        <v>11500</v>
       </c>
       <c r="N19" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O19" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -2543,7 +2555,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2551,46 +2563,46 @@
         <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F20">
-        <v>1600000</v>
+        <v>6450000</v>
       </c>
       <c r="G20">
-        <v>1600000</v>
+        <v>6450000</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="J20">
-        <v>23500</v>
+        <v>2000</v>
       </c>
       <c r="K20">
-        <v>8751446</v>
+        <v>6930000</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>30000</v>
+        <v>2000</v>
       </c>
       <c r="N20" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="O20" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -2620,84 +2632,161 @@
         <v>0</v>
       </c>
       <c r="Y20" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="1:25">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="D21" t="s">
         <v>73</v>
       </c>
       <c r="E21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F21">
+        <v>1600000</v>
+      </c>
+      <c r="G21">
+        <v>1600000</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>20000</v>
+      </c>
+      <c r="J21">
+        <v>23500</v>
+      </c>
+      <c r="K21">
+        <v>8751446</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>30000</v>
+      </c>
+      <c r="N21" t="s">
+        <v>115</v>
+      </c>
+      <c r="O21" t="s">
+        <v>130</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25">
+      <c r="A22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" t="s">
+        <v>95</v>
+      </c>
+      <c r="F22">
         <v>23333334</v>
       </c>
-      <c r="G21">
+      <c r="G22">
         <v>23333334</v>
       </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
         <v>3000</v>
       </c>
-      <c r="J21">
+      <c r="J22">
         <v>3800</v>
       </c>
-      <c r="K21">
+      <c r="K22">
         <v>43477664</v>
       </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
         <v>3000</v>
       </c>
-      <c r="N21" t="s">
-        <v>113</v>
-      </c>
-      <c r="O21" t="s">
+      <c r="N22" t="s">
+        <v>116</v>
+      </c>
+      <c r="O22" t="s">
         <v>118</v>
       </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>144</v>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -2712,53 +2801,53 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B2" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C2" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D2" t="s">
         <v>118</v>
       </c>
       <c r="E2" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D3" t="s">
         <v>118</v>
@@ -2767,267 +2856,267 @@
         <v>118</v>
       </c>
       <c r="F3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B4" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C4" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D4" t="s">
         <v>118</v>
       </c>
       <c r="E4" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="F4" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B5" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C5" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D5" t="s">
         <v>118</v>
       </c>
       <c r="E5" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F5" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B6" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C6" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="D6" t="s">
         <v>118</v>
       </c>
       <c r="E6" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F6" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B7" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C7" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="D7" t="s">
         <v>118</v>
       </c>
       <c r="E7" t="s">
-        <v>212</v>
+        <v>118</v>
       </c>
       <c r="F7" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B8" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C8" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D8" t="s">
         <v>118</v>
       </c>
       <c r="E8" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="F8" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B9" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C9" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D9" t="s">
         <v>118</v>
       </c>
       <c r="E9" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F9" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B10" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C10" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D10" t="s">
         <v>118</v>
       </c>
       <c r="E10" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B11" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C11" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="D11" t="s">
         <v>118</v>
       </c>
       <c r="E11" t="s">
-        <v>118</v>
+        <v>220</v>
       </c>
       <c r="F11" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B12" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C12" t="s">
         <v>192</v>
       </c>
       <c r="D12" t="s">
-        <v>199</v>
+        <v>118</v>
       </c>
       <c r="E12" t="s">
-        <v>216</v>
+        <v>118</v>
       </c>
       <c r="F12" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C13" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="D13" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="E13" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="F13" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D14" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="E14" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="F14" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C15" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="D15" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E15" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F15" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="B16" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C16" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="D16" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E16" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="F16" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -3035,56 +3124,56 @@
         <v>75</v>
       </c>
       <c r="B17" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C17" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D17" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E17" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="F17" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="B18" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C18" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="D18" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E18" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F18" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B19" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C19" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="D19" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="E19" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F19" t="s">
         <v>235</v>
@@ -3092,42 +3181,42 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>171</v>
       </c>
       <c r="B20" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C20" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D20" t="s">
         <v>206</v>
       </c>
       <c r="E20" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="F20" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B21" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C21" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="D21" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E21" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="F21" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="241">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -92,6 +92,9 @@
     <t>주요제품</t>
   </si>
   <si>
+    <t>2024-08-02</t>
+  </si>
+  <si>
     <t>2024-07-31</t>
   </si>
   <si>
@@ -143,12 +146,12 @@
     <t>2024-05-30</t>
   </si>
   <si>
+    <t>2024-08-08</t>
+  </si>
+  <si>
     <t>2024-08-06</t>
   </si>
   <si>
-    <t>2024-08-02</t>
-  </si>
-  <si>
     <t>2024-07-19</t>
   </si>
   <si>
@@ -167,6 +170,9 @@
     <t>2024-06-17</t>
   </si>
   <si>
+    <t>2024-08-23</t>
+  </si>
+  <si>
     <t>2024-08-21</t>
   </si>
   <si>
@@ -206,6 +212,9 @@
     <t>2024-07-01</t>
   </si>
   <si>
+    <t>NH</t>
+  </si>
+  <si>
     <t>한국</t>
   </si>
   <si>
@@ -227,9 +236,6 @@
     <t>삼성</t>
   </si>
   <si>
-    <t>NH</t>
-  </si>
-  <si>
     <t>SK</t>
   </si>
   <si>
@@ -242,6 +248,9 @@
     <t>신한, 한국</t>
   </si>
   <si>
+    <t>이엔셀</t>
+  </si>
+  <si>
     <t>티디에스팜</t>
   </si>
   <si>
@@ -305,6 +314,9 @@
     <t>신한글로벌액티브리츠</t>
   </si>
   <si>
+    <t>949.3:1</t>
+  </si>
+  <si>
     <t>1331.20:1</t>
   </si>
   <si>
@@ -368,6 +380,9 @@
     <t>38.7:1</t>
   </si>
   <si>
+    <t>0.24%</t>
+  </si>
+  <si>
     <t>4.23%</t>
   </si>
   <si>
@@ -410,6 +425,9 @@
     <t>12.44%</t>
   </si>
   <si>
+    <t>첨단바이오의약품 위탁개발생산(CDMO) 서비스 / 차세대 세포,유전자 치료제</t>
+  </si>
+  <si>
     <t>경피약물전달시스템(습포제, 첩부제)</t>
   </si>
   <si>
@@ -482,9 +500,18 @@
     <t>주간사</t>
   </si>
   <si>
+    <t>신한스팩14호</t>
+  </si>
+  <si>
     <t>루미르</t>
   </si>
   <si>
+    <t>웨이비스</t>
+  </si>
+  <si>
+    <t>에이치이엠파마(구.에이치이엠)</t>
+  </si>
+  <si>
     <t>한켐</t>
   </si>
   <si>
@@ -509,9 +536,6 @@
     <t>아이언디바이스</t>
   </si>
   <si>
-    <t>에이치이엠파마(구.에이치이엠)</t>
-  </si>
-  <si>
     <t>미래에셋비전스팩7호</t>
   </si>
   <si>
@@ -521,16 +545,13 @@
     <t>대신밸런스스팩18호</t>
   </si>
   <si>
-    <t>이엔셀</t>
-  </si>
-  <si>
     <t>엠83</t>
   </si>
   <si>
     <t>전진건설로봇(구.전진중공업)(유가)</t>
   </si>
   <si>
-    <t>교보스팩16호</t>
+    <t>2024.10.01~10.02</t>
   </si>
   <si>
     <t>2024.09.09~09.13</t>
@@ -554,9 +575,6 @@
     <t>2024.08.30~09.05</t>
   </si>
   <si>
-    <t>2024.08.26~08.30</t>
-  </si>
-  <si>
     <t>2024.08.26~08.27</t>
   </si>
   <si>
@@ -578,24 +596,24 @@
     <t>2024.07.30~08.05</t>
   </si>
   <si>
-    <t>2024.07.29~07.30</t>
-  </si>
-  <si>
-    <t>2024.07.29~08.02</t>
+    <t>2,000~2,000</t>
   </si>
   <si>
     <t>16,500~20,500</t>
   </si>
   <si>
+    <t>11,000~12,500</t>
+  </si>
+  <si>
+    <t>16,400~19,000</t>
+  </si>
+  <si>
     <t>12,500~14,500</t>
   </si>
   <si>
     <t>8,600~9,800</t>
   </si>
   <si>
-    <t>2,000~2,000</t>
-  </si>
-  <si>
     <t>28,000~34,000</t>
   </si>
   <si>
@@ -608,9 +626,6 @@
     <t>4,900~5,700</t>
   </si>
   <si>
-    <t>18,000~21,000</t>
-  </si>
-  <si>
     <t>32,000~40,200</t>
   </si>
   <si>
@@ -629,9 +644,6 @@
     <t>13,800~15,700</t>
   </si>
   <si>
-    <t>24,000~29,000</t>
-  </si>
-  <si>
     <t>32000</t>
   </si>
   <si>
@@ -653,18 +665,18 @@
     <t>16500</t>
   </si>
   <si>
-    <t>29000</t>
+    <t>10000</t>
   </si>
   <si>
     <t>49500</t>
   </si>
   <si>
+    <t>11430</t>
+  </si>
+  <si>
     <t>30616</t>
   </si>
   <si>
-    <t>10000</t>
-  </si>
-  <si>
     <t>18480</t>
   </si>
   <si>
@@ -677,9 +689,6 @@
     <t>14700</t>
   </si>
   <si>
-    <t>12546</t>
-  </si>
-  <si>
     <t>78720</t>
   </si>
   <si>
@@ -695,12 +704,15 @@
     <t>50781</t>
   </si>
   <si>
-    <t>11600</t>
+    <t>신한투자증권</t>
   </si>
   <si>
     <t>NH투자증권</t>
   </si>
   <si>
+    <t>대신증권</t>
+  </si>
+  <si>
     <t>신영증권,유진증권</t>
   </si>
   <si>
@@ -710,18 +722,12 @@
     <t>신영증권,케이비증권</t>
   </si>
   <si>
-    <t>대신증권</t>
-  </si>
-  <si>
     <t>키움증권</t>
   </si>
   <si>
     <t>한국투자증권</t>
   </si>
   <si>
-    <t>신한투자증권</t>
-  </si>
-  <si>
     <t>미래에셋증권</t>
   </si>
   <si>
@@ -732,9 +738,6 @@
   </si>
   <si>
     <t>하나증권</t>
-  </si>
-  <si>
-    <t>교보증권</t>
   </si>
 </sst>
 </file>
@@ -1092,7 +1095,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y22"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1177,76 +1180,76 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F2">
-        <v>1000000</v>
+        <v>1566800</v>
       </c>
       <c r="G2">
-        <v>500000</v>
+        <v>1566800</v>
       </c>
       <c r="H2">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>9500</v>
+        <v>13600</v>
       </c>
       <c r="J2">
-        <v>10700</v>
+        <v>15300</v>
       </c>
       <c r="K2">
-        <v>5530000</v>
+        <v>9349954</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>13000</v>
+        <v>15300</v>
       </c>
       <c r="N2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="O2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="P2">
-        <v>25588</v>
+        <v>7367362</v>
       </c>
       <c r="Q2">
-        <v>30049</v>
+        <v>10525887</v>
       </c>
       <c r="R2">
-        <v>7363</v>
+        <v>1790340</v>
       </c>
       <c r="S2">
-        <v>3780</v>
+        <v>-9315442</v>
       </c>
       <c r="T2">
-        <v>5016</v>
+        <v>-11755057</v>
       </c>
       <c r="U2">
-        <v>938</v>
+        <v>-2929307</v>
       </c>
       <c r="V2">
-        <v>3456</v>
+        <v>-45566953</v>
       </c>
       <c r="W2">
-        <v>4688</v>
+        <v>-5053520</v>
       </c>
       <c r="X2">
-        <v>809</v>
+        <v>-2903334</v>
       </c>
       <c r="Y2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1254,76 +1257,76 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F3">
-        <v>6500000</v>
+        <v>1000000</v>
       </c>
       <c r="G3">
-        <v>6500000</v>
+        <v>500000</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="I3">
-        <v>2000</v>
+        <v>9500</v>
       </c>
       <c r="J3">
-        <v>2000</v>
+        <v>10700</v>
       </c>
       <c r="K3">
-        <v>7910000</v>
+        <v>5530000</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="N3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="O3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>25588</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>30049</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>7363</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>3780</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>5016</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>938</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>3456</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>4688</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>809</v>
       </c>
       <c r="Y3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1331,76 +1334,76 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F4">
-        <v>1400000</v>
+        <v>6500000</v>
       </c>
       <c r="G4">
-        <v>1400000</v>
+        <v>6500000</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>12500</v>
+        <v>2000</v>
       </c>
       <c r="J4">
-        <v>15500</v>
+        <v>2000</v>
       </c>
       <c r="K4">
-        <v>7486442</v>
+        <v>7910000</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>15500</v>
+        <v>2000</v>
       </c>
       <c r="N4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="O4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="P4">
-        <v>10740898602</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>13058877126</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>3506428302</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>1748628548</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>1115790858</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>191527654</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>1491084554</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>1185231988</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>219774608</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1408,123 +1411,123 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F5">
-        <v>1000000</v>
+        <v>1400000</v>
       </c>
       <c r="G5">
-        <v>1000000</v>
+        <v>1400000</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>24000</v>
+        <v>12500</v>
       </c>
       <c r="J5">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="K5">
-        <v>8008066</v>
+        <v>7486442</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="N5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="O5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>10740898602</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>13058877126</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>3506428302</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1748628548</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1115790858</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>191527654</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1491084554</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1185231988</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>219774608</v>
       </c>
       <c r="Y5" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:25">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
         <v>66</v>
       </c>
       <c r="E6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F6">
-        <v>751000</v>
+        <v>1000000</v>
       </c>
       <c r="G6">
-        <v>203700</v>
+        <v>1000000</v>
       </c>
       <c r="H6">
-        <v>547300</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>18000</v>
+        <v>24000</v>
       </c>
       <c r="J6">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="K6">
-        <v>4330068</v>
+        <v>8008066</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="N6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="O6" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1554,54 +1557,54 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:25">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F7">
-        <v>5800000</v>
+        <v>751000</v>
       </c>
       <c r="G7">
-        <v>5800000</v>
+        <v>203700</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>547300</v>
       </c>
       <c r="I7">
-        <v>2000</v>
+        <v>18000</v>
       </c>
       <c r="J7">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="K7">
-        <v>6100000</v>
+        <v>4330068</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="N7" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="O7" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1631,7 +1634,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1642,73 +1645,73 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F8">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="G8">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="J8">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="K8">
-        <v>10000988</v>
+        <v>6100000</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N8" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="O8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P8">
-        <v>72895458363</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>72913766913</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>11230711680</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>-6524077412</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>-4556157069</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>-3633759729</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>-11528915410</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>-7978634776</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>-3801868433</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1716,76 +1719,76 @@
         <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F9">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="G9">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>7300</v>
+        <v>16000</v>
       </c>
       <c r="J9">
-        <v>8500</v>
+        <v>19000</v>
       </c>
       <c r="K9">
-        <v>14965620</v>
+        <v>10000988</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="N9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="O9" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="P9">
-        <v>1337894447</v>
+        <v>72895458363</v>
       </c>
       <c r="Q9">
-        <v>4495088983</v>
+        <v>72913766913</v>
       </c>
       <c r="R9">
-        <v>99398351</v>
+        <v>11230711680</v>
       </c>
       <c r="S9">
-        <v>-3330678562</v>
+        <v>-6524077412</v>
       </c>
       <c r="T9">
-        <v>-2905069801</v>
+        <v>-4556157069</v>
       </c>
       <c r="U9">
-        <v>-1314068310</v>
+        <v>-3633759729</v>
       </c>
       <c r="V9">
-        <v>-9735376868</v>
+        <v>-11528915410</v>
       </c>
       <c r="W9">
-        <v>-5043515600</v>
+        <v>-7978634776</v>
       </c>
       <c r="X9">
-        <v>-1257080998</v>
+        <v>-3801868433</v>
       </c>
       <c r="Y9" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1796,73 +1799,73 @@
         <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F10">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="G10">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>14000</v>
+        <v>7300</v>
       </c>
       <c r="J10">
-        <v>17000</v>
+        <v>8500</v>
       </c>
       <c r="K10">
-        <v>6471740</v>
+        <v>14965620</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="N10" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="O10" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="P10">
-        <v>5214628820</v>
+        <v>1337894447</v>
       </c>
       <c r="Q10">
-        <v>6009352447</v>
+        <v>4495088983</v>
       </c>
       <c r="R10">
-        <v>965797975</v>
+        <v>99398351</v>
       </c>
       <c r="S10">
-        <v>2015081728</v>
+        <v>-3330678562</v>
       </c>
       <c r="T10">
-        <v>1319755337</v>
+        <v>-2905069801</v>
       </c>
       <c r="U10">
-        <v>-44547594</v>
+        <v>-1314068310</v>
       </c>
       <c r="V10">
-        <v>1503069100</v>
+        <v>-9735376868</v>
       </c>
       <c r="W10">
-        <v>1410469786</v>
+        <v>-5043515600</v>
       </c>
       <c r="X10">
-        <v>24178632</v>
+        <v>-1257080998</v>
       </c>
       <c r="Y10" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1873,96 +1876,96 @@
         <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F11">
-        <v>6000000</v>
+        <v>1350000</v>
       </c>
       <c r="G11">
-        <v>6000000</v>
+        <v>1350000</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>2000</v>
+        <v>14000</v>
       </c>
       <c r="J11">
-        <v>2000</v>
+        <v>17000</v>
       </c>
       <c r="K11">
-        <v>6345000</v>
+        <v>6471740</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>2000</v>
+        <v>22000</v>
       </c>
       <c r="N11" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="O11" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>5214628820</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>6009352447</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>965797975</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>2015081728</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1319755337</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>-44547594</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1503069100</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1410469786</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>24178632</v>
       </c>
       <c r="Y11" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:25">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F12">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="G12">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1974,7 +1977,7 @@
         <v>2000</v>
       </c>
       <c r="K12">
-        <v>4420000</v>
+        <v>6345000</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1983,10 +1986,10 @@
         <v>2000</v>
       </c>
       <c r="N12" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="O12" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -2016,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -2027,43 +2030,43 @@
         <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F13">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="G13">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>6200</v>
+        <v>2000</v>
       </c>
       <c r="J13">
-        <v>7700</v>
+        <v>2000</v>
       </c>
       <c r="K13">
-        <v>10830212</v>
+        <v>4420000</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="N13" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="O13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -2093,7 +2096,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -2101,46 +2104,46 @@
         <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E14" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F14">
-        <v>4000000</v>
+        <v>1618000</v>
       </c>
       <c r="G14">
-        <v>4000000</v>
+        <v>1618000</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>2000</v>
+        <v>6200</v>
       </c>
       <c r="J14">
-        <v>2000</v>
+        <v>7700</v>
       </c>
       <c r="K14">
-        <v>5020000</v>
+        <v>10830212</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="N14" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="O14" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -2170,7 +2173,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -2181,73 +2184,73 @@
         <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F15">
-        <v>1810000</v>
+        <v>4000000</v>
       </c>
       <c r="G15">
-        <v>1810000</v>
+        <v>4000000</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="J15">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="K15">
-        <v>7836009</v>
+        <v>5020000</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N15" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="O15" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="P15">
-        <v>12596039842</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>14910346438</v>
+        <v>0</v>
       </c>
       <c r="R15">
-        <v>16039074617</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>1732604466</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>2893667787</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>1613779678</v>
+        <v>0</v>
       </c>
       <c r="V15">
-        <v>1558081149</v>
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>2643467726</v>
+        <v>0</v>
       </c>
       <c r="X15">
-        <v>1795726428</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -2258,73 +2261,73 @@
         <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F16">
-        <v>1330000</v>
+        <v>1810000</v>
       </c>
       <c r="G16">
-        <v>1330000</v>
+        <v>1810000</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16">
-        <v>36400</v>
+        <v>9000</v>
       </c>
       <c r="J16">
-        <v>43300</v>
+        <v>12000</v>
       </c>
       <c r="K16">
-        <v>9375694</v>
+        <v>7836009</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <v>43300</v>
+        <v>16000</v>
       </c>
       <c r="N16" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="O16" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="P16">
-        <v>103267682</v>
+        <v>12596039842</v>
       </c>
       <c r="Q16">
-        <v>342201581</v>
+        <v>14910346438</v>
       </c>
       <c r="R16">
-        <v>231425455</v>
+        <v>16039074617</v>
       </c>
       <c r="S16">
-        <v>-7598692896</v>
+        <v>1732604466</v>
       </c>
       <c r="T16">
-        <v>-25822444575</v>
+        <v>2893667787</v>
       </c>
       <c r="U16">
-        <v>-15929213281</v>
+        <v>1613779678</v>
       </c>
       <c r="V16">
-        <v>-6973258680</v>
+        <v>1558081149</v>
       </c>
       <c r="W16">
-        <v>-48433907514</v>
+        <v>2643467726</v>
       </c>
       <c r="X16">
-        <v>-83246975113</v>
+        <v>1795726428</v>
       </c>
       <c r="Y16" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2332,76 +2335,76 @@
         <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D17" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E17" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F17">
-        <v>3400000</v>
+        <v>1330000</v>
       </c>
       <c r="G17">
-        <v>3400000</v>
+        <v>1330000</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>4500</v>
+        <v>36400</v>
       </c>
       <c r="J17">
-        <v>5500</v>
+        <v>43300</v>
       </c>
       <c r="K17">
-        <v>30888000</v>
+        <v>9375694</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <v>7000</v>
+        <v>43300</v>
       </c>
       <c r="N17" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="O17" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="P17">
-        <v>85187882584</v>
+        <v>103267682</v>
       </c>
       <c r="Q17">
-        <v>87525689695</v>
+        <v>342201581</v>
       </c>
       <c r="R17">
-        <v>77247394706</v>
+        <v>231425455</v>
       </c>
       <c r="S17">
-        <v>2205797752</v>
+        <v>-7598692896</v>
       </c>
       <c r="T17">
-        <v>4920387020</v>
+        <v>-25822444575</v>
       </c>
       <c r="U17">
-        <v>4336496285</v>
+        <v>-15929213281</v>
       </c>
       <c r="V17">
-        <v>1613954566</v>
+        <v>-6973258680</v>
       </c>
       <c r="W17">
-        <v>3980493669</v>
+        <v>-48433907514</v>
       </c>
       <c r="X17">
-        <v>2646634321</v>
+        <v>-83246975113</v>
       </c>
       <c r="Y17" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2412,73 +2415,73 @@
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E18" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F18">
-        <v>6250000</v>
+        <v>3400000</v>
       </c>
       <c r="G18">
-        <v>6250000</v>
+        <v>3400000</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>2000</v>
+        <v>4500</v>
       </c>
       <c r="J18">
-        <v>2000</v>
+        <v>5500</v>
       </c>
       <c r="K18">
-        <v>6870000</v>
+        <v>30888000</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="N18" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="O18" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>85187882584</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>87525689695</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>77247394706</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>2205797752</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>4920387020</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>4336496285</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1613954566</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>3980493669</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>2646634321</v>
       </c>
       <c r="Y18" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2486,46 +2489,46 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E19" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F19">
-        <v>2000000</v>
+        <v>6250000</v>
       </c>
       <c r="G19">
-        <v>2000000</v>
+        <v>6250000</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>7500</v>
+        <v>2000</v>
       </c>
       <c r="J19">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="K19">
-        <v>17529140</v>
+        <v>6870000</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>11500</v>
+        <v>2000</v>
       </c>
       <c r="N19" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="O19" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -2555,7 +2558,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2563,46 +2566,46 @@
         <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E20" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F20">
-        <v>6450000</v>
+        <v>2000000</v>
       </c>
       <c r="G20">
-        <v>6450000</v>
+        <v>2000000</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>2000</v>
+        <v>7500</v>
       </c>
       <c r="J20">
-        <v>2000</v>
+        <v>9000</v>
       </c>
       <c r="K20">
-        <v>6930000</v>
+        <v>17529140</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>2000</v>
+        <v>11500</v>
       </c>
       <c r="N20" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="O20" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -2632,7 +2635,7 @@
         <v>0</v>
       </c>
       <c r="Y20" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2640,46 +2643,46 @@
         <v>41</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E21" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F21">
-        <v>1600000</v>
+        <v>6450000</v>
       </c>
       <c r="G21">
-        <v>1600000</v>
+        <v>6450000</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="J21">
-        <v>23500</v>
+        <v>2000</v>
       </c>
       <c r="K21">
-        <v>8751446</v>
+        <v>6930000</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>30000</v>
+        <v>2000</v>
       </c>
       <c r="N21" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="O21" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -2709,84 +2712,161 @@
         <v>0</v>
       </c>
       <c r="Y21" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:25">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" t="s">
+        <v>97</v>
+      </c>
+      <c r="F22">
+        <v>1600000</v>
+      </c>
+      <c r="G22">
+        <v>1600000</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>20000</v>
+      </c>
+      <c r="J22">
+        <v>23500</v>
+      </c>
+      <c r="K22">
+        <v>8751446</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>30000</v>
+      </c>
+      <c r="N22" t="s">
+        <v>119</v>
+      </c>
+      <c r="O22" t="s">
+        <v>135</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25">
+      <c r="A23" t="s">
         <v>40</v>
       </c>
-      <c r="C22" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" t="s">
-        <v>74</v>
-      </c>
-      <c r="E22" t="s">
-        <v>95</v>
-      </c>
-      <c r="F22">
+      <c r="B23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" t="s">
+        <v>98</v>
+      </c>
+      <c r="F23">
         <v>23333334</v>
       </c>
-      <c r="G22">
+      <c r="G23">
         <v>23333334</v>
       </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
         <v>3000</v>
       </c>
-      <c r="J22">
+      <c r="J23">
         <v>3800</v>
       </c>
-      <c r="K22">
+      <c r="K23">
         <v>43477664</v>
       </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
         <v>3000</v>
       </c>
-      <c r="N22" t="s">
-        <v>116</v>
-      </c>
-      <c r="O22" t="s">
-        <v>118</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>0</v>
-      </c>
-      <c r="V22">
-        <v>0</v>
-      </c>
-      <c r="W22">
-        <v>0</v>
-      </c>
-      <c r="X22">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>148</v>
+      <c r="N23" t="s">
+        <v>120</v>
+      </c>
+      <c r="O23" t="s">
+        <v>123</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -2801,99 +2881,99 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D2" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B3" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="C3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E3" t="s">
-        <v>118</v>
+        <v>217</v>
       </c>
       <c r="F3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B4" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="C4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D4" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E4" t="s">
-        <v>214</v>
+        <v>123</v>
       </c>
       <c r="F4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B5" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D5" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E5" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F5" t="s">
         <v>229</v>
@@ -2901,99 +2981,99 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B6" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C6" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D6" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E6" t="s">
-        <v>216</v>
+        <v>123</v>
       </c>
       <c r="F6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B7" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C7" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D7" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E7" t="s">
-        <v>118</v>
+        <v>219</v>
       </c>
       <c r="F7" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B8" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B9" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C9" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E9" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B10" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C10" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D10" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E10" t="s">
-        <v>219</v>
+        <v>123</v>
       </c>
       <c r="F10" t="s">
         <v>231</v>
@@ -3001,222 +3081,222 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B11" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C11" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D11" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E11" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B12" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C12" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D12" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E12" t="s">
-        <v>118</v>
+        <v>222</v>
       </c>
       <c r="F12" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B13" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C13" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D13" t="s">
-        <v>205</v>
+        <v>123</v>
       </c>
       <c r="E13" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F13" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B14" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D14" t="s">
-        <v>206</v>
+        <v>123</v>
       </c>
       <c r="E14" t="s">
-        <v>209</v>
+        <v>123</v>
       </c>
       <c r="F14" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C15" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D15" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E15" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F15" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C16" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="D16" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E16" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="F16" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B17" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C17" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D17" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E17" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="F17" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="B18" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C18" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D18" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E18" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F18" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>170</v>
+        <v>78</v>
       </c>
       <c r="B19" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C19" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D19" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E19" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F19" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="B20" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C20" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="D20" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="E20" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F20" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>78</v>
+        <v>177</v>
       </c>
       <c r="B21" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C21" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D21" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E21" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="F21" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="234">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -140,36 +140,33 @@
     <t>2024-06-03</t>
   </si>
   <si>
+    <t>2024-08-08</t>
+  </si>
+  <si>
+    <t>2024-08-06</t>
+  </si>
+  <si>
+    <t>2024-07-19</t>
+  </si>
+  <si>
+    <t>2024-07-17</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>2024-06-28</t>
+  </si>
+  <si>
+    <t>2024-06-19</t>
+  </si>
+  <si>
+    <t>2024-06-17</t>
+  </si>
+  <si>
     <t>2024-06-05</t>
   </si>
   <si>
-    <t>2024-05-30</t>
-  </si>
-  <si>
-    <t>2024-08-08</t>
-  </si>
-  <si>
-    <t>2024-08-06</t>
-  </si>
-  <si>
-    <t>2024-07-19</t>
-  </si>
-  <si>
-    <t>2024-07-17</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>2024-06-28</t>
-  </si>
-  <si>
-    <t>2024-06-19</t>
-  </si>
-  <si>
-    <t>2024-06-17</t>
-  </si>
-  <si>
     <t>2024-08-23</t>
   </si>
   <si>
@@ -242,9 +239,6 @@
     <t>엘에스</t>
   </si>
   <si>
-    <t>IBK</t>
-  </si>
-  <si>
     <t>신한, 한국</t>
   </si>
   <si>
@@ -305,12 +299,6 @@
     <t>에스오에스랩</t>
   </si>
   <si>
-    <t>미래에셋비전스팩6호</t>
-  </si>
-  <si>
-    <t>한중엔시에스</t>
-  </si>
-  <si>
     <t>신한글로벌액티브리츠</t>
   </si>
   <si>
@@ -371,12 +359,6 @@
     <t>1072.30:1</t>
   </si>
   <si>
-    <t>1,107.2:1</t>
-  </si>
-  <si>
-    <t>725.94:1</t>
-  </si>
-  <si>
     <t>38.7:1</t>
   </si>
   <si>
@@ -422,9 +404,6 @@
     <t>4.19%</t>
   </si>
   <si>
-    <t>12.44%</t>
-  </si>
-  <si>
     <t>첨단바이오의약품 위탁개발생산(CDMO) 서비스 / 차세대 세포,유전자 치료제</t>
   </si>
   <si>
@@ -476,9 +455,6 @@
     <t>산업용 및 차량용 라이다(LiDAR)</t>
   </si>
   <si>
-    <t>수냉식 냉각시스템 ESS Parts, 공랭식 ESS Module Parts, EV Module 및 내연기관 Parts</t>
-  </si>
-  <si>
     <t>신탁 및 집합투자</t>
   </si>
   <si>
@@ -503,6 +479,9 @@
     <t>신한스팩14호</t>
   </si>
   <si>
+    <t>씨메스</t>
+  </si>
+  <si>
     <t>루미르</t>
   </si>
   <si>
@@ -548,12 +527,12 @@
     <t>엠83</t>
   </si>
   <si>
-    <t>전진건설로봇(구.전진중공업)(유가)</t>
-  </si>
-  <si>
     <t>2024.10.01~10.02</t>
   </si>
   <si>
+    <t>2024.09.19~09.25</t>
+  </si>
+  <si>
     <t>2024.09.09~09.13</t>
   </si>
   <si>
@@ -599,6 +578,9 @@
     <t>2,000~2,000</t>
   </si>
   <si>
+    <t>20,000~24,000</t>
+  </si>
+  <si>
     <t>16,500~20,500</t>
   </si>
   <si>
@@ -641,9 +623,6 @@
     <t>12,500~15,500</t>
   </si>
   <si>
-    <t>13,800~15,700</t>
-  </si>
-  <si>
     <t>32000</t>
   </si>
   <si>
@@ -662,12 +641,12 @@
     <t>15500</t>
   </si>
   <si>
-    <t>16500</t>
-  </si>
-  <si>
     <t>10000</t>
   </si>
   <si>
+    <t>52000</t>
+  </si>
+  <si>
     <t>49500</t>
   </si>
   <si>
@@ -701,10 +680,10 @@
     <t>21700</t>
   </si>
   <si>
-    <t>50781</t>
-  </si>
-  <si>
     <t>신한투자증권</t>
+  </si>
+  <si>
+    <t>삼성증권,유진투자증권,유안타증권</t>
   </si>
   <si>
     <t>NH투자증권</t>
@@ -1095,7 +1074,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y23"/>
+  <dimension ref="A1:Y21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1180,16 +1159,16 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F2">
         <v>1566800</v>
@@ -1216,10 +1195,10 @@
         <v>15300</v>
       </c>
       <c r="N2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="O2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="P2">
         <v>7367362</v>
@@ -1249,7 +1228,7 @@
         <v>-2903334</v>
       </c>
       <c r="Y2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1257,16 +1236,16 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F3">
         <v>1000000</v>
@@ -1293,10 +1272,10 @@
         <v>13000</v>
       </c>
       <c r="N3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O3" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="P3">
         <v>25588</v>
@@ -1326,7 +1305,7 @@
         <v>809</v>
       </c>
       <c r="Y3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1334,16 +1313,16 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F4">
         <v>6500000</v>
@@ -1370,10 +1349,10 @@
         <v>2000</v>
       </c>
       <c r="N4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O4" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1403,7 +1382,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1414,13 +1393,13 @@
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F5">
         <v>1400000</v>
@@ -1447,10 +1426,10 @@
         <v>15500</v>
       </c>
       <c r="N5" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="O5" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="P5">
         <v>10740898602</v>
@@ -1480,7 +1459,7 @@
         <v>219774608</v>
       </c>
       <c r="Y5" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1491,13 +1470,13 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F6">
         <v>1000000</v>
@@ -1524,10 +1503,10 @@
         <v>29000</v>
       </c>
       <c r="N6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="O6" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1557,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1568,13 +1547,13 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F7">
         <v>751000</v>
@@ -1601,10 +1580,10 @@
         <v>21000</v>
       </c>
       <c r="N7" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O7" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1634,7 +1613,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1645,13 +1624,13 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F8">
         <v>5800000</v>
@@ -1678,10 +1657,10 @@
         <v>2000</v>
       </c>
       <c r="N8" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1711,7 +1690,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1722,13 +1701,13 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F9">
         <v>1400000</v>
@@ -1755,10 +1734,10 @@
         <v>16000</v>
       </c>
       <c r="N9" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="O9" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="P9">
         <v>72895458363</v>
@@ -1788,7 +1767,7 @@
         <v>-3801868433</v>
       </c>
       <c r="Y9" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1796,16 +1775,16 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F10">
         <v>2234000</v>
@@ -1832,10 +1811,10 @@
         <v>10000</v>
       </c>
       <c r="N10" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="O10" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="P10">
         <v>1337894447</v>
@@ -1865,7 +1844,7 @@
         <v>-1257080998</v>
       </c>
       <c r="Y10" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1873,16 +1852,16 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F11">
         <v>1350000</v>
@@ -1909,10 +1888,10 @@
         <v>22000</v>
       </c>
       <c r="N11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="O11" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="P11">
         <v>5214628820</v>
@@ -1942,7 +1921,7 @@
         <v>24178632</v>
       </c>
       <c r="Y11" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1950,16 +1929,16 @@
         <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F12">
         <v>6000000</v>
@@ -1986,10 +1965,10 @@
         <v>2000</v>
       </c>
       <c r="N12" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="O12" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -2019,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -2027,16 +2006,16 @@
         <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F13">
         <v>4000000</v>
@@ -2063,10 +2042,10 @@
         <v>2000</v>
       </c>
       <c r="N13" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="O13" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -2096,7 +2075,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -2104,16 +2083,16 @@
         <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F14">
         <v>1618000</v>
@@ -2140,10 +2119,10 @@
         <v>10000</v>
       </c>
       <c r="N14" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="O14" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -2173,7 +2152,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -2181,16 +2160,16 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F15">
         <v>4000000</v>
@@ -2217,10 +2196,10 @@
         <v>2000</v>
       </c>
       <c r="N15" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="O15" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -2250,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="Y15" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -2258,16 +2237,16 @@
         <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F16">
         <v>1810000</v>
@@ -2294,10 +2273,10 @@
         <v>16000</v>
       </c>
       <c r="N16" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="O16" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="P16">
         <v>12596039842</v>
@@ -2327,7 +2306,7 @@
         <v>1795726428</v>
       </c>
       <c r="Y16" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2335,16 +2314,16 @@
         <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F17">
         <v>1330000</v>
@@ -2371,10 +2350,10 @@
         <v>43300</v>
       </c>
       <c r="N17" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="O17" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="P17">
         <v>103267682</v>
@@ -2404,7 +2383,7 @@
         <v>-83246975113</v>
       </c>
       <c r="Y17" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2418,10 +2397,10 @@
         <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E18" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F18">
         <v>3400000</v>
@@ -2448,10 +2427,10 @@
         <v>7000</v>
       </c>
       <c r="N18" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="O18" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="P18">
         <v>85187882584</v>
@@ -2481,7 +2460,7 @@
         <v>2646634321</v>
       </c>
       <c r="Y18" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2492,13 +2471,13 @@
         <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E19" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F19">
         <v>6250000</v>
@@ -2525,10 +2504,10 @@
         <v>2000</v>
       </c>
       <c r="N19" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="O19" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -2558,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2569,13 +2548,13 @@
         <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E20" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F20">
         <v>2000000</v>
@@ -2602,10 +2581,10 @@
         <v>11500</v>
       </c>
       <c r="N20" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="O20" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -2635,54 +2614,54 @@
         <v>0</v>
       </c>
       <c r="Y20" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" spans="1:25">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F21">
-        <v>6450000</v>
+        <v>23333334</v>
       </c>
       <c r="G21">
-        <v>6450000</v>
+        <v>23333334</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="J21">
-        <v>2000</v>
+        <v>3800</v>
       </c>
       <c r="K21">
-        <v>6930000</v>
+        <v>43477664</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="N21" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="O21" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -2712,161 +2691,7 @@
         <v>0</v>
       </c>
       <c r="Y21" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25">
-      <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E22" t="s">
-        <v>97</v>
-      </c>
-      <c r="F22">
-        <v>1600000</v>
-      </c>
-      <c r="G22">
-        <v>1600000</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>20000</v>
-      </c>
-      <c r="J22">
-        <v>23500</v>
-      </c>
-      <c r="K22">
-        <v>8751446</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>30000</v>
-      </c>
-      <c r="N22" t="s">
-        <v>119</v>
-      </c>
-      <c r="O22" t="s">
-        <v>135</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>0</v>
-      </c>
-      <c r="V22">
-        <v>0</v>
-      </c>
-      <c r="W22">
-        <v>0</v>
-      </c>
-      <c r="X22">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25">
-      <c r="A23" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" t="s">
-        <v>64</v>
-      </c>
-      <c r="D23" t="s">
-        <v>76</v>
-      </c>
-      <c r="E23" t="s">
-        <v>98</v>
-      </c>
-      <c r="F23">
-        <v>23333334</v>
-      </c>
-      <c r="G23">
-        <v>23333334</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>3000</v>
-      </c>
-      <c r="J23">
-        <v>3800</v>
-      </c>
-      <c r="K23">
-        <v>43477664</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>3000</v>
-      </c>
-      <c r="N23" t="s">
-        <v>120</v>
-      </c>
-      <c r="O23" t="s">
-        <v>123</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>0</v>
-      </c>
-      <c r="V23">
-        <v>0</v>
-      </c>
-      <c r="W23">
-        <v>0</v>
-      </c>
-      <c r="X23">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -2881,319 +2706,319 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B2" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C2" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D2" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E2" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="F2" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="B3" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C3" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D3" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E3" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="F3" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="B4" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C4" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="D4" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E4" t="s">
-        <v>123</v>
+        <v>210</v>
       </c>
       <c r="F4" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="B5" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C5" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D5" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E5" t="s">
-        <v>218</v>
+        <v>117</v>
       </c>
       <c r="F5" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="B6" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C6" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="D6" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E6" t="s">
-        <v>123</v>
+        <v>211</v>
       </c>
       <c r="F6" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="B7" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C7" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D7" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E7" t="s">
-        <v>219</v>
+        <v>117</v>
       </c>
       <c r="F7" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B8" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E8" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F8" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="B9" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C9" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="D9" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E9" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="F9" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="B10" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C10" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="D10" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E10" t="s">
-        <v>123</v>
+        <v>213</v>
       </c>
       <c r="F10" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B11" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D11" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E11" t="s">
-        <v>221</v>
+        <v>117</v>
       </c>
       <c r="F11" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B12" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C12" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="D12" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E12" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="F12" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C13" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D13" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E13" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="F13" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="C14" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D14" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E14" t="s">
-        <v>123</v>
+        <v>216</v>
       </c>
       <c r="F14" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C15" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="D15" t="s">
-        <v>209</v>
+        <v>117</v>
       </c>
       <c r="E15" t="s">
-        <v>224</v>
+        <v>117</v>
       </c>
       <c r="F15" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="B16" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="C16" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D16" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="E16" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="F16" t="s">
         <v>231</v>
@@ -3201,102 +3026,102 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>77</v>
+        <v>168</v>
       </c>
       <c r="B17" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C17" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="D17" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="E17" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="F17" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>176</v>
+        <v>75</v>
       </c>
       <c r="B18" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C18" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="D18" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="E18" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="F18" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>169</v>
       </c>
       <c r="B19" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C19" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D19" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="E19" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="F19" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B20" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C20" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D20" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E20" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="F20" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="B21" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C21" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="D21" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="E21" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="F21" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="229">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -203,9 +203,6 @@
     <t>2024-06-26</t>
   </si>
   <si>
-    <t>2024-06-25</t>
-  </si>
-  <si>
     <t>2024-07-01</t>
   </si>
   <si>
@@ -296,9 +293,6 @@
     <t>한국제15호스팩</t>
   </si>
   <si>
-    <t>에스오에스랩</t>
-  </si>
-  <si>
     <t>신한글로벌액티브리츠</t>
   </si>
   <si>
@@ -356,9 +350,6 @@
     <t>1,073.31:1</t>
   </si>
   <si>
-    <t>1072.30:1</t>
-  </si>
-  <si>
     <t>38.7:1</t>
   </si>
   <si>
@@ -401,9 +392,6 @@
     <t>11.80%</t>
   </si>
   <si>
-    <t>4.19%</t>
-  </si>
-  <si>
     <t>첨단바이오의약품 위탁개발생산(CDMO) 서비스 / 차세대 세포,유전자 치료제</t>
   </si>
   <si>
@@ -450,9 +438,6 @@
   </si>
   <si>
     <t>전동기 및 발전기 (범용모터, 서보모터)</t>
-  </si>
-  <si>
-    <t>산업용 및 차량용 라이다(LiDAR)</t>
   </si>
   <si>
     <t>신탁 및 집합투자</t>
@@ -1074,7 +1059,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y21"/>
+  <dimension ref="A1:Y20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1165,10 +1150,10 @@
         <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F2">
         <v>1566800</v>
@@ -1195,10 +1180,10 @@
         <v>15300</v>
       </c>
       <c r="N2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="P2">
         <v>7367362</v>
@@ -1228,7 +1213,7 @@
         <v>-2903334</v>
       </c>
       <c r="Y2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1242,10 +1227,10 @@
         <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F3">
         <v>1000000</v>
@@ -1272,10 +1257,10 @@
         <v>13000</v>
       </c>
       <c r="N3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="O3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="P3">
         <v>25588</v>
@@ -1305,7 +1290,7 @@
         <v>809</v>
       </c>
       <c r="Y3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1319,10 +1304,10 @@
         <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F4">
         <v>6500000</v>
@@ -1349,10 +1334,10 @@
         <v>2000</v>
       </c>
       <c r="N4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="O4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1382,7 +1367,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1396,10 +1381,10 @@
         <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F5">
         <v>1400000</v>
@@ -1426,10 +1411,10 @@
         <v>15500</v>
       </c>
       <c r="N5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="O5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="P5">
         <v>10740898602</v>
@@ -1459,7 +1444,7 @@
         <v>219774608</v>
       </c>
       <c r="Y5" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1473,10 +1458,10 @@
         <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F6">
         <v>1000000</v>
@@ -1503,10 +1488,10 @@
         <v>29000</v>
       </c>
       <c r="N6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="O6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1536,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1550,10 +1535,10 @@
         <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F7">
         <v>751000</v>
@@ -1580,10 +1565,10 @@
         <v>21000</v>
       </c>
       <c r="N7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1613,7 +1598,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1627,10 +1612,10 @@
         <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F8">
         <v>5800000</v>
@@ -1657,10 +1642,10 @@
         <v>2000</v>
       </c>
       <c r="N8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="O8" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1690,7 +1675,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1704,10 +1689,10 @@
         <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F9">
         <v>1400000</v>
@@ -1734,10 +1719,10 @@
         <v>16000</v>
       </c>
       <c r="N9" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="O9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="P9">
         <v>72895458363</v>
@@ -1767,7 +1752,7 @@
         <v>-3801868433</v>
       </c>
       <c r="Y9" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1781,10 +1766,10 @@
         <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F10">
         <v>2234000</v>
@@ -1811,10 +1796,10 @@
         <v>10000</v>
       </c>
       <c r="N10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P10">
         <v>1337894447</v>
@@ -1844,7 +1829,7 @@
         <v>-1257080998</v>
       </c>
       <c r="Y10" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1858,10 +1843,10 @@
         <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F11">
         <v>1350000</v>
@@ -1888,10 +1873,10 @@
         <v>22000</v>
       </c>
       <c r="N11" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="O11" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="P11">
         <v>5214628820</v>
@@ -1921,7 +1906,7 @@
         <v>24178632</v>
       </c>
       <c r="Y11" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1935,10 +1920,10 @@
         <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F12">
         <v>6000000</v>
@@ -1965,10 +1950,10 @@
         <v>2000</v>
       </c>
       <c r="N12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="O12" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1998,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -2012,10 +1997,10 @@
         <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F13">
         <v>4000000</v>
@@ -2042,10 +2027,10 @@
         <v>2000</v>
       </c>
       <c r="N13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="O13" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -2075,7 +2060,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -2089,10 +2074,10 @@
         <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F14">
         <v>1618000</v>
@@ -2119,10 +2104,10 @@
         <v>10000</v>
       </c>
       <c r="N14" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="O14" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -2152,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -2166,10 +2151,10 @@
         <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F15">
         <v>4000000</v>
@@ -2196,10 +2181,10 @@
         <v>2000</v>
       </c>
       <c r="N15" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="O15" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -2229,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="Y15" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -2243,10 +2228,10 @@
         <v>59</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F16">
         <v>1810000</v>
@@ -2273,10 +2258,10 @@
         <v>16000</v>
       </c>
       <c r="N16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O16" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="P16">
         <v>12596039842</v>
@@ -2306,7 +2291,7 @@
         <v>1795726428</v>
       </c>
       <c r="Y16" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2320,10 +2305,10 @@
         <v>60</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F17">
         <v>1330000</v>
@@ -2350,10 +2335,10 @@
         <v>43300</v>
       </c>
       <c r="N17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="O17" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="P17">
         <v>103267682</v>
@@ -2383,7 +2368,7 @@
         <v>-83246975113</v>
       </c>
       <c r="Y17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2397,10 +2382,10 @@
         <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F18">
         <v>3400000</v>
@@ -2427,10 +2412,10 @@
         <v>7000</v>
       </c>
       <c r="N18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O18" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="P18">
         <v>85187882584</v>
@@ -2460,7 +2445,7 @@
         <v>2646634321</v>
       </c>
       <c r="Y18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2474,10 +2459,10 @@
         <v>61</v>
       </c>
       <c r="D19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F19">
         <v>6250000</v>
@@ -2504,10 +2489,10 @@
         <v>2000</v>
       </c>
       <c r="N19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="O19" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -2537,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2545,46 +2530,46 @@
         <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s">
         <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F20">
-        <v>2000000</v>
+        <v>23333334</v>
       </c>
       <c r="G20">
-        <v>2000000</v>
+        <v>23333334</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>7500</v>
+        <v>3000</v>
       </c>
       <c r="J20">
-        <v>9000</v>
+        <v>3800</v>
       </c>
       <c r="K20">
-        <v>17529140</v>
+        <v>43477664</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>11500</v>
+        <v>3000</v>
       </c>
       <c r="N20" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="O20" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -2614,84 +2599,7 @@
         <v>0</v>
       </c>
       <c r="Y20" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25">
-      <c r="A21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" t="s">
-        <v>63</v>
-      </c>
-      <c r="D21" t="s">
-        <v>74</v>
-      </c>
-      <c r="E21" t="s">
-        <v>94</v>
-      </c>
-      <c r="F21">
-        <v>23333334</v>
-      </c>
-      <c r="G21">
-        <v>23333334</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>3000</v>
-      </c>
-      <c r="J21">
-        <v>3800</v>
-      </c>
-      <c r="K21">
-        <v>43477664</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>3000</v>
-      </c>
-      <c r="N21" t="s">
-        <v>114</v>
-      </c>
-      <c r="O21" t="s">
-        <v>117</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -2706,422 +2614,422 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E2" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="F2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B3" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E3" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B4" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C4" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E4" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F4" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B5" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C5" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F5" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B6" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C6" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E6" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F6" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B7" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D7" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E7" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F7" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C8" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E8" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F8" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C9" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E9" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="F9" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B10" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E10" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="F10" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B11" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C11" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D11" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E11" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F11" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C12" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F12" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C13" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D13" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E13" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="F13" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C14" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D14" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F14" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B15" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C15" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D15" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E15" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F15" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B16" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C16" t="s">
+        <v>192</v>
+      </c>
+      <c r="D16" t="s">
         <v>197</v>
       </c>
-      <c r="D16" t="s">
-        <v>202</v>
-      </c>
       <c r="E16" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="F16" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B17" t="s">
+        <v>176</v>
+      </c>
+      <c r="C17" t="s">
         <v>181</v>
       </c>
-      <c r="C17" t="s">
-        <v>186</v>
-      </c>
       <c r="D17" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E17" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F17" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B18" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C18" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D18" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="E18" t="s">
+        <v>213</v>
+      </c>
+      <c r="F18" t="s">
         <v>218</v>
-      </c>
-      <c r="F18" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B19" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C19" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D19" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E19" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="F19" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C20" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D20" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E20" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F20" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B21" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C21" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D21" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="E21" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="F21" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="225">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -134,9 +134,6 @@
     <t>2024-06-07</t>
   </si>
   <si>
-    <t>2024-06-10</t>
-  </si>
-  <si>
     <t>2024-06-03</t>
   </si>
   <si>
@@ -200,9 +197,6 @@
     <t>2024-07-02</t>
   </si>
   <si>
-    <t>2024-06-26</t>
-  </si>
-  <si>
     <t>2024-07-01</t>
   </si>
   <si>
@@ -290,9 +284,6 @@
     <t>하이젠알앤엠</t>
   </si>
   <si>
-    <t>한국제15호스팩</t>
-  </si>
-  <si>
     <t>신한글로벌액티브리츠</t>
   </si>
   <si>
@@ -345,9 +336,6 @@
   </si>
   <si>
     <t>1099.21:1</t>
-  </si>
-  <si>
-    <t>1,073.31:1</t>
   </si>
   <si>
     <t>38.7:1</t>
@@ -1059,7 +1047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y20"/>
+  <dimension ref="A1:Y19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1144,16 +1132,16 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F2">
         <v>1566800</v>
@@ -1180,10 +1168,10 @@
         <v>15300</v>
       </c>
       <c r="N2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="O2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="P2">
         <v>7367362</v>
@@ -1213,7 +1201,7 @@
         <v>-2903334</v>
       </c>
       <c r="Y2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1221,16 +1209,16 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F3">
         <v>1000000</v>
@@ -1257,10 +1245,10 @@
         <v>13000</v>
       </c>
       <c r="N3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="P3">
         <v>25588</v>
@@ -1290,7 +1278,7 @@
         <v>809</v>
       </c>
       <c r="Y3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1298,16 +1286,16 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F4">
         <v>6500000</v>
@@ -1334,10 +1322,10 @@
         <v>2000</v>
       </c>
       <c r="N4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1367,7 +1355,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1378,13 +1366,13 @@
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F5">
         <v>1400000</v>
@@ -1411,10 +1399,10 @@
         <v>15500</v>
       </c>
       <c r="N5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="O5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="P5">
         <v>10740898602</v>
@@ -1444,7 +1432,7 @@
         <v>219774608</v>
       </c>
       <c r="Y5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1455,13 +1443,13 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F6">
         <v>1000000</v>
@@ -1488,10 +1476,10 @@
         <v>29000</v>
       </c>
       <c r="N6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1521,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1532,13 +1520,13 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F7">
         <v>751000</v>
@@ -1565,10 +1553,10 @@
         <v>21000</v>
       </c>
       <c r="N7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O7" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1598,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1609,13 +1597,13 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F8">
         <v>5800000</v>
@@ -1642,10 +1630,10 @@
         <v>2000</v>
       </c>
       <c r="N8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1675,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1686,13 +1674,13 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F9">
         <v>1400000</v>
@@ -1719,10 +1707,10 @@
         <v>16000</v>
       </c>
       <c r="N9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O9" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="P9">
         <v>72895458363</v>
@@ -1752,7 +1740,7 @@
         <v>-3801868433</v>
       </c>
       <c r="Y9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1760,16 +1748,16 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F10">
         <v>2234000</v>
@@ -1796,10 +1784,10 @@
         <v>10000</v>
       </c>
       <c r="N10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="P10">
         <v>1337894447</v>
@@ -1829,7 +1817,7 @@
         <v>-1257080998</v>
       </c>
       <c r="Y10" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1837,16 +1825,16 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F11">
         <v>1350000</v>
@@ -1873,10 +1861,10 @@
         <v>22000</v>
       </c>
       <c r="N11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="O11" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="P11">
         <v>5214628820</v>
@@ -1906,7 +1894,7 @@
         <v>24178632</v>
       </c>
       <c r="Y11" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1914,16 +1902,16 @@
         <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F12">
         <v>6000000</v>
@@ -1950,10 +1938,10 @@
         <v>2000</v>
       </c>
       <c r="N12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="O12" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1983,7 +1971,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1991,16 +1979,16 @@
         <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F13">
         <v>4000000</v>
@@ -2027,10 +2015,10 @@
         <v>2000</v>
       </c>
       <c r="N13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O13" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -2060,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -2068,16 +2056,16 @@
         <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F14">
         <v>1618000</v>
@@ -2104,10 +2092,10 @@
         <v>10000</v>
       </c>
       <c r="N14" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="O14" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -2137,7 +2125,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -2145,16 +2133,16 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F15">
         <v>4000000</v>
@@ -2181,10 +2169,10 @@
         <v>2000</v>
       </c>
       <c r="N15" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O15" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -2214,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="Y15" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -2222,16 +2210,16 @@
         <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F16">
         <v>1810000</v>
@@ -2258,10 +2246,10 @@
         <v>16000</v>
       </c>
       <c r="N16" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="O16" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="P16">
         <v>12596039842</v>
@@ -2291,7 +2279,7 @@
         <v>1795726428</v>
       </c>
       <c r="Y16" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2299,16 +2287,16 @@
         <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F17">
         <v>1330000</v>
@@ -2335,10 +2323,10 @@
         <v>43300</v>
       </c>
       <c r="N17" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="O17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="P17">
         <v>103267682</v>
@@ -2368,7 +2356,7 @@
         <v>-83246975113</v>
       </c>
       <c r="Y17" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2382,10 +2370,10 @@
         <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F18">
         <v>3400000</v>
@@ -2412,10 +2400,10 @@
         <v>7000</v>
       </c>
       <c r="N18" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="O18" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="P18">
         <v>85187882584</v>
@@ -2445,7 +2433,7 @@
         <v>2646634321</v>
       </c>
       <c r="Y18" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2453,47 +2441,47 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D19" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E19" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F19">
-        <v>6250000</v>
+        <v>23333334</v>
       </c>
       <c r="G19">
-        <v>6250000</v>
+        <v>23333334</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="J19">
-        <v>2000</v>
+        <v>3800</v>
       </c>
       <c r="K19">
-        <v>6870000</v>
+        <v>43477664</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="N19" t="s">
+        <v>107</v>
+      </c>
+      <c r="O19" t="s">
         <v>110</v>
       </c>
-      <c r="O19" t="s">
-        <v>114</v>
-      </c>
       <c r="P19">
         <v>0</v>
       </c>
@@ -2522,84 +2510,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25">
-      <c r="A20" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" t="s">
-        <v>62</v>
-      </c>
-      <c r="D20" t="s">
-        <v>73</v>
-      </c>
-      <c r="E20" t="s">
-        <v>92</v>
-      </c>
-      <c r="F20">
-        <v>23333334</v>
-      </c>
-      <c r="G20">
-        <v>23333334</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>3000</v>
-      </c>
-      <c r="J20">
-        <v>3800</v>
-      </c>
-      <c r="K20">
-        <v>43477664</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>3000</v>
-      </c>
-      <c r="N20" t="s">
-        <v>111</v>
-      </c>
-      <c r="O20" t="s">
-        <v>114</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>0</v>
-      </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
-      <c r="W20">
-        <v>0</v>
-      </c>
-      <c r="X20">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -2614,422 +2525,422 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B4" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C4" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F4" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B5" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C5" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F5" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B7" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C7" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E7" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F7" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B8" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C8" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F8" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B9" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C9" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F9" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B10" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C10" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E10" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F10" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B11" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C11" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D11" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E11" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F11" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C12" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E12" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F12" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C13" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D13" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E13" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="F13" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B14" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C14" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E14" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="F14" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B15" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C15" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E15" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F15" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B16" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C16" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D16" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E16" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="F16" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B17" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C17" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D17" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E17" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F17" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B18" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C18" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D18" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E18" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="F18" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B19" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C19" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D19" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E19" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="F19" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B20" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C20" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D20" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E20" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F20" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B21" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C21" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D21" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E21" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="F21" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="220">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -131,9 +131,6 @@
     <t>2024-06-11</t>
   </si>
   <si>
-    <t>2024-06-07</t>
-  </si>
-  <si>
     <t>2024-06-03</t>
   </si>
   <si>
@@ -281,9 +278,6 @@
     <t>이노스페이스</t>
   </si>
   <si>
-    <t>하이젠알앤엠</t>
-  </si>
-  <si>
     <t>신한글로벌액티브리츠</t>
   </si>
   <si>
@@ -335,9 +329,6 @@
     <t>598.87:1</t>
   </si>
   <si>
-    <t>1099.21:1</t>
-  </si>
-  <si>
     <t>38.7:1</t>
   </si>
   <si>
@@ -377,9 +368,6 @@
     <t>1.99%</t>
   </si>
   <si>
-    <t>11.80%</t>
-  </si>
-  <si>
     <t>첨단바이오의약품 위탁개발생산(CDMO) 서비스 / 차세대 세포,유전자 치료제</t>
   </si>
   <si>
@@ -423,9 +411,6 @@
   </si>
   <si>
     <t>소형발사체, 로켓추진기관, 과학로켓, 시험평가용역</t>
-  </si>
-  <si>
-    <t>전동기 및 발전기 (범용모터, 서보모터)</t>
   </si>
   <si>
     <t>신탁 및 집합투자</t>
@@ -1047,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y19"/>
+  <dimension ref="A1:Y18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1132,16 +1117,16 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F2">
         <v>1566800</v>
@@ -1168,10 +1153,10 @@
         <v>15300</v>
       </c>
       <c r="N2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="O2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="P2">
         <v>7367362</v>
@@ -1201,7 +1186,7 @@
         <v>-2903334</v>
       </c>
       <c r="Y2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1209,16 +1194,16 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F3">
         <v>1000000</v>
@@ -1245,10 +1230,10 @@
         <v>13000</v>
       </c>
       <c r="N3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="O3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="P3">
         <v>25588</v>
@@ -1278,7 +1263,7 @@
         <v>809</v>
       </c>
       <c r="Y3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1286,16 +1271,16 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F4">
         <v>6500000</v>
@@ -1322,10 +1307,10 @@
         <v>2000</v>
       </c>
       <c r="N4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="O4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1355,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1366,13 +1351,13 @@
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F5">
         <v>1400000</v>
@@ -1399,10 +1384,10 @@
         <v>15500</v>
       </c>
       <c r="N5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="P5">
         <v>10740898602</v>
@@ -1432,7 +1417,7 @@
         <v>219774608</v>
       </c>
       <c r="Y5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1443,13 +1428,13 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F6">
         <v>1000000</v>
@@ -1476,10 +1461,10 @@
         <v>29000</v>
       </c>
       <c r="N6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="O6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1509,7 +1494,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1520,13 +1505,13 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F7">
         <v>751000</v>
@@ -1553,10 +1538,10 @@
         <v>21000</v>
       </c>
       <c r="N7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1586,7 +1571,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1597,13 +1582,13 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F8">
         <v>5800000</v>
@@ -1630,10 +1615,10 @@
         <v>2000</v>
       </c>
       <c r="N8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="O8" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1663,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1674,13 +1659,13 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F9">
         <v>1400000</v>
@@ -1707,10 +1692,10 @@
         <v>16000</v>
       </c>
       <c r="N9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="O9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="P9">
         <v>72895458363</v>
@@ -1740,7 +1725,7 @@
         <v>-3801868433</v>
       </c>
       <c r="Y9" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1748,16 +1733,16 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F10">
         <v>2234000</v>
@@ -1784,10 +1769,10 @@
         <v>10000</v>
       </c>
       <c r="N10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="O10" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="P10">
         <v>1337894447</v>
@@ -1817,7 +1802,7 @@
         <v>-1257080998</v>
       </c>
       <c r="Y10" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1825,16 +1810,16 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F11">
         <v>1350000</v>
@@ -1861,10 +1846,10 @@
         <v>22000</v>
       </c>
       <c r="N11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="O11" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="P11">
         <v>5214628820</v>
@@ -1894,7 +1879,7 @@
         <v>24178632</v>
       </c>
       <c r="Y11" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1902,16 +1887,16 @@
         <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F12">
         <v>6000000</v>
@@ -1938,10 +1923,10 @@
         <v>2000</v>
       </c>
       <c r="N12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O12" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1971,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1979,16 +1964,16 @@
         <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F13">
         <v>4000000</v>
@@ -2015,10 +2000,10 @@
         <v>2000</v>
       </c>
       <c r="N13" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="O13" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -2048,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -2056,16 +2041,16 @@
         <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F14">
         <v>1618000</v>
@@ -2092,10 +2077,10 @@
         <v>10000</v>
       </c>
       <c r="N14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="O14" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -2125,7 +2110,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -2133,16 +2118,16 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F15">
         <v>4000000</v>
@@ -2169,10 +2154,10 @@
         <v>2000</v>
       </c>
       <c r="N15" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -2202,7 +2187,7 @@
         <v>0</v>
       </c>
       <c r="Y15" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -2210,16 +2195,16 @@
         <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F16">
         <v>1810000</v>
@@ -2246,10 +2231,10 @@
         <v>16000</v>
       </c>
       <c r="N16" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="O16" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="P16">
         <v>12596039842</v>
@@ -2279,7 +2264,7 @@
         <v>1795726428</v>
       </c>
       <c r="Y16" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2287,16 +2272,16 @@
         <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F17">
         <v>1330000</v>
@@ -2323,10 +2308,10 @@
         <v>43300</v>
       </c>
       <c r="N17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="O17" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="P17">
         <v>103267682</v>
@@ -2356,7 +2341,7 @@
         <v>-83246975113</v>
       </c>
       <c r="Y17" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2364,153 +2349,76 @@
         <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F18">
-        <v>3400000</v>
+        <v>23333334</v>
       </c>
       <c r="G18">
-        <v>3400000</v>
+        <v>23333334</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>4500</v>
+        <v>3000</v>
       </c>
       <c r="J18">
-        <v>5500</v>
+        <v>3800</v>
       </c>
       <c r="K18">
-        <v>30888000</v>
+        <v>43477664</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>7000</v>
+        <v>3000</v>
       </c>
       <c r="N18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="O18" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="P18">
-        <v>85187882584</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>87525689695</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>77247394706</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>2205797752</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>4920387020</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>4336496285</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>1613954566</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>3980493669</v>
+        <v>0</v>
       </c>
       <c r="X18">
-        <v>2646634321</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25">
-      <c r="A19" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19" t="s">
-        <v>89</v>
-      </c>
-      <c r="F19">
-        <v>23333334</v>
-      </c>
-      <c r="G19">
-        <v>23333334</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>3000</v>
-      </c>
-      <c r="J19">
-        <v>3800</v>
-      </c>
-      <c r="K19">
-        <v>43477664</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>3000</v>
-      </c>
-      <c r="N19" t="s">
-        <v>107</v>
-      </c>
-      <c r="O19" t="s">
-        <v>110</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>0</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-      <c r="U19">
-        <v>0</v>
-      </c>
-      <c r="V19">
-        <v>0</v>
-      </c>
-      <c r="W19">
-        <v>0</v>
-      </c>
-      <c r="X19">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -2525,422 +2433,422 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E2" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="F2" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="F3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B4" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C4" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E4" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="F4" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B5" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C5" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F5" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B6" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C6" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E6" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F6" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B7" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C7" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F7" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B8" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C8" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="F8" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B9" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C9" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E9" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="F9" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B10" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C10" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E10" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="F10" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C11" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F11" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B12" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C12" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E12" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="F12" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B13" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C13" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E13" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F13" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B14" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C14" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D14" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E14" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F14" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B15" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C15" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F15" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B16" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C16" t="s">
+        <v>183</v>
+      </c>
+      <c r="D16" t="s">
         <v>188</v>
       </c>
-      <c r="D16" t="s">
-        <v>193</v>
-      </c>
       <c r="E16" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="F16" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B17" t="s">
+        <v>167</v>
+      </c>
+      <c r="C17" t="s">
         <v>172</v>
       </c>
-      <c r="C17" t="s">
-        <v>177</v>
-      </c>
       <c r="D17" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="E17" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="F17" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B18" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C18" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D18" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E18" t="s">
+        <v>204</v>
+      </c>
+      <c r="F18" t="s">
         <v>209</v>
-      </c>
-      <c r="F18" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B19" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C19" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D19" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E19" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F19" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B20" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C20" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D20" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="E20" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="F20" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B21" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C21" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D21" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E21" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F21" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -437,6 +437,9 @@
     <t>신한스팩14호</t>
   </si>
   <si>
+    <t>클로봇</t>
+  </si>
+  <si>
     <t>씨메스</t>
   </si>
   <si>
@@ -488,6 +491,9 @@
     <t>2024.10.01~10.02</t>
   </si>
   <si>
+    <t>2024.09.23~09.27</t>
+  </si>
+  <si>
     <t>2024.09.19~09.25</t>
   </si>
   <si>
@@ -530,12 +536,12 @@
     <t>2024.07.31~08.06</t>
   </si>
   <si>
-    <t>2024.07.30~08.05</t>
-  </si>
-  <si>
     <t>2,000~2,000</t>
   </si>
   <si>
+    <t>9,400~10,900</t>
+  </si>
+  <si>
     <t>20,000~24,000</t>
   </si>
   <si>
@@ -578,9 +584,6 @@
     <t>9,500~10,700</t>
   </si>
   <si>
-    <t>12,500~15,500</t>
-  </si>
-  <si>
     <t>32000</t>
   </si>
   <si>
@@ -596,12 +599,12 @@
     <t>13000</t>
   </si>
   <si>
-    <t>15500</t>
-  </si>
-  <si>
     <t>10000</t>
   </si>
   <si>
+    <t>28200</t>
+  </si>
+  <si>
     <t>52000</t>
   </si>
   <si>
@@ -635,12 +638,12 @@
     <t>24000</t>
   </si>
   <si>
-    <t>21700</t>
-  </si>
-  <si>
     <t>신한투자증권</t>
   </si>
   <si>
+    <t>미래에셋증권,신영증권</t>
+  </si>
+  <si>
     <t>삼성증권,유진투자증권,유안타증권</t>
   </si>
   <si>
@@ -672,9 +675,6 @@
   </si>
   <si>
     <t>신영증권,유진투자증권</t>
-  </si>
-  <si>
-    <t>하나증권</t>
   </si>
 </sst>
 </file>
@@ -2456,10 +2456,10 @@
         <v>139</v>
       </c>
       <c r="B2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D2" t="s">
         <v>107</v>
@@ -2476,10 +2476,10 @@
         <v>140</v>
       </c>
       <c r="B3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D3" t="s">
         <v>107</v>
@@ -2496,10 +2496,10 @@
         <v>141</v>
       </c>
       <c r="B4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D4" t="s">
         <v>107</v>
@@ -2516,16 +2516,16 @@
         <v>142</v>
       </c>
       <c r="B5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D5" t="s">
         <v>107</v>
       </c>
       <c r="E5" t="s">
-        <v>107</v>
+        <v>197</v>
       </c>
       <c r="F5" t="s">
         <v>210</v>
@@ -2536,19 +2536,19 @@
         <v>143</v>
       </c>
       <c r="B6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D6" t="s">
         <v>107</v>
       </c>
       <c r="E6" t="s">
-        <v>197</v>
+        <v>107</v>
       </c>
       <c r="F6" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2556,19 +2556,19 @@
         <v>144</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D7" t="s">
         <v>107</v>
       </c>
       <c r="E7" t="s">
-        <v>107</v>
+        <v>198</v>
       </c>
       <c r="F7" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2576,16 +2576,16 @@
         <v>145</v>
       </c>
       <c r="B8" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D8" t="s">
         <v>107</v>
       </c>
       <c r="E8" t="s">
-        <v>198</v>
+        <v>107</v>
       </c>
       <c r="F8" t="s">
         <v>212</v>
@@ -2596,19 +2596,19 @@
         <v>146</v>
       </c>
       <c r="B9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C9" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D9" t="s">
         <v>107</v>
       </c>
       <c r="E9" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2616,16 +2616,16 @@
         <v>147</v>
       </c>
       <c r="B10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C10" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D10" t="s">
         <v>107</v>
       </c>
       <c r="E10" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="F10" t="s">
         <v>213</v>
@@ -2636,19 +2636,19 @@
         <v>148</v>
       </c>
       <c r="B11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D11" t="s">
         <v>107</v>
       </c>
       <c r="E11" t="s">
-        <v>107</v>
+        <v>200</v>
       </c>
       <c r="F11" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2656,19 +2656,19 @@
         <v>149</v>
       </c>
       <c r="B12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C12" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="D12" t="s">
         <v>107</v>
       </c>
       <c r="E12" t="s">
-        <v>200</v>
+        <v>107</v>
       </c>
       <c r="F12" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2676,10 +2676,10 @@
         <v>150</v>
       </c>
       <c r="B13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C13" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D13" t="s">
         <v>107</v>
@@ -2696,10 +2696,10 @@
         <v>151</v>
       </c>
       <c r="B14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D14" t="s">
         <v>107</v>
@@ -2708,7 +2708,7 @@
         <v>202</v>
       </c>
       <c r="F14" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2716,19 +2716,19 @@
         <v>152</v>
       </c>
       <c r="B15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C15" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="D15" t="s">
         <v>107</v>
       </c>
       <c r="E15" t="s">
-        <v>107</v>
+        <v>203</v>
       </c>
       <c r="F15" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2736,16 +2736,16 @@
         <v>153</v>
       </c>
       <c r="B16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C16" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="D16" t="s">
-        <v>188</v>
+        <v>107</v>
       </c>
       <c r="E16" t="s">
-        <v>203</v>
+        <v>107</v>
       </c>
       <c r="F16" t="s">
         <v>217</v>
@@ -2756,50 +2756,50 @@
         <v>154</v>
       </c>
       <c r="B17" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C17" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="D17" t="s">
         <v>189</v>
       </c>
       <c r="E17" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="F17" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>71</v>
+        <v>155</v>
       </c>
       <c r="B18" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C18" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="D18" t="s">
         <v>190</v>
       </c>
       <c r="E18" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="F18" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>155</v>
+        <v>71</v>
       </c>
       <c r="B19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C19" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D19" t="s">
         <v>191</v>
@@ -2808,47 +2808,47 @@
         <v>205</v>
       </c>
       <c r="F19" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>72</v>
+        <v>156</v>
       </c>
       <c r="B20" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C20" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D20" t="s">
         <v>192</v>
       </c>
       <c r="E20" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="F20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D21" t="s">
         <v>193</v>
       </c>
       <c r="E21" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="F21" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -488,7 +488,7 @@
     <t>엠83</t>
   </si>
   <si>
-    <t>2024.10.01~10.02</t>
+    <t>2024.09.26~09.27</t>
   </si>
   <si>
     <t>2024.09.23~09.27</t>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="210">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -131,9 +131,6 @@
     <t>2024-06-11</t>
   </si>
   <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
     <t>2024-08-08</t>
   </si>
   <si>
@@ -158,9 +155,6 @@
     <t>2024-06-17</t>
   </si>
   <si>
-    <t>2024-06-05</t>
-  </si>
-  <si>
     <t>2024-08-23</t>
   </si>
   <si>
@@ -194,9 +188,6 @@
     <t>2024-07-02</t>
   </si>
   <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
     <t>NH</t>
   </si>
   <si>
@@ -227,9 +218,6 @@
     <t>엘에스</t>
   </si>
   <si>
-    <t>신한, 한국</t>
-  </si>
-  <si>
     <t>이엔셀</t>
   </si>
   <si>
@@ -278,9 +266,6 @@
     <t>이노스페이스</t>
   </si>
   <si>
-    <t>신한글로벌액티브리츠</t>
-  </si>
-  <si>
     <t>949.3:1</t>
   </si>
   <si>
@@ -329,9 +314,6 @@
     <t>598.87:1</t>
   </si>
   <si>
-    <t>38.7:1</t>
-  </si>
-  <si>
     <t>0.24%</t>
   </si>
   <si>
@@ -413,9 +395,6 @@
     <t>소형발사체, 로켓추진기관, 과학로켓, 시험평가용역</t>
   </si>
   <si>
-    <t>신탁 및 집합투자</t>
-  </si>
-  <si>
     <t>종목명</t>
   </si>
   <si>
@@ -434,12 +413,27 @@
     <t>주간사</t>
   </si>
   <si>
+    <t>쓰리빌리언</t>
+  </si>
+  <si>
     <t>신한스팩14호</t>
   </si>
   <si>
+    <t>탑런토탈솔루션</t>
+  </si>
+  <si>
+    <t>인스피언</t>
+  </si>
+  <si>
+    <t>한켐</t>
+  </si>
+  <si>
     <t>클로봇</t>
   </si>
   <si>
+    <t>토모큐브</t>
+  </si>
+  <si>
     <t>씨메스</t>
   </si>
   <si>
@@ -452,9 +446,6 @@
     <t>에이치이엠파마(구.에이치이엠)</t>
   </si>
   <si>
-    <t>한켐</t>
-  </si>
-  <si>
     <t>와이제이링크</t>
   </si>
   <si>
@@ -470,9 +461,6 @@
     <t>키움스팩9호</t>
   </si>
   <si>
-    <t>인스피언</t>
-  </si>
-  <si>
     <t>아이언디바이스</t>
   </si>
   <si>
@@ -485,15 +473,21 @@
     <t>대신밸런스스팩18호</t>
   </si>
   <si>
-    <t>엠83</t>
+    <t>2024.09.27~10.04</t>
   </si>
   <si>
     <t>2024.09.26~09.27</t>
   </si>
   <si>
+    <t>2024.09.24~09.30</t>
+  </si>
+  <si>
     <t>2024.09.23~09.27</t>
   </si>
   <si>
+    <t>2024.09.20~09.26</t>
+  </si>
+  <si>
     <t>2024.09.19~09.25</t>
   </si>
   <si>
@@ -512,9 +506,6 @@
     <t>2024.09.04~09.05</t>
   </si>
   <si>
-    <t>2024.09.04~09.10</t>
-  </si>
-  <si>
     <t>2024.08.30~09.05</t>
   </si>
   <si>
@@ -527,21 +518,27 @@
     <t>2024.08.05~08.06</t>
   </si>
   <si>
-    <t>2024.08.02~08.08</t>
-  </si>
-  <si>
-    <t>2024.08.01~08.07</t>
-  </si>
-  <si>
-    <t>2024.07.31~08.06</t>
+    <t>4,500~6,500</t>
   </si>
   <si>
     <t>2,000~2,000</t>
   </si>
   <si>
+    <t>12,000~14,000</t>
+  </si>
+  <si>
+    <t>8,000~10,000</t>
+  </si>
+  <si>
+    <t>12,500~14,500</t>
+  </si>
+  <si>
     <t>9,400~10,900</t>
   </si>
   <si>
+    <t>10,900~13,400</t>
+  </si>
+  <si>
     <t>20,000~24,000</t>
   </si>
   <si>
@@ -554,9 +551,6 @@
     <t>16,400~19,000</t>
   </si>
   <si>
-    <t>12,500~14,500</t>
-  </si>
-  <si>
     <t>8,600~9,800</t>
   </si>
   <si>
@@ -566,115 +560,91 @@
     <t>10,000~12,200</t>
   </si>
   <si>
-    <t>8,000~10,000</t>
-  </si>
-  <si>
     <t>4,900~5,700</t>
   </si>
   <si>
     <t>32,000~40,200</t>
   </si>
   <si>
-    <t>13,600~15,300</t>
-  </si>
-  <si>
-    <t>11,000~13,000</t>
-  </si>
-  <si>
-    <t>9,500~10,700</t>
+    <t>2000</t>
   </si>
   <si>
     <t>32000</t>
   </si>
   <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>15300</t>
-  </si>
-  <si>
-    <t>16000</t>
+    <t>10000</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>28200</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>49500</t>
+  </si>
+  <si>
+    <t>11430</t>
+  </si>
+  <si>
+    <t>30616</t>
+  </si>
+  <si>
+    <t>18480</t>
+  </si>
+  <si>
+    <t>6000</t>
+  </si>
+  <si>
+    <t>14700</t>
+  </si>
+  <si>
+    <t>15900</t>
+  </si>
+  <si>
+    <t>78720</t>
   </si>
   <si>
     <t>13000</t>
   </si>
   <si>
-    <t>10000</t>
-  </si>
-  <si>
-    <t>28200</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>49500</t>
-  </si>
-  <si>
-    <t>11430</t>
-  </si>
-  <si>
-    <t>30616</t>
-  </si>
-  <si>
-    <t>18480</t>
-  </si>
-  <si>
-    <t>6000</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>14700</t>
-  </si>
-  <si>
-    <t>78720</t>
-  </si>
-  <si>
-    <t>23972</t>
-  </si>
-  <si>
-    <t>24000</t>
+    <t>한국투자증권</t>
   </si>
   <si>
     <t>신한투자증권</t>
   </si>
   <si>
+    <t>KB증권</t>
+  </si>
+  <si>
+    <t>신영증권,유진증권</t>
+  </si>
+  <si>
     <t>미래에셋증권,신영증권</t>
   </si>
   <si>
+    <t>대신증권</t>
+  </si>
+  <si>
     <t>삼성증권,유진투자증권,유안타증권</t>
   </si>
   <si>
     <t>NH투자증권</t>
   </si>
   <si>
-    <t>대신증권</t>
-  </si>
-  <si>
-    <t>신영증권,유진증권</t>
-  </si>
-  <si>
-    <t>KB증권</t>
-  </si>
-  <si>
     <t>신영증권,케이비증권</t>
   </si>
   <si>
     <t>키움증권</t>
   </si>
   <si>
-    <t>한국투자증권</t>
-  </si>
-  <si>
     <t>미래에셋증권</t>
   </si>
   <si>
     <t>삼성증권</t>
-  </si>
-  <si>
-    <t>신영증권,유진투자증권</t>
   </si>
 </sst>
 </file>
@@ -1032,7 +1002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y18"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1117,16 +1087,16 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F2">
         <v>1566800</v>
@@ -1153,10 +1123,10 @@
         <v>15300</v>
       </c>
       <c r="N2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="O2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="P2">
         <v>7367362</v>
@@ -1186,7 +1156,7 @@
         <v>-2903334</v>
       </c>
       <c r="Y2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1194,16 +1164,16 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F3">
         <v>1000000</v>
@@ -1230,10 +1200,10 @@
         <v>13000</v>
       </c>
       <c r="N3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="O3" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="P3">
         <v>25588</v>
@@ -1263,7 +1233,7 @@
         <v>809</v>
       </c>
       <c r="Y3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1271,16 +1241,16 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F4">
         <v>6500000</v>
@@ -1307,10 +1277,10 @@
         <v>2000</v>
       </c>
       <c r="N4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="O4" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1340,7 +1310,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1351,13 +1321,13 @@
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F5">
         <v>1400000</v>
@@ -1384,10 +1354,10 @@
         <v>15500</v>
       </c>
       <c r="N5" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="O5" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="P5">
         <v>10740898602</v>
@@ -1417,7 +1387,7 @@
         <v>219774608</v>
       </c>
       <c r="Y5" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1428,13 +1398,13 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F6">
         <v>1000000</v>
@@ -1461,10 +1431,10 @@
         <v>29000</v>
       </c>
       <c r="N6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="O6" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1494,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1505,13 +1475,13 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F7">
         <v>751000</v>
@@ -1538,10 +1508,10 @@
         <v>21000</v>
       </c>
       <c r="N7" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="O7" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1571,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1582,13 +1552,13 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F8">
         <v>5800000</v>
@@ -1615,10 +1585,10 @@
         <v>2000</v>
       </c>
       <c r="N8" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="O8" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1648,7 +1618,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1659,13 +1629,13 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F9">
         <v>1400000</v>
@@ -1692,10 +1662,10 @@
         <v>16000</v>
       </c>
       <c r="N9" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="O9" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="P9">
         <v>72895458363</v>
@@ -1725,7 +1695,7 @@
         <v>-3801868433</v>
       </c>
       <c r="Y9" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1733,16 +1703,16 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F10">
         <v>2234000</v>
@@ -1769,10 +1739,10 @@
         <v>10000</v>
       </c>
       <c r="N10" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="O10" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="P10">
         <v>1337894447</v>
@@ -1802,7 +1772,7 @@
         <v>-1257080998</v>
       </c>
       <c r="Y10" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1810,16 +1780,16 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F11">
         <v>1350000</v>
@@ -1846,10 +1816,10 @@
         <v>22000</v>
       </c>
       <c r="N11" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="O11" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="P11">
         <v>5214628820</v>
@@ -1879,7 +1849,7 @@
         <v>24178632</v>
       </c>
       <c r="Y11" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1887,16 +1857,16 @@
         <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F12">
         <v>6000000</v>
@@ -1923,10 +1893,10 @@
         <v>2000</v>
       </c>
       <c r="N12" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="O12" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1956,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1964,16 +1934,16 @@
         <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E13" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F13">
         <v>4000000</v>
@@ -2000,10 +1970,10 @@
         <v>2000</v>
       </c>
       <c r="N13" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="O13" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -2033,7 +2003,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -2041,16 +2011,16 @@
         <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E14" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F14">
         <v>1618000</v>
@@ -2077,10 +2047,10 @@
         <v>10000</v>
       </c>
       <c r="N14" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O14" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -2110,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -2118,16 +2088,16 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F15">
         <v>4000000</v>
@@ -2154,11 +2124,11 @@
         <v>2000</v>
       </c>
       <c r="N15" t="s">
+        <v>96</v>
+      </c>
+      <c r="O15" t="s">
         <v>101</v>
       </c>
-      <c r="O15" t="s">
-        <v>107</v>
-      </c>
       <c r="P15">
         <v>0</v>
       </c>
@@ -2187,7 +2157,7 @@
         <v>0</v>
       </c>
       <c r="Y15" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -2195,16 +2165,16 @@
         <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F16">
         <v>1810000</v>
@@ -2231,10 +2201,10 @@
         <v>16000</v>
       </c>
       <c r="N16" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="O16" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="P16">
         <v>12596039842</v>
@@ -2264,7 +2234,7 @@
         <v>1795726428</v>
       </c>
       <c r="Y16" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2272,16 +2242,16 @@
         <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E17" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F17">
         <v>1330000</v>
@@ -2308,10 +2278,10 @@
         <v>43300</v>
       </c>
       <c r="N17" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="O17" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="P17">
         <v>103267682</v>
@@ -2341,84 +2311,7 @@
         <v>-83246975113</v>
       </c>
       <c r="Y17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25">
-      <c r="A18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" t="s">
-        <v>70</v>
-      </c>
-      <c r="E18" t="s">
-        <v>87</v>
-      </c>
-      <c r="F18">
-        <v>23333334</v>
-      </c>
-      <c r="G18">
-        <v>23333334</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>3000</v>
-      </c>
-      <c r="J18">
-        <v>3800</v>
-      </c>
-      <c r="K18">
-        <v>43477664</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>3000</v>
-      </c>
-      <c r="N18" t="s">
-        <v>104</v>
-      </c>
-      <c r="O18" t="s">
-        <v>107</v>
-      </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <v>0</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>0</v>
-      </c>
-      <c r="V18">
-        <v>0</v>
-      </c>
-      <c r="W18">
-        <v>0</v>
-      </c>
-      <c r="X18">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -2433,422 +2326,422 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C2" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
-        <v>194</v>
+        <v>101</v>
       </c>
       <c r="F2" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C3" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="F3" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B4" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C4" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E4" t="s">
-        <v>196</v>
+        <v>101</v>
       </c>
       <c r="F4" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C5" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E5" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="F5" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B6" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C6" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E6" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F6" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B7" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C7" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="F7" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="B8" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C8" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F8" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="B9" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C9" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="F9" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E10" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F10" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B11" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C11" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E11" t="s">
-        <v>200</v>
+        <v>101</v>
       </c>
       <c r="F11" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B12" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C12" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E12" t="s">
-        <v>107</v>
+        <v>190</v>
       </c>
       <c r="F12" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="B13" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C13" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E13" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="F13" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B14" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C14" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="D14" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E14" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="F14" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="B15" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C15" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D15" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E15" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="F15" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B16" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C16" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="D16" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E16" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F16" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B17" t="s">
+        <v>162</v>
+      </c>
+      <c r="C17" t="s">
         <v>168</v>
       </c>
-      <c r="C17" t="s">
-        <v>185</v>
-      </c>
       <c r="D17" t="s">
-        <v>189</v>
+        <v>101</v>
       </c>
       <c r="E17" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="F17" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="B18" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C18" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D18" t="s">
-        <v>190</v>
+        <v>101</v>
       </c>
       <c r="E18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F18" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>71</v>
+        <v>149</v>
       </c>
       <c r="B19" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C19" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="D19" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="E19" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="F19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B20" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C20" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D20" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="E20" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="F20" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>151</v>
       </c>
       <c r="B21" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C21" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="D21" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E21" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F21" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="203">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -128,9 +128,6 @@
     <t>2024-06-13</t>
   </si>
   <si>
-    <t>2024-06-11</t>
-  </si>
-  <si>
     <t>2024-08-08</t>
   </si>
   <si>
@@ -152,9 +149,6 @@
     <t>2024-06-19</t>
   </si>
   <si>
-    <t>2024-06-17</t>
-  </si>
-  <si>
     <t>2024-08-23</t>
   </si>
   <si>
@@ -185,9 +179,6 @@
     <t>2024-07-03</t>
   </si>
   <si>
-    <t>2024-07-02</t>
-  </si>
-  <si>
     <t>NH</t>
   </si>
   <si>
@@ -263,9 +254,6 @@
     <t>하스</t>
   </si>
   <si>
-    <t>이노스페이스</t>
-  </si>
-  <si>
     <t>949.3:1</t>
   </si>
   <si>
@@ -311,9 +299,6 @@
     <t>946.40:1</t>
   </si>
   <si>
-    <t>598.87:1</t>
-  </si>
-  <si>
     <t>0.24%</t>
   </si>
   <si>
@@ -347,9 +332,6 @@
     <t>6.36%</t>
   </si>
   <si>
-    <t>1.99%</t>
-  </si>
-  <si>
     <t>첨단바이오의약품 위탁개발생산(CDMO) 서비스 / 차세대 세포,유전자 치료제</t>
   </si>
   <si>
@@ -390,9 +372,6 @@
   </si>
   <si>
     <t>리튬디실리케이트 수복소재(Amber block, Amber Ingot 등), 지르코니아 유치관</t>
-  </si>
-  <si>
-    <t>소형발사체, 로켓추진기관, 과학로켓, 시험평가용역</t>
   </si>
   <si>
     <t>종목명</t>
@@ -1002,7 +981,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y17"/>
+  <dimension ref="A1:Y16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1087,16 +1066,16 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F2">
         <v>1566800</v>
@@ -1123,10 +1102,10 @@
         <v>15300</v>
       </c>
       <c r="N2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="P2">
         <v>7367362</v>
@@ -1156,7 +1135,7 @@
         <v>-2903334</v>
       </c>
       <c r="Y2" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1164,16 +1143,16 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F3">
         <v>1000000</v>
@@ -1200,10 +1179,10 @@
         <v>13000</v>
       </c>
       <c r="N3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="O3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P3">
         <v>25588</v>
@@ -1233,7 +1212,7 @@
         <v>809</v>
       </c>
       <c r="Y3" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1241,16 +1220,16 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F4">
         <v>6500000</v>
@@ -1277,10 +1256,10 @@
         <v>2000</v>
       </c>
       <c r="N4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1310,7 +1289,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1321,13 +1300,13 @@
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F5">
         <v>1400000</v>
@@ -1354,10 +1333,10 @@
         <v>15500</v>
       </c>
       <c r="N5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="O5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="P5">
         <v>10740898602</v>
@@ -1387,7 +1366,7 @@
         <v>219774608</v>
       </c>
       <c r="Y5" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1398,13 +1377,13 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F6">
         <v>1000000</v>
@@ -1431,10 +1410,10 @@
         <v>29000</v>
       </c>
       <c r="N6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="O6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1464,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1475,13 +1454,13 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F7">
         <v>751000</v>
@@ -1508,10 +1487,10 @@
         <v>21000</v>
       </c>
       <c r="N7" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="O7" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1541,7 +1520,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1552,13 +1531,13 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F8">
         <v>5800000</v>
@@ -1585,10 +1564,10 @@
         <v>2000</v>
       </c>
       <c r="N8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="O8" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1618,7 +1597,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1629,13 +1608,13 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F9">
         <v>1400000</v>
@@ -1662,10 +1641,10 @@
         <v>16000</v>
       </c>
       <c r="N9" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="O9" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="P9">
         <v>72895458363</v>
@@ -1695,7 +1674,7 @@
         <v>-3801868433</v>
       </c>
       <c r="Y9" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1703,16 +1682,16 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F10">
         <v>2234000</v>
@@ -1739,10 +1718,10 @@
         <v>10000</v>
       </c>
       <c r="N10" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="O10" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="P10">
         <v>1337894447</v>
@@ -1772,7 +1751,7 @@
         <v>-1257080998</v>
       </c>
       <c r="Y10" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1780,16 +1759,16 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F11">
         <v>1350000</v>
@@ -1816,10 +1795,10 @@
         <v>22000</v>
       </c>
       <c r="N11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O11" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="P11">
         <v>5214628820</v>
@@ -1849,7 +1828,7 @@
         <v>24178632</v>
       </c>
       <c r="Y11" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1857,16 +1836,16 @@
         <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F12">
         <v>6000000</v>
@@ -1893,10 +1872,10 @@
         <v>2000</v>
       </c>
       <c r="N12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="O12" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1926,7 +1905,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1934,16 +1913,16 @@
         <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E13" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F13">
         <v>4000000</v>
@@ -1970,10 +1949,10 @@
         <v>2000</v>
       </c>
       <c r="N13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="O13" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -2003,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -2011,16 +1990,16 @@
         <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F14">
         <v>1618000</v>
@@ -2047,10 +2026,10 @@
         <v>10000</v>
       </c>
       <c r="N14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="O14" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -2080,7 +2059,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -2088,16 +2067,16 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E15" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F15">
         <v>4000000</v>
@@ -2124,10 +2103,10 @@
         <v>2000</v>
       </c>
       <c r="N15" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="O15" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -2157,7 +2136,7 @@
         <v>0</v>
       </c>
       <c r="Y15" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -2165,16 +2144,16 @@
         <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E16" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F16">
         <v>1810000</v>
@@ -2201,10 +2180,10 @@
         <v>16000</v>
       </c>
       <c r="N16" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="O16" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="P16">
         <v>12596039842</v>
@@ -2234,84 +2213,7 @@
         <v>1795726428</v>
       </c>
       <c r="Y16" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25">
-      <c r="A17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" t="s">
-        <v>63</v>
-      </c>
-      <c r="E17" t="s">
-        <v>82</v>
-      </c>
-      <c r="F17">
-        <v>1330000</v>
-      </c>
-      <c r="G17">
-        <v>1330000</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>36400</v>
-      </c>
-      <c r="J17">
-        <v>43300</v>
-      </c>
-      <c r="K17">
-        <v>9375694</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>43300</v>
-      </c>
-      <c r="N17" t="s">
-        <v>98</v>
-      </c>
-      <c r="O17" t="s">
-        <v>110</v>
-      </c>
-      <c r="P17">
-        <v>103267682</v>
-      </c>
-      <c r="Q17">
-        <v>342201581</v>
-      </c>
-      <c r="R17">
-        <v>231425455</v>
-      </c>
-      <c r="S17">
-        <v>-7598692896</v>
-      </c>
-      <c r="T17">
-        <v>-25822444575</v>
-      </c>
-      <c r="U17">
-        <v>-15929213281</v>
-      </c>
-      <c r="V17">
-        <v>-6973258680</v>
-      </c>
-      <c r="W17">
-        <v>-48433907514</v>
-      </c>
-      <c r="X17">
-        <v>-83246975113</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -2326,422 +2228,422 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B2" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F2" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B3" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C3" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F3" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="B4" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C4" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F4" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B5" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C5" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="F5" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="B6" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C6" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F6" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B7" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C7" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E7" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F7" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="B8" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C8" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E8" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F8" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E9" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="F9" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B10" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C10" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E10" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="F10" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B11" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C11" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E11" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F11" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B12" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C12" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E12" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F12" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B13" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C13" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E13" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="F13" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B14" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C14" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D14" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E14" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F14" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="B15" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C15" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D15" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E15" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="F15" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="B16" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C16" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D16" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E16" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F16" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B17" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C17" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D17" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E17" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F17" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B18" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C18" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D18" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E18" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="F18" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B19" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C19" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D19" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="E19" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="F19" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="B20" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C20" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="D20" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="E20" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="F20" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B21" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C21" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D21" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="E21" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="F21" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="196">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -125,9 +125,6 @@
     <t>2024-06-27</t>
   </si>
   <si>
-    <t>2024-06-13</t>
-  </si>
-  <si>
     <t>2024-08-08</t>
   </si>
   <si>
@@ -146,9 +143,6 @@
     <t>2024-06-28</t>
   </si>
   <si>
-    <t>2024-06-19</t>
-  </si>
-  <si>
     <t>2024-08-23</t>
   </si>
   <si>
@@ -176,9 +170,6 @@
     <t>2024-07-12</t>
   </si>
   <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
     <t>NH</t>
   </si>
   <si>
@@ -251,9 +242,6 @@
     <t>이베스트스팩6호</t>
   </si>
   <si>
-    <t>하스</t>
-  </si>
-  <si>
     <t>949.3:1</t>
   </si>
   <si>
@@ -296,9 +284,6 @@
     <t>1131.75:1</t>
   </si>
   <si>
-    <t>946.40:1</t>
-  </si>
-  <si>
     <t>0.24%</t>
   </si>
   <si>
@@ -329,9 +314,6 @@
     <t>4.50%</t>
   </si>
   <si>
-    <t>6.36%</t>
-  </si>
-  <si>
     <t>첨단바이오의약품 위탁개발생산(CDMO) 서비스 / 차세대 세포,유전자 치료제</t>
   </si>
   <si>
@@ -369,9 +351,6 @@
   </si>
   <si>
     <t>CellCor SFD/CD(세포배양배지)</t>
-  </si>
-  <si>
-    <t>리튬디실리케이트 수복소재(Amber block, Amber Ingot 등), 지르코니아 유치관</t>
   </si>
   <si>
     <t>종목명</t>
@@ -981,7 +960,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y16"/>
+  <dimension ref="A1:Y15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1066,16 +1045,16 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F2">
         <v>1566800</v>
@@ -1102,10 +1081,10 @@
         <v>15300</v>
       </c>
       <c r="N2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="O2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="P2">
         <v>7367362</v>
@@ -1135,7 +1114,7 @@
         <v>-2903334</v>
       </c>
       <c r="Y2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1143,16 +1122,16 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F3">
         <v>1000000</v>
@@ -1179,10 +1158,10 @@
         <v>13000</v>
       </c>
       <c r="N3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="O3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="P3">
         <v>25588</v>
@@ -1212,7 +1191,7 @@
         <v>809</v>
       </c>
       <c r="Y3" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1220,16 +1199,16 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F4">
         <v>6500000</v>
@@ -1256,10 +1235,10 @@
         <v>2000</v>
       </c>
       <c r="N4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="O4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1289,7 +1268,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1300,13 +1279,13 @@
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F5">
         <v>1400000</v>
@@ -1333,10 +1312,10 @@
         <v>15500</v>
       </c>
       <c r="N5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="O5" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="P5">
         <v>10740898602</v>
@@ -1366,7 +1345,7 @@
         <v>219774608</v>
       </c>
       <c r="Y5" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1377,13 +1356,13 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F6">
         <v>1000000</v>
@@ -1410,10 +1389,10 @@
         <v>29000</v>
       </c>
       <c r="N6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O6" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1443,7 +1422,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1454,13 +1433,13 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F7">
         <v>751000</v>
@@ -1487,10 +1466,10 @@
         <v>21000</v>
       </c>
       <c r="N7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="O7" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1520,7 +1499,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1531,13 +1510,13 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F8">
         <v>5800000</v>
@@ -1564,10 +1543,10 @@
         <v>2000</v>
       </c>
       <c r="N8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O8" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1597,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1608,13 +1587,13 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F9">
         <v>1400000</v>
@@ -1641,10 +1620,10 @@
         <v>16000</v>
       </c>
       <c r="N9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="O9" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P9">
         <v>72895458363</v>
@@ -1674,7 +1653,7 @@
         <v>-3801868433</v>
       </c>
       <c r="Y9" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1682,16 +1661,16 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F10">
         <v>2234000</v>
@@ -1718,10 +1697,10 @@
         <v>10000</v>
       </c>
       <c r="N10" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="O10" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="P10">
         <v>1337894447</v>
@@ -1751,7 +1730,7 @@
         <v>-1257080998</v>
       </c>
       <c r="Y10" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1759,16 +1738,16 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F11">
         <v>1350000</v>
@@ -1795,10 +1774,10 @@
         <v>22000</v>
       </c>
       <c r="N11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="O11" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="P11">
         <v>5214628820</v>
@@ -1828,7 +1807,7 @@
         <v>24178632</v>
       </c>
       <c r="Y11" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1836,16 +1815,16 @@
         <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="s">
         <v>51</v>
       </c>
-      <c r="D12" t="s">
-        <v>54</v>
-      </c>
       <c r="E12" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F12">
         <v>6000000</v>
@@ -1872,10 +1851,10 @@
         <v>2000</v>
       </c>
       <c r="N12" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="O12" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1905,7 +1884,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1913,16 +1892,16 @@
         <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F13">
         <v>4000000</v>
@@ -1949,10 +1928,10 @@
         <v>2000</v>
       </c>
       <c r="N13" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="O13" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -1982,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1990,16 +1969,16 @@
         <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F14">
         <v>1618000</v>
@@ -2026,10 +2005,10 @@
         <v>10000</v>
       </c>
       <c r="N14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="O14" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -2059,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -2067,16 +2046,16 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F15">
         <v>4000000</v>
@@ -2103,10 +2082,10 @@
         <v>2000</v>
       </c>
       <c r="N15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O15" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -2136,84 +2115,7 @@
         <v>0</v>
       </c>
       <c r="Y15" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25">
-      <c r="A16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16" t="s">
-        <v>78</v>
-      </c>
-      <c r="F16">
-        <v>1810000</v>
-      </c>
-      <c r="G16">
-        <v>1810000</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>9000</v>
-      </c>
-      <c r="J16">
-        <v>12000</v>
-      </c>
-      <c r="K16">
-        <v>7836009</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>16000</v>
-      </c>
-      <c r="N16" t="s">
-        <v>93</v>
-      </c>
-      <c r="O16" t="s">
-        <v>104</v>
-      </c>
-      <c r="P16">
-        <v>12596039842</v>
-      </c>
-      <c r="Q16">
-        <v>14910346438</v>
-      </c>
-      <c r="R16">
-        <v>16039074617</v>
-      </c>
-      <c r="S16">
-        <v>1732604466</v>
-      </c>
-      <c r="T16">
-        <v>2893667787</v>
-      </c>
-      <c r="U16">
-        <v>1613779678</v>
-      </c>
-      <c r="V16">
-        <v>1558081149</v>
-      </c>
-      <c r="W16">
-        <v>2643467726</v>
-      </c>
-      <c r="X16">
-        <v>1795726428</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -2228,422 +2130,422 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C2" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F2" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="B3" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C3" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F3" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C4" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B5" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C5" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="B6" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C6" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F6" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B7" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C7" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E7" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="F7" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C8" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E8" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F8" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B9" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C9" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="F9" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B10" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C10" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="F10" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="B11" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C11" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E11" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F11" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B12" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C12" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E12" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F12" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="B13" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C13" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E13" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F13" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B14" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C14" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E14" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F14" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C15" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E15" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F15" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C16" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="D16" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E16" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F16" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B17" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C17" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D17" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E17" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="F17" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C18" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D18" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E18" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F18" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B19" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C19" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D19" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E19" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="F19" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B20" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C20" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D20" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="E20" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="F20" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B21" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C21" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D21" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E21" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F21" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="197">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -377,6 +377,9 @@
     <t>신한스팩14호</t>
   </si>
   <si>
+    <t>와이제이링크</t>
+  </si>
+  <si>
     <t>탑런토탈솔루션</t>
   </si>
   <si>
@@ -404,9 +407,6 @@
     <t>에이치이엠파마(구.에이치이엠)</t>
   </si>
   <si>
-    <t>와이제이링크</t>
-  </si>
-  <si>
     <t>KB스팩30호</t>
   </si>
   <si>
@@ -437,6 +437,9 @@
     <t>2024.09.26~09.27</t>
   </si>
   <si>
+    <t>2024.09.25~10.02</t>
+  </si>
+  <si>
     <t>2024.09.24~09.30</t>
   </si>
   <si>
@@ -482,6 +485,9 @@
     <t>2,000~2,000</t>
   </si>
   <si>
+    <t>8,600~9,800</t>
+  </si>
+  <si>
     <t>12,000~14,000</t>
   </si>
   <si>
@@ -509,9 +515,6 @@
     <t>16,400~19,000</t>
   </si>
   <si>
-    <t>8,600~9,800</t>
-  </si>
-  <si>
     <t>28,000~34,000</t>
   </si>
   <si>
@@ -533,6 +536,9 @@
     <t>10000</t>
   </si>
   <si>
+    <t>30616</t>
+  </si>
+  <si>
     <t>18000</t>
   </si>
   <si>
@@ -546,9 +552,6 @@
   </si>
   <si>
     <t>11430</t>
-  </si>
-  <si>
-    <t>30616</t>
   </si>
   <si>
     <t>18480</t>
@@ -2156,7 +2159,7 @@
         <v>138</v>
       </c>
       <c r="C2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D2" t="s">
         <v>91</v>
@@ -2165,7 +2168,7 @@
         <v>91</v>
       </c>
       <c r="F2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2176,16 +2179,16 @@
         <v>139</v>
       </c>
       <c r="C3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D3" t="s">
         <v>91</v>
       </c>
       <c r="E3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2196,16 +2199,16 @@
         <v>140</v>
       </c>
       <c r="C4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D4" t="s">
         <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>91</v>
+        <v>173</v>
       </c>
       <c r="F4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2216,16 +2219,16 @@
         <v>141</v>
       </c>
       <c r="C5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D5" t="s">
         <v>91</v>
       </c>
       <c r="E5" t="s">
-        <v>172</v>
+        <v>91</v>
       </c>
       <c r="F5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2233,19 +2236,19 @@
         <v>122</v>
       </c>
       <c r="B6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D6" t="s">
         <v>91</v>
       </c>
       <c r="E6" t="s">
-        <v>91</v>
+        <v>174</v>
       </c>
       <c r="F6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2253,16 +2256,16 @@
         <v>123</v>
       </c>
       <c r="B7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D7" t="s">
         <v>91</v>
       </c>
       <c r="E7" t="s">
-        <v>173</v>
+        <v>91</v>
       </c>
       <c r="F7" t="s">
         <v>188</v>
@@ -2276,13 +2279,13 @@
         <v>142</v>
       </c>
       <c r="C8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D8" t="s">
         <v>91</v>
       </c>
       <c r="E8" t="s">
-        <v>91</v>
+        <v>175</v>
       </c>
       <c r="F8" t="s">
         <v>189</v>
@@ -2296,13 +2299,13 @@
         <v>143</v>
       </c>
       <c r="C9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D9" t="s">
         <v>91</v>
       </c>
       <c r="E9" t="s">
-        <v>174</v>
+        <v>91</v>
       </c>
       <c r="F9" t="s">
         <v>190</v>
@@ -2316,13 +2319,13 @@
         <v>144</v>
       </c>
       <c r="C10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D10" t="s">
         <v>91</v>
       </c>
       <c r="E10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F10" t="s">
         <v>191</v>
@@ -2333,19 +2336,19 @@
         <v>127</v>
       </c>
       <c r="B11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D11" t="s">
         <v>91</v>
       </c>
       <c r="E11" t="s">
-        <v>91</v>
+        <v>177</v>
       </c>
       <c r="F11" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2356,16 +2359,16 @@
         <v>145</v>
       </c>
       <c r="C12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D12" t="s">
         <v>91</v>
       </c>
       <c r="E12" t="s">
-        <v>176</v>
+        <v>91</v>
       </c>
       <c r="F12" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2373,16 +2376,16 @@
         <v>129</v>
       </c>
       <c r="B13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D13" t="s">
         <v>91</v>
       </c>
       <c r="E13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F13" t="s">
         <v>186</v>
@@ -2393,19 +2396,19 @@
         <v>130</v>
       </c>
       <c r="B14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D14" t="s">
         <v>91</v>
       </c>
       <c r="E14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2413,19 +2416,19 @@
         <v>131</v>
       </c>
       <c r="B15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D15" t="s">
         <v>91</v>
       </c>
       <c r="E15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F15" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2433,10 +2436,10 @@
         <v>132</v>
       </c>
       <c r="B16" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D16" t="s">
         <v>91</v>
@@ -2445,7 +2448,7 @@
         <v>91</v>
       </c>
       <c r="F16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2453,19 +2456,19 @@
         <v>133</v>
       </c>
       <c r="B17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D17" t="s">
         <v>91</v>
       </c>
       <c r="E17" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -2473,19 +2476,19 @@
         <v>134</v>
       </c>
       <c r="B18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C18" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D18" t="s">
         <v>91</v>
       </c>
       <c r="E18" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F18" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2493,19 +2496,19 @@
         <v>135</v>
       </c>
       <c r="B19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E19" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F19" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -2513,19 +2516,19 @@
         <v>136</v>
       </c>
       <c r="B20" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C20" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D20" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E20" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F20" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -2533,19 +2536,19 @@
         <v>137</v>
       </c>
       <c r="B21" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C21" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E21" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F21" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="198">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -374,12 +374,18 @@
     <t>쓰리빌리언</t>
   </si>
   <si>
+    <t>루미르</t>
+  </si>
+  <si>
     <t>신한스팩14호</t>
   </si>
   <si>
     <t>와이제이링크</t>
   </si>
   <si>
+    <t>셀비온</t>
+  </si>
+  <si>
     <t>탑런토탈솔루션</t>
   </si>
   <si>
@@ -398,9 +404,6 @@
     <t>씨메스</t>
   </si>
   <si>
-    <t>루미르</t>
-  </si>
-  <si>
     <t>웨이비스</t>
   </si>
   <si>
@@ -413,9 +416,6 @@
     <t>제닉스</t>
   </si>
   <si>
-    <t>셀비온</t>
-  </si>
-  <si>
     <t>키움스팩9호</t>
   </si>
   <si>
@@ -434,6 +434,9 @@
     <t>2024.09.27~10.04</t>
   </si>
   <si>
+    <t>2024.09.26~10.04</t>
+  </si>
+  <si>
     <t>2024.09.26~09.27</t>
   </si>
   <si>
@@ -482,12 +485,18 @@
     <t>4,500~6,500</t>
   </si>
   <si>
+    <t>16,500~20,500</t>
+  </si>
+  <si>
     <t>2,000~2,000</t>
   </si>
   <si>
     <t>8,600~9,800</t>
   </si>
   <si>
+    <t>10,000~12,200</t>
+  </si>
+  <si>
     <t>12,000~14,000</t>
   </si>
   <si>
@@ -506,9 +515,6 @@
     <t>20,000~24,000</t>
   </si>
   <si>
-    <t>16,500~20,500</t>
-  </si>
-  <si>
     <t>11,000~12,500</t>
   </si>
   <si>
@@ -518,9 +524,6 @@
     <t>28,000~34,000</t>
   </si>
   <si>
-    <t>10,000~12,200</t>
-  </si>
-  <si>
     <t>4,900~5,700</t>
   </si>
   <si>
@@ -533,6 +536,9 @@
     <t>32000</t>
   </si>
   <si>
+    <t>49500</t>
+  </si>
+  <si>
     <t>10000</t>
   </si>
   <si>
@@ -548,9 +554,6 @@
     <t>52000</t>
   </si>
   <si>
-    <t>49500</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -575,28 +578,28 @@
     <t>한국투자증권</t>
   </si>
   <si>
+    <t>NH투자증권</t>
+  </si>
+  <si>
     <t>신한투자증권</t>
   </si>
   <si>
     <t>KB증권</t>
   </si>
   <si>
+    <t>대신증권</t>
+  </si>
+  <si>
     <t>신영증권,유진증권</t>
   </si>
   <si>
     <t>미래에셋증권,신영증권</t>
   </si>
   <si>
-    <t>대신증권</t>
-  </si>
-  <si>
     <t>삼성증권,유진투자증권,유안타증권</t>
   </si>
   <si>
-    <t>NH투자증권</t>
-  </si>
-  <si>
-    <t>신영증권,케이비증권</t>
+    <t>신영증권,KB증권</t>
   </si>
   <si>
     <t>키움증권</t>
@@ -2159,7 +2162,7 @@
         <v>138</v>
       </c>
       <c r="C2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D2" t="s">
         <v>91</v>
@@ -2168,7 +2171,7 @@
         <v>91</v>
       </c>
       <c r="F2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2179,16 +2182,16 @@
         <v>139</v>
       </c>
       <c r="C3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D3" t="s">
         <v>91</v>
       </c>
       <c r="E3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2199,16 +2202,16 @@
         <v>140</v>
       </c>
       <c r="C4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D4" t="s">
         <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2219,16 +2222,16 @@
         <v>141</v>
       </c>
       <c r="C5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D5" t="s">
         <v>91</v>
       </c>
       <c r="E5" t="s">
-        <v>91</v>
+        <v>175</v>
       </c>
       <c r="F5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2239,16 +2242,16 @@
         <v>142</v>
       </c>
       <c r="C6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D6" t="s">
         <v>91</v>
       </c>
       <c r="E6" t="s">
-        <v>174</v>
+        <v>91</v>
       </c>
       <c r="F6" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2259,7 +2262,7 @@
         <v>142</v>
       </c>
       <c r="C7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D7" t="s">
         <v>91</v>
@@ -2268,7 +2271,7 @@
         <v>91</v>
       </c>
       <c r="F7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2276,19 +2279,19 @@
         <v>124</v>
       </c>
       <c r="B8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D8" t="s">
         <v>91</v>
       </c>
       <c r="E8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F8" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2299,7 +2302,7 @@
         <v>143</v>
       </c>
       <c r="C9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D9" t="s">
         <v>91</v>
@@ -2308,7 +2311,7 @@
         <v>91</v>
       </c>
       <c r="F9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2316,19 +2319,19 @@
         <v>126</v>
       </c>
       <c r="B10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D10" t="s">
         <v>91</v>
       </c>
       <c r="E10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2336,19 +2339,19 @@
         <v>127</v>
       </c>
       <c r="B11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C11" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D11" t="s">
         <v>91</v>
       </c>
       <c r="E11" t="s">
-        <v>177</v>
+        <v>91</v>
       </c>
       <c r="F11" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2359,16 +2362,16 @@
         <v>145</v>
       </c>
       <c r="C12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D12" t="s">
         <v>91</v>
       </c>
       <c r="E12" t="s">
-        <v>91</v>
+        <v>178</v>
       </c>
       <c r="F12" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2379,16 +2382,16 @@
         <v>146</v>
       </c>
       <c r="C13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D13" t="s">
         <v>91</v>
       </c>
       <c r="E13" t="s">
-        <v>178</v>
+        <v>91</v>
       </c>
       <c r="F13" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2399,16 +2402,16 @@
         <v>147</v>
       </c>
       <c r="C14" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="D14" t="s">
         <v>91</v>
       </c>
       <c r="E14" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="F14" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2419,16 +2422,16 @@
         <v>148</v>
       </c>
       <c r="C15" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="D15" t="s">
         <v>91</v>
       </c>
       <c r="E15" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F15" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2436,19 +2439,19 @@
         <v>132</v>
       </c>
       <c r="B16" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C16" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D16" t="s">
         <v>91</v>
       </c>
       <c r="E16" t="s">
-        <v>91</v>
+        <v>180</v>
       </c>
       <c r="F16" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2456,19 +2459,19 @@
         <v>133</v>
       </c>
       <c r="B17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C17" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D17" t="s">
         <v>91</v>
       </c>
       <c r="E17" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F17" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -2476,16 +2479,16 @@
         <v>134</v>
       </c>
       <c r="B18" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C18" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D18" t="s">
         <v>91</v>
       </c>
       <c r="E18" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F18" t="s">
         <v>190</v>
@@ -2496,19 +2499,19 @@
         <v>135</v>
       </c>
       <c r="B19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C19" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E19" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F19" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -2516,19 +2519,19 @@
         <v>136</v>
       </c>
       <c r="B20" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E20" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -2536,16 +2539,16 @@
         <v>137</v>
       </c>
       <c r="B21" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C21" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D21" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E21" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F21" t="s">
         <v>190</v>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="200">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -371,6 +371,9 @@
     <t>주간사</t>
   </si>
   <si>
+    <t>더본코리아(유가)</t>
+  </si>
+  <si>
     <t>쓰리빌리언</t>
   </si>
   <si>
@@ -428,7 +431,7 @@
     <t>아이스크림미디어(구.시공미디어)</t>
   </si>
   <si>
-    <t>대신밸런스스팩18호</t>
+    <t>2024.10.15~10.21</t>
   </si>
   <si>
     <t>2024.09.27~10.04</t>
@@ -479,7 +482,7 @@
     <t>2024.08.09~08.16</t>
   </si>
   <si>
-    <t>2024.08.05~08.06</t>
+    <t>23,000~28,000</t>
   </si>
   <si>
     <t>4,500~6,500</t>
@@ -536,6 +539,9 @@
     <t>32000</t>
   </si>
   <si>
+    <t>69000</t>
+  </si>
+  <si>
     <t>49500</t>
   </si>
   <si>
@@ -572,7 +578,7 @@
     <t>78720</t>
   </si>
   <si>
-    <t>13000</t>
+    <t>한국투자증권,NH투자증권</t>
   </si>
   <si>
     <t>한국투자증권</t>
@@ -2168,10 +2174,10 @@
         <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>91</v>
+        <v>174</v>
       </c>
       <c r="F2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2188,10 +2194,10 @@
         <v>91</v>
       </c>
       <c r="E3" t="s">
-        <v>173</v>
+        <v>91</v>
       </c>
       <c r="F3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2208,10 +2214,10 @@
         <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2228,10 +2234,10 @@
         <v>91</v>
       </c>
       <c r="E5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2248,10 +2254,10 @@
         <v>91</v>
       </c>
       <c r="E6" t="s">
-        <v>91</v>
+        <v>177</v>
       </c>
       <c r="F6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2259,7 +2265,7 @@
         <v>123</v>
       </c>
       <c r="B7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C7" t="s">
         <v>160</v>
@@ -2271,7 +2277,7 @@
         <v>91</v>
       </c>
       <c r="F7" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2288,10 +2294,10 @@
         <v>91</v>
       </c>
       <c r="E8" t="s">
-        <v>176</v>
+        <v>91</v>
       </c>
       <c r="F8" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2299,7 +2305,7 @@
         <v>125</v>
       </c>
       <c r="B9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C9" t="s">
         <v>162</v>
@@ -2308,10 +2314,10 @@
         <v>91</v>
       </c>
       <c r="E9" t="s">
-        <v>91</v>
+        <v>178</v>
       </c>
       <c r="F9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2319,7 +2325,7 @@
         <v>126</v>
       </c>
       <c r="B10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C10" t="s">
         <v>163</v>
@@ -2328,10 +2334,10 @@
         <v>91</v>
       </c>
       <c r="E10" t="s">
-        <v>177</v>
+        <v>91</v>
       </c>
       <c r="F10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2348,10 +2354,10 @@
         <v>91</v>
       </c>
       <c r="E11" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="F11" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2368,10 +2374,10 @@
         <v>91</v>
       </c>
       <c r="E12" t="s">
-        <v>178</v>
+        <v>91</v>
       </c>
       <c r="F12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2388,10 +2394,10 @@
         <v>91</v>
       </c>
       <c r="E13" t="s">
-        <v>91</v>
+        <v>180</v>
       </c>
       <c r="F13" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2408,10 +2414,10 @@
         <v>91</v>
       </c>
       <c r="E14" t="s">
-        <v>179</v>
+        <v>91</v>
       </c>
       <c r="F14" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2422,16 +2428,16 @@
         <v>148</v>
       </c>
       <c r="C15" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="D15" t="s">
         <v>91</v>
       </c>
       <c r="E15" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="F15" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2442,16 +2448,16 @@
         <v>149</v>
       </c>
       <c r="C16" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D16" t="s">
         <v>91</v>
       </c>
       <c r="E16" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F16" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2462,16 +2468,16 @@
         <v>150</v>
       </c>
       <c r="C17" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="D17" t="s">
         <v>91</v>
       </c>
       <c r="E17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F17" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -2482,16 +2488,16 @@
         <v>151</v>
       </c>
       <c r="C18" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="D18" t="s">
         <v>91</v>
       </c>
       <c r="E18" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F18" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2502,16 +2508,16 @@
         <v>152</v>
       </c>
       <c r="C19" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="D19" t="s">
-        <v>171</v>
+        <v>91</v>
       </c>
       <c r="E19" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F19" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -2522,16 +2528,16 @@
         <v>153</v>
       </c>
       <c r="C20" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="D20" t="s">
         <v>172</v>
       </c>
       <c r="E20" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F20" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -2542,16 +2548,16 @@
         <v>154</v>
       </c>
       <c r="C21" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="D21" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E21" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F21" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -419,9 +419,6 @@
     <t>제닉스</t>
   </si>
   <si>
-    <t>키움스팩9호</t>
-  </si>
-  <si>
     <t>아이언디바이스</t>
   </si>
   <si>
@@ -431,6 +428,9 @@
     <t>아이스크림미디어(구.시공미디어)</t>
   </si>
   <si>
+    <t>대신밸런스스팩18호</t>
+  </si>
+  <si>
     <t>2024.10.15~10.21</t>
   </si>
   <si>
@@ -470,9 +470,6 @@
     <t>2024.09.05~09.11</t>
   </si>
   <si>
-    <t>2024.09.04~09.05</t>
-  </si>
-  <si>
     <t>2024.08.30~09.05</t>
   </si>
   <si>
@@ -482,6 +479,9 @@
     <t>2024.08.09~08.16</t>
   </si>
   <si>
+    <t>2024.08.05~08.06</t>
+  </si>
+  <si>
     <t>23,000~28,000</t>
   </si>
   <si>
@@ -536,6 +536,9 @@
     <t>2000</t>
   </si>
   <si>
+    <t>7000</t>
+  </si>
+  <si>
     <t>32000</t>
   </si>
   <si>
@@ -566,10 +569,7 @@
     <t>18480</t>
   </si>
   <si>
-    <t>6000</t>
-  </si>
-  <si>
-    <t>14700</t>
+    <t>21000</t>
   </si>
   <si>
     <t>15900</t>
@@ -578,6 +578,9 @@
     <t>78720</t>
   </si>
   <si>
+    <t>13000</t>
+  </si>
+  <si>
     <t>한국투자증권,NH투자증권</t>
   </si>
   <si>
@@ -606,9 +609,6 @@
   </si>
   <si>
     <t>신영증권,KB증권</t>
-  </si>
-  <si>
-    <t>키움증권</t>
   </si>
   <si>
     <t>미래에셋증권</t>
@@ -2174,10 +2174,10 @@
         <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2197,7 +2197,7 @@
         <v>91</v>
       </c>
       <c r="F3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2214,10 +2214,10 @@
         <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2234,10 +2234,10 @@
         <v>91</v>
       </c>
       <c r="E5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2254,10 +2254,10 @@
         <v>91</v>
       </c>
       <c r="E6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2277,7 +2277,7 @@
         <v>91</v>
       </c>
       <c r="F7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2297,7 +2297,7 @@
         <v>91</v>
       </c>
       <c r="F8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2314,10 +2314,10 @@
         <v>91</v>
       </c>
       <c r="E9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2337,7 +2337,7 @@
         <v>91</v>
       </c>
       <c r="F10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2354,10 +2354,10 @@
         <v>91</v>
       </c>
       <c r="E11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F11" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2377,7 +2377,7 @@
         <v>91</v>
       </c>
       <c r="F12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2394,10 +2394,10 @@
         <v>91</v>
       </c>
       <c r="E13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2417,7 +2417,7 @@
         <v>91</v>
       </c>
       <c r="F14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2434,10 +2434,10 @@
         <v>91</v>
       </c>
       <c r="E15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F15" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2451,13 +2451,13 @@
         <v>158</v>
       </c>
       <c r="D16" t="s">
-        <v>91</v>
+        <v>172</v>
       </c>
       <c r="E16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2474,10 +2474,10 @@
         <v>91</v>
       </c>
       <c r="E17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -2488,16 +2488,16 @@
         <v>151</v>
       </c>
       <c r="C18" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>173</v>
       </c>
       <c r="E18" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F18" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2508,16 +2508,16 @@
         <v>152</v>
       </c>
       <c r="C19" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="D19" t="s">
-        <v>91</v>
+        <v>172</v>
       </c>
       <c r="E19" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F19" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -2528,16 +2528,16 @@
         <v>153</v>
       </c>
       <c r="C20" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="D20" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E20" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F20" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -2548,16 +2548,16 @@
         <v>154</v>
       </c>
       <c r="C21" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="D21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E21" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F21" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="199">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -92,6 +92,9 @@
     <t>주요제품</t>
   </si>
   <si>
+    <t>2024-08-26</t>
+  </si>
+  <si>
     <t>2024-08-02</t>
   </si>
   <si>
@@ -122,7 +125,7 @@
     <t>2024-06-24</t>
   </si>
   <si>
-    <t>2024-06-27</t>
+    <t>2024-08-27</t>
   </si>
   <si>
     <t>2024-08-08</t>
@@ -143,6 +146,9 @@
     <t>2024-06-28</t>
   </si>
   <si>
+    <t>2024-09-11</t>
+  </si>
+  <si>
     <t>2024-08-23</t>
   </si>
   <si>
@@ -167,7 +173,7 @@
     <t>2024-07-26</t>
   </si>
   <si>
-    <t>2024-07-12</t>
+    <t>미래</t>
   </si>
   <si>
     <t>NH</t>
@@ -188,16 +194,13 @@
     <t>교보</t>
   </si>
   <si>
-    <t>미래</t>
-  </si>
-  <si>
     <t>삼성</t>
   </si>
   <si>
     <t>SK</t>
   </si>
   <si>
-    <t>엘에스</t>
+    <t>미래에셋비전스팩7호</t>
   </si>
   <si>
     <t>이엔셀</t>
@@ -239,7 +242,7 @@
     <t>엑셀세라퓨틱스</t>
   </si>
   <si>
-    <t>이베스트스팩6호</t>
+    <t>1051.62 :1</t>
   </si>
   <si>
     <t>949.3:1</t>
@@ -281,7 +284,7 @@
     <t>1233.80:1</t>
   </si>
   <si>
-    <t>1131.75:1</t>
+    <t>-</t>
   </si>
   <si>
     <t>0.24%</t>
@@ -290,9 +293,6 @@
     <t>4.23%</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>1.03%</t>
   </si>
   <si>
@@ -314,6 +314,9 @@
     <t>4.50%</t>
   </si>
   <si>
+    <t>기업인수합병</t>
+  </si>
+  <si>
     <t>첨단바이오의약품 위탁개발생산(CDMO) 서비스 / 차세대 세포,유전자 치료제</t>
   </si>
   <si>
@@ -332,9 +335,6 @@
     <t>모바일 앱 개발 플랫폼</t>
   </si>
   <si>
-    <t>기업인수합병</t>
-  </si>
-  <si>
     <t>국내외 은행 및 금융기업 대상 코어뱅킹 소프트웨어</t>
   </si>
   <si>
@@ -374,6 +374,9 @@
     <t>더본코리아(유가)</t>
   </si>
   <si>
+    <t>씨메스</t>
+  </si>
+  <si>
     <t>쓰리빌리언</t>
   </si>
   <si>
@@ -404,9 +407,6 @@
     <t>토모큐브</t>
   </si>
   <si>
-    <t>씨메스</t>
-  </si>
-  <si>
     <t>웨이비스</t>
   </si>
   <si>
@@ -422,9 +422,6 @@
     <t>아이언디바이스</t>
   </si>
   <si>
-    <t>미래에셋비전스팩7호</t>
-  </si>
-  <si>
     <t>아이스크림미디어(구.시공미디어)</t>
   </si>
   <si>
@@ -434,6 +431,9 @@
     <t>2024.10.15~10.21</t>
   </si>
   <si>
+    <t>2024.09.30~10.08</t>
+  </si>
+  <si>
     <t>2024.09.27~10.04</t>
   </si>
   <si>
@@ -455,9 +455,6 @@
     <t>2024.09.20~09.26</t>
   </si>
   <si>
-    <t>2024.09.19~09.25</t>
-  </si>
-  <si>
     <t>2024.09.09~09.13</t>
   </si>
   <si>
@@ -485,6 +482,9 @@
     <t>23,000~28,000</t>
   </si>
   <si>
+    <t>20,000~24,000</t>
+  </si>
+  <si>
     <t>4,500~6,500</t>
   </si>
   <si>
@@ -515,9 +515,6 @@
     <t>10,900~13,400</t>
   </si>
   <si>
-    <t>20,000~24,000</t>
-  </si>
-  <si>
     <t>11,000~12,500</t>
   </si>
   <si>
@@ -545,6 +542,9 @@
     <t>69000</t>
   </si>
   <si>
+    <t>52000</t>
+  </si>
+  <si>
     <t>49500</t>
   </si>
   <si>
@@ -560,9 +560,6 @@
     <t>28200</t>
   </si>
   <si>
-    <t>52000</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -584,6 +581,9 @@
     <t>한국투자증권,NH투자증권</t>
   </si>
   <si>
+    <t>삼성증권,유진투자증권,유안타증권</t>
+  </si>
+  <si>
     <t>한국투자증권</t>
   </si>
   <si>
@@ -603,9 +603,6 @@
   </si>
   <si>
     <t>미래에셋증권,신영증권</t>
-  </si>
-  <si>
-    <t>삼성증권,유진투자증권,유안타증권</t>
   </si>
   <si>
     <t>신영증권,KB증권</t>
@@ -1060,37 +1057,37 @@
         <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
         <v>61</v>
       </c>
       <c r="F2">
-        <v>1566800</v>
+        <v>7950000</v>
       </c>
       <c r="G2">
-        <v>1566800</v>
+        <v>7950000</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>13600</v>
+        <v>2000</v>
       </c>
       <c r="J2">
-        <v>15300</v>
+        <v>2000</v>
       </c>
       <c r="K2">
-        <v>9349954</v>
+        <v>8215000</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>15300</v>
+        <v>2000</v>
       </c>
       <c r="N2" t="s">
         <v>75</v>
@@ -1099,31 +1096,31 @@
         <v>89</v>
       </c>
       <c r="P2">
-        <v>7367362</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>10525887</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>1790340</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>-9315442</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>-11755057</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>-2929307</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>-45566953</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>-5053520</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>-2903334</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="s">
         <v>99</v>
@@ -1137,37 +1134,37 @@
         <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
         <v>62</v>
       </c>
       <c r="F3">
-        <v>1000000</v>
+        <v>1566800</v>
       </c>
       <c r="G3">
-        <v>500000</v>
+        <v>1566800</v>
       </c>
       <c r="H3">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>9500</v>
+        <v>13600</v>
       </c>
       <c r="J3">
-        <v>10700</v>
+        <v>15300</v>
       </c>
       <c r="K3">
-        <v>5530000</v>
+        <v>9349954</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>13000</v>
+        <v>15300</v>
       </c>
       <c r="N3" t="s">
         <v>76</v>
@@ -1176,31 +1173,31 @@
         <v>90</v>
       </c>
       <c r="P3">
-        <v>25588</v>
+        <v>7367362</v>
       </c>
       <c r="Q3">
-        <v>30049</v>
+        <v>10525887</v>
       </c>
       <c r="R3">
-        <v>7363</v>
+        <v>1790340</v>
       </c>
       <c r="S3">
-        <v>3780</v>
+        <v>-9315442</v>
       </c>
       <c r="T3">
-        <v>5016</v>
+        <v>-11755057</v>
       </c>
       <c r="U3">
-        <v>938</v>
+        <v>-2929307</v>
       </c>
       <c r="V3">
-        <v>3456</v>
+        <v>-45566953</v>
       </c>
       <c r="W3">
-        <v>4688</v>
+        <v>-5053520</v>
       </c>
       <c r="X3">
-        <v>809</v>
+        <v>-2903334</v>
       </c>
       <c r="Y3" t="s">
         <v>100</v>
@@ -1211,40 +1208,40 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E4" t="s">
         <v>63</v>
       </c>
       <c r="F4">
-        <v>6500000</v>
+        <v>1000000</v>
       </c>
       <c r="G4">
-        <v>6500000</v>
+        <v>500000</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="I4">
-        <v>2000</v>
+        <v>9500</v>
       </c>
       <c r="J4">
-        <v>2000</v>
+        <v>10700</v>
       </c>
       <c r="K4">
-        <v>7910000</v>
+        <v>5530000</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="N4" t="s">
         <v>77</v>
@@ -1253,31 +1250,31 @@
         <v>91</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>25588</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>30049</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>7363</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>3780</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>5016</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>938</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>3456</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>4688</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>809</v>
       </c>
       <c r="Y4" t="s">
         <v>101</v>
@@ -1288,73 +1285,73 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
         <v>64</v>
       </c>
       <c r="F5">
-        <v>1400000</v>
+        <v>6500000</v>
       </c>
       <c r="G5">
-        <v>1400000</v>
+        <v>6500000</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>12500</v>
+        <v>2000</v>
       </c>
       <c r="J5">
-        <v>15500</v>
+        <v>2000</v>
       </c>
       <c r="K5">
-        <v>7486442</v>
+        <v>7910000</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>15500</v>
+        <v>2000</v>
       </c>
       <c r="N5" t="s">
         <v>78</v>
       </c>
       <c r="O5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="P5">
-        <v>10740898602</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>13058877126</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>3506428302</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>1748628548</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>1115790858</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>191527654</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>1491084554</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>1185231988</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>219774608</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="s">
         <v>102</v>
@@ -1365,73 +1362,73 @@
         <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
         <v>65</v>
       </c>
       <c r="F6">
-        <v>1000000</v>
+        <v>1400000</v>
       </c>
       <c r="G6">
-        <v>1000000</v>
+        <v>1400000</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>24000</v>
+        <v>12500</v>
       </c>
       <c r="J6">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="K6">
-        <v>8008066</v>
+        <v>7486442</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>29000</v>
+        <v>15500</v>
       </c>
       <c r="N6" t="s">
         <v>79</v>
       </c>
       <c r="O6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>10740898602</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>13058877126</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>3506428302</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1748628548</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1115790858</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>191527654</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1491084554</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1185231988</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>219774608</v>
       </c>
       <c r="Y6" t="s">
         <v>103</v>
@@ -1439,49 +1436,49 @@
     </row>
     <row r="7" spans="1:25">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E7" t="s">
         <v>66</v>
       </c>
       <c r="F7">
-        <v>751000</v>
+        <v>1000000</v>
       </c>
       <c r="G7">
-        <v>203700</v>
+        <v>1000000</v>
       </c>
       <c r="H7">
-        <v>547300</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>18000</v>
+        <v>24000</v>
       </c>
       <c r="J7">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="K7">
-        <v>4330068</v>
+        <v>8008066</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="N7" t="s">
         <v>80</v>
       </c>
       <c r="O7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1516,49 +1513,49 @@
     </row>
     <row r="8" spans="1:25">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
         <v>67</v>
       </c>
       <c r="F8">
-        <v>5800000</v>
+        <v>751000</v>
       </c>
       <c r="G8">
-        <v>5800000</v>
+        <v>203700</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>547300</v>
       </c>
       <c r="I8">
-        <v>2000</v>
+        <v>18000</v>
       </c>
       <c r="J8">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="K8">
-        <v>6100000</v>
+        <v>4330068</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="N8" t="s">
         <v>81</v>
       </c>
       <c r="O8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1599,73 +1596,73 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
         <v>68</v>
       </c>
       <c r="F9">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="G9">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="J9">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="K9">
-        <v>10000988</v>
+        <v>6100000</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N9" t="s">
         <v>82</v>
       </c>
       <c r="O9" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="P9">
-        <v>72895458363</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>72913766913</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>11230711680</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>-6524077412</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>-4556157069</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>-3633759729</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>-11528915410</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>-7978634776</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>-3801868433</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1673,76 +1670,76 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
         <v>69</v>
       </c>
       <c r="F10">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="G10">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>7300</v>
+        <v>16000</v>
       </c>
       <c r="J10">
-        <v>8500</v>
+        <v>19000</v>
       </c>
       <c r="K10">
-        <v>14965620</v>
+        <v>10000988</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="N10" t="s">
         <v>83</v>
       </c>
       <c r="O10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P10">
-        <v>1337894447</v>
+        <v>72895458363</v>
       </c>
       <c r="Q10">
-        <v>4495088983</v>
+        <v>72913766913</v>
       </c>
       <c r="R10">
-        <v>99398351</v>
+        <v>11230711680</v>
       </c>
       <c r="S10">
-        <v>-3330678562</v>
+        <v>-6524077412</v>
       </c>
       <c r="T10">
-        <v>-2905069801</v>
+        <v>-4556157069</v>
       </c>
       <c r="U10">
-        <v>-1314068310</v>
+        <v>-3633759729</v>
       </c>
       <c r="V10">
-        <v>-9735376868</v>
+        <v>-11528915410</v>
       </c>
       <c r="W10">
-        <v>-5043515600</v>
+        <v>-7978634776</v>
       </c>
       <c r="X10">
-        <v>-1257080998</v>
+        <v>-3801868433</v>
       </c>
       <c r="Y10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1753,73 +1750,73 @@
         <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s">
         <v>70</v>
       </c>
       <c r="F11">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="G11">
-        <v>1350000</v>
+        <v>2234000</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>14000</v>
+        <v>7300</v>
       </c>
       <c r="J11">
-        <v>17000</v>
+        <v>8500</v>
       </c>
       <c r="K11">
-        <v>6471740</v>
+        <v>14965620</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="N11" t="s">
         <v>84</v>
       </c>
       <c r="O11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P11">
-        <v>5214628820</v>
+        <v>1337894447</v>
       </c>
       <c r="Q11">
-        <v>6009352447</v>
+        <v>4495088983</v>
       </c>
       <c r="R11">
-        <v>965797975</v>
+        <v>99398351</v>
       </c>
       <c r="S11">
-        <v>2015081728</v>
+        <v>-3330678562</v>
       </c>
       <c r="T11">
-        <v>1319755337</v>
+        <v>-2905069801</v>
       </c>
       <c r="U11">
-        <v>-44547594</v>
+        <v>-1314068310</v>
       </c>
       <c r="V11">
-        <v>1503069100</v>
+        <v>-9735376868</v>
       </c>
       <c r="W11">
-        <v>1410469786</v>
+        <v>-5043515600</v>
       </c>
       <c r="X11">
-        <v>24178632</v>
+        <v>-1257080998</v>
       </c>
       <c r="Y11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1830,96 +1827,96 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
         <v>71</v>
       </c>
       <c r="F12">
-        <v>6000000</v>
+        <v>1350000</v>
       </c>
       <c r="G12">
-        <v>6000000</v>
+        <v>1350000</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>2000</v>
+        <v>14000</v>
       </c>
       <c r="J12">
-        <v>2000</v>
+        <v>17000</v>
       </c>
       <c r="K12">
-        <v>6345000</v>
+        <v>6471740</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <v>2000</v>
+        <v>22000</v>
       </c>
       <c r="N12" t="s">
         <v>85</v>
       </c>
       <c r="O12" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>5214628820</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>6009352447</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>965797975</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>2015081728</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>1319755337</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>-44547594</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1503069100</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1410469786</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>24178632</v>
       </c>
       <c r="Y12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:25">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E13" t="s">
         <v>72</v>
       </c>
       <c r="F13">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="G13">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -1931,7 +1928,7 @@
         <v>2000</v>
       </c>
       <c r="K13">
-        <v>4420000</v>
+        <v>6345000</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1943,7 +1940,7 @@
         <v>86</v>
       </c>
       <c r="O13" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -1973,7 +1970,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1984,43 +1981,43 @@
         <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E14" t="s">
         <v>73</v>
       </c>
       <c r="F14">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="G14">
-        <v>1618000</v>
+        <v>4000000</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>6200</v>
+        <v>2000</v>
       </c>
       <c r="J14">
-        <v>7700</v>
+        <v>2000</v>
       </c>
       <c r="K14">
-        <v>10830212</v>
+        <v>4420000</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="N14" t="s">
         <v>87</v>
       </c>
       <c r="O14" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -2050,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -2058,46 +2055,46 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E15" t="s">
         <v>74</v>
       </c>
       <c r="F15">
-        <v>4000000</v>
+        <v>1618000</v>
       </c>
       <c r="G15">
-        <v>4000000</v>
+        <v>1618000</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>2000</v>
+        <v>6200</v>
       </c>
       <c r="J15">
-        <v>2000</v>
+        <v>7700</v>
       </c>
       <c r="K15">
-        <v>5020000</v>
+        <v>10830212</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="N15" t="s">
         <v>88</v>
       </c>
       <c r="O15" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -2127,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="Y15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -2165,19 +2162,19 @@
         <v>118</v>
       </c>
       <c r="B2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2185,19 +2182,19 @@
         <v>119</v>
       </c>
       <c r="B3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
-        <v>91</v>
+        <v>175</v>
       </c>
       <c r="F3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2205,19 +2202,19 @@
         <v>120</v>
       </c>
       <c r="B4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>176</v>
+        <v>89</v>
       </c>
       <c r="F4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2225,19 +2222,19 @@
         <v>121</v>
       </c>
       <c r="B5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2245,19 +2242,19 @@
         <v>122</v>
       </c>
       <c r="B6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2265,19 +2262,19 @@
         <v>123</v>
       </c>
       <c r="B7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
-        <v>91</v>
+        <v>178</v>
       </c>
       <c r="F7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2288,16 +2285,16 @@
         <v>143</v>
       </c>
       <c r="C8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2305,19 +2302,19 @@
         <v>125</v>
       </c>
       <c r="B9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
-        <v>179</v>
+        <v>89</v>
       </c>
       <c r="F9" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2328,16 +2325,16 @@
         <v>144</v>
       </c>
       <c r="C10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E10" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="F10" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2348,16 +2345,16 @@
         <v>144</v>
       </c>
       <c r="C11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
-        <v>180</v>
+        <v>89</v>
       </c>
       <c r="F11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2365,19 +2362,19 @@
         <v>128</v>
       </c>
       <c r="B12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C12" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E12" t="s">
-        <v>91</v>
+        <v>180</v>
       </c>
       <c r="F12" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2385,19 +2382,19 @@
         <v>129</v>
       </c>
       <c r="B13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E13" t="s">
-        <v>181</v>
+        <v>89</v>
       </c>
       <c r="F13" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2405,16 +2402,16 @@
         <v>130</v>
       </c>
       <c r="B14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F14" t="s">
         <v>193</v>
@@ -2425,16 +2422,16 @@
         <v>131</v>
       </c>
       <c r="B15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F15" t="s">
         <v>191</v>
@@ -2445,13 +2442,13 @@
         <v>132</v>
       </c>
       <c r="B16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C16" t="s">
         <v>158</v>
       </c>
       <c r="D16" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E16" t="s">
         <v>177</v>
@@ -2465,19 +2462,19 @@
         <v>133</v>
       </c>
       <c r="B17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C17" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E17" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F17" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -2485,16 +2482,16 @@
         <v>134</v>
       </c>
       <c r="B18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C18" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E18" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F18" t="s">
         <v>193</v>
@@ -2502,59 +2499,59 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="B19" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C19" t="s">
         <v>158</v>
       </c>
       <c r="D19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E19" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F19" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B20" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E20" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F20" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B21" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C21" t="s">
         <v>158</v>
       </c>
       <c r="D21" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E21" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F21" t="s">
         <v>193</v>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -374,6 +374,12 @@
     <t>더본코리아(유가)</t>
   </si>
   <si>
+    <t>닷밀</t>
+  </si>
+  <si>
+    <t>웨이비스</t>
+  </si>
+  <si>
     <t>씨메스</t>
   </si>
   <si>
@@ -407,9 +413,6 @@
     <t>토모큐브</t>
   </si>
   <si>
-    <t>웨이비스</t>
-  </si>
-  <si>
     <t>에이치이엠파마(구.에이치이엠)</t>
   </si>
   <si>
@@ -425,12 +428,15 @@
     <t>아이스크림미디어(구.시공미디어)</t>
   </si>
   <si>
-    <t>대신밸런스스팩18호</t>
-  </si>
-  <si>
     <t>2024.10.15~10.21</t>
   </si>
   <si>
+    <t>2024.10.10~10.16</t>
+  </si>
+  <si>
+    <t>2024.10.07~10.14</t>
+  </si>
+  <si>
     <t>2024.09.30~10.08</t>
   </si>
   <si>
@@ -455,9 +461,6 @@
     <t>2024.09.20~09.26</t>
   </si>
   <si>
-    <t>2024.09.09~09.13</t>
-  </si>
-  <si>
     <t>2024.09.06~09.12</t>
   </si>
   <si>
@@ -476,12 +479,15 @@
     <t>2024.08.09~08.16</t>
   </si>
   <si>
-    <t>2024.08.05~08.06</t>
-  </si>
-  <si>
     <t>23,000~28,000</t>
   </si>
   <si>
+    <t>11,000~13,000</t>
+  </si>
+  <si>
+    <t>11,000~12,500</t>
+  </si>
+  <si>
     <t>20,000~24,000</t>
   </si>
   <si>
@@ -515,9 +521,6 @@
     <t>10,900~13,400</t>
   </si>
   <si>
-    <t>11,000~12,500</t>
-  </si>
-  <si>
     <t>16,400~19,000</t>
   </si>
   <si>
@@ -575,12 +578,15 @@
     <t>78720</t>
   </si>
   <si>
-    <t>13000</t>
-  </si>
-  <si>
     <t>한국투자증권,NH투자증권</t>
   </si>
   <si>
+    <t>미래에셋증권</t>
+  </si>
+  <si>
+    <t>대신증권</t>
+  </si>
+  <si>
     <t>삼성증권,유진투자증권,유안타증권</t>
   </si>
   <si>
@@ -596,9 +602,6 @@
     <t>KB증권</t>
   </si>
   <si>
-    <t>대신증권</t>
-  </si>
-  <si>
     <t>신영증권,유진증권</t>
   </si>
   <si>
@@ -606,9 +609,6 @@
   </si>
   <si>
     <t>신영증권,KB증권</t>
-  </si>
-  <si>
-    <t>미래에셋증권</t>
   </si>
   <si>
     <t>삼성증권</t>
@@ -2171,7 +2171,7 @@
         <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F2" t="s">
         <v>187</v>
@@ -2191,7 +2191,7 @@
         <v>89</v>
       </c>
       <c r="E3" t="s">
-        <v>175</v>
+        <v>89</v>
       </c>
       <c r="F3" t="s">
         <v>188</v>
@@ -2251,7 +2251,7 @@
         <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>177</v>
+        <v>89</v>
       </c>
       <c r="F6" t="s">
         <v>191</v>
@@ -2271,7 +2271,7 @@
         <v>89</v>
       </c>
       <c r="E7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F7" t="s">
         <v>192</v>
@@ -2291,7 +2291,7 @@
         <v>89</v>
       </c>
       <c r="E8" t="s">
-        <v>89</v>
+        <v>178</v>
       </c>
       <c r="F8" t="s">
         <v>193</v>
@@ -2302,7 +2302,7 @@
         <v>125</v>
       </c>
       <c r="B9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C9" t="s">
         <v>161</v>
@@ -2311,10 +2311,10 @@
         <v>89</v>
       </c>
       <c r="E9" t="s">
-        <v>89</v>
+        <v>179</v>
       </c>
       <c r="F9" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2322,7 +2322,7 @@
         <v>126</v>
       </c>
       <c r="B10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C10" t="s">
         <v>162</v>
@@ -2331,7 +2331,7 @@
         <v>89</v>
       </c>
       <c r="E10" t="s">
-        <v>179</v>
+        <v>89</v>
       </c>
       <c r="F10" t="s">
         <v>189</v>
@@ -2342,7 +2342,7 @@
         <v>127</v>
       </c>
       <c r="B11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C11" t="s">
         <v>163</v>
@@ -2362,7 +2362,7 @@
         <v>128</v>
       </c>
       <c r="B12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C12" t="s">
         <v>164</v>
@@ -2374,7 +2374,7 @@
         <v>180</v>
       </c>
       <c r="F12" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2382,7 +2382,7 @@
         <v>129</v>
       </c>
       <c r="B13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C13" t="s">
         <v>165</v>
@@ -2394,7 +2394,7 @@
         <v>89</v>
       </c>
       <c r="F13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2411,10 +2411,10 @@
         <v>89</v>
       </c>
       <c r="E14" t="s">
-        <v>89</v>
+        <v>181</v>
       </c>
       <c r="F14" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2431,10 +2431,10 @@
         <v>89</v>
       </c>
       <c r="E15" t="s">
-        <v>181</v>
+        <v>89</v>
       </c>
       <c r="F15" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2445,16 +2445,16 @@
         <v>148</v>
       </c>
       <c r="C16" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="D16" t="s">
-        <v>171</v>
+        <v>89</v>
       </c>
       <c r="E16" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F16" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2465,16 +2465,16 @@
         <v>149</v>
       </c>
       <c r="C17" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>172</v>
       </c>
       <c r="E17" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F17" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -2488,53 +2488,53 @@
         <v>169</v>
       </c>
       <c r="D18" t="s">
-        <v>172</v>
+        <v>89</v>
       </c>
       <c r="E18" t="s">
         <v>183</v>
       </c>
       <c r="F18" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>135</v>
       </c>
       <c r="B19" t="s">
         <v>151</v>
       </c>
       <c r="C19" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="D19" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E19" t="s">
         <v>184</v>
       </c>
       <c r="F19" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="B20" t="s">
         <v>152</v>
       </c>
       <c r="C20" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="D20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E20" t="s">
         <v>185</v>
       </c>
       <c r="F20" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -2545,16 +2545,16 @@
         <v>153</v>
       </c>
       <c r="C21" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="D21" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E21" t="s">
         <v>186</v>
       </c>
       <c r="F21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="198">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -371,15 +371,24 @@
     <t>주간사</t>
   </si>
   <si>
+    <t>위츠</t>
+  </si>
+  <si>
     <t>더본코리아(유가)</t>
   </si>
   <si>
     <t>닷밀</t>
   </si>
   <si>
+    <t>성우</t>
+  </si>
+  <si>
     <t>웨이비스</t>
   </si>
   <si>
+    <t>클로봇</t>
+  </si>
+  <si>
     <t>씨메스</t>
   </si>
   <si>
@@ -407,9 +416,6 @@
     <t>한켐</t>
   </si>
   <si>
-    <t>클로봇</t>
-  </si>
-  <si>
     <t>토모큐브</t>
   </si>
   <si>
@@ -425,7 +431,7 @@
     <t>아이언디바이스</t>
   </si>
   <si>
-    <t>아이스크림미디어(구.시공미디어)</t>
+    <t>2024.10.28~11.01</t>
   </si>
   <si>
     <t>2024.10.15~10.21</t>
@@ -473,10 +479,7 @@
     <t>2024.08.30~09.05</t>
   </si>
   <si>
-    <t>2024.08.26~08.27</t>
-  </si>
-  <si>
-    <t>2024.08.09~08.16</t>
+    <t>5,300~6,400</t>
   </si>
   <si>
     <t>23,000~28,000</t>
@@ -485,9 +488,15 @@
     <t>11,000~13,000</t>
   </si>
   <si>
+    <t>25,000~29,000</t>
+  </si>
+  <si>
     <t>11,000~12,500</t>
   </si>
   <si>
+    <t>9,400~10,900</t>
+  </si>
+  <si>
     <t>20,000~24,000</t>
   </si>
   <si>
@@ -515,9 +524,6 @@
     <t>12,500~14,500</t>
   </si>
   <si>
-    <t>9,400~10,900</t>
-  </si>
-  <si>
     <t>10,900~13,400</t>
   </si>
   <si>
@@ -530,21 +536,24 @@
     <t>4,900~5,700</t>
   </si>
   <si>
-    <t>32,000~40,200</t>
-  </si>
-  <si>
     <t>2000</t>
   </si>
   <si>
     <t>7000</t>
   </si>
   <si>
-    <t>32000</t>
+    <t>15900</t>
   </si>
   <si>
     <t>69000</t>
   </si>
   <si>
+    <t>75000</t>
+  </si>
+  <si>
+    <t>28200</t>
+  </si>
+  <si>
     <t>52000</t>
   </si>
   <si>
@@ -560,9 +569,6 @@
     <t>18000</t>
   </si>
   <si>
-    <t>28200</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -572,10 +578,7 @@
     <t>21000</t>
   </si>
   <si>
-    <t>15900</t>
-  </si>
-  <si>
-    <t>78720</t>
+    <t>신한투자증권</t>
   </si>
   <si>
     <t>한국투자증권,NH투자증권</t>
@@ -584,34 +587,28 @@
     <t>미래에셋증권</t>
   </si>
   <si>
+    <t>한국투자증권</t>
+  </si>
+  <si>
     <t>대신증권</t>
   </si>
   <si>
+    <t>미래에셋증권,신영증권</t>
+  </si>
+  <si>
     <t>삼성증권,유진투자증권,유안타증권</t>
   </si>
   <si>
-    <t>한국투자증권</t>
-  </si>
-  <si>
     <t>NH투자증권</t>
   </si>
   <si>
-    <t>신한투자증권</t>
-  </si>
-  <si>
     <t>KB증권</t>
   </si>
   <si>
     <t>신영증권,유진증권</t>
   </si>
   <si>
-    <t>미래에셋증권,신영증권</t>
-  </si>
-  <si>
     <t>신영증권,KB증권</t>
-  </si>
-  <si>
-    <t>삼성증권</t>
   </si>
 </sst>
 </file>
@@ -2162,7 +2159,7 @@
         <v>118</v>
       </c>
       <c r="B2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C2" t="s">
         <v>154</v>
@@ -2182,7 +2179,7 @@
         <v>119</v>
       </c>
       <c r="B3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C3" t="s">
         <v>155</v>
@@ -2191,7 +2188,7 @@
         <v>89</v>
       </c>
       <c r="E3" t="s">
-        <v>89</v>
+        <v>176</v>
       </c>
       <c r="F3" t="s">
         <v>188</v>
@@ -2202,7 +2199,7 @@
         <v>120</v>
       </c>
       <c r="B4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C4" t="s">
         <v>156</v>
@@ -2231,7 +2228,7 @@
         <v>89</v>
       </c>
       <c r="E5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F5" t="s">
         <v>190</v>
@@ -2262,7 +2259,7 @@
         <v>123</v>
       </c>
       <c r="B7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C7" t="s">
         <v>159</v>
@@ -2271,7 +2268,7 @@
         <v>89</v>
       </c>
       <c r="E7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F7" t="s">
         <v>192</v>
@@ -2282,7 +2279,7 @@
         <v>124</v>
       </c>
       <c r="B8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C8" t="s">
         <v>160</v>
@@ -2291,7 +2288,7 @@
         <v>89</v>
       </c>
       <c r="E8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F8" t="s">
         <v>193</v>
@@ -2302,7 +2299,7 @@
         <v>125</v>
       </c>
       <c r="B9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C9" t="s">
         <v>161</v>
@@ -2311,10 +2308,10 @@
         <v>89</v>
       </c>
       <c r="E9" t="s">
-        <v>179</v>
+        <v>89</v>
       </c>
       <c r="F9" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2322,7 +2319,7 @@
         <v>126</v>
       </c>
       <c r="B10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C10" t="s">
         <v>162</v>
@@ -2331,10 +2328,10 @@
         <v>89</v>
       </c>
       <c r="E10" t="s">
-        <v>89</v>
+        <v>180</v>
       </c>
       <c r="F10" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2351,10 +2348,10 @@
         <v>89</v>
       </c>
       <c r="E11" t="s">
-        <v>89</v>
+        <v>181</v>
       </c>
       <c r="F11" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2371,10 +2368,10 @@
         <v>89</v>
       </c>
       <c r="E12" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F12" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2382,7 +2379,7 @@
         <v>129</v>
       </c>
       <c r="B13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C13" t="s">
         <v>165</v>
@@ -2394,7 +2391,7 @@
         <v>89</v>
       </c>
       <c r="F13" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2402,7 +2399,7 @@
         <v>130</v>
       </c>
       <c r="B14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C14" t="s">
         <v>166</v>
@@ -2411,10 +2408,10 @@
         <v>89</v>
       </c>
       <c r="E14" t="s">
-        <v>181</v>
+        <v>89</v>
       </c>
       <c r="F14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2422,7 +2419,7 @@
         <v>131</v>
       </c>
       <c r="B15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C15" t="s">
         <v>167</v>
@@ -2431,10 +2428,10 @@
         <v>89</v>
       </c>
       <c r="E15" t="s">
-        <v>89</v>
+        <v>183</v>
       </c>
       <c r="F15" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2451,10 +2448,10 @@
         <v>89</v>
       </c>
       <c r="E16" t="s">
-        <v>182</v>
+        <v>89</v>
       </c>
       <c r="F16" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2465,16 +2462,16 @@
         <v>149</v>
       </c>
       <c r="C17" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="D17" t="s">
-        <v>172</v>
+        <v>89</v>
       </c>
       <c r="E17" t="s">
-        <v>178</v>
+        <v>89</v>
       </c>
       <c r="F17" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -2485,16 +2482,16 @@
         <v>150</v>
       </c>
       <c r="C18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D18" t="s">
         <v>89</v>
       </c>
       <c r="E18" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F18" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2505,47 +2502,47 @@
         <v>151</v>
       </c>
       <c r="C19" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D19" t="s">
         <v>173</v>
       </c>
       <c r="E19" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F19" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>136</v>
       </c>
       <c r="B20" t="s">
         <v>152</v>
       </c>
       <c r="C20" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="D20" t="s">
-        <v>172</v>
+        <v>89</v>
       </c>
       <c r="E20" t="s">
         <v>185</v>
       </c>
       <c r="F20" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B21" t="s">
         <v>153</v>
       </c>
       <c r="C21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D21" t="s">
         <v>174</v>
@@ -2554,7 +2551,7 @@
         <v>186</v>
       </c>
       <c r="F21" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="190">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -122,9 +122,6 @@
     <t>2024-07-09</t>
   </si>
   <si>
-    <t>2024-06-24</t>
-  </si>
-  <si>
     <t>2024-08-27</t>
   </si>
   <si>
@@ -143,9 +140,6 @@
     <t>2024-07-10</t>
   </si>
   <si>
-    <t>2024-06-28</t>
-  </si>
-  <si>
     <t>2024-09-11</t>
   </si>
   <si>
@@ -239,9 +233,6 @@
     <t>SK증권제13호스팩</t>
   </si>
   <si>
-    <t>엑셀세라퓨틱스</t>
-  </si>
-  <si>
     <t>1051.62 :1</t>
   </si>
   <si>
@@ -281,9 +272,6 @@
     <t>1197.45:1</t>
   </si>
   <si>
-    <t>1233.80:1</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -311,9 +299,6 @@
     <t>5.60%</t>
   </si>
   <si>
-    <t>4.50%</t>
-  </si>
-  <si>
     <t>기업인수합병</t>
   </si>
   <si>
@@ -350,9 +335,6 @@
     <t>기업인수목적 주식회사</t>
   </si>
   <si>
-    <t>CellCor SFD/CD(세포배양배지)</t>
-  </si>
-  <si>
     <t>종목명</t>
   </si>
   <si>
@@ -377,12 +359,24 @@
     <t>더본코리아(유가)</t>
   </si>
   <si>
+    <t>유진스팩11호</t>
+  </si>
+  <si>
+    <t>노머스</t>
+  </si>
+  <si>
     <t>닷밀</t>
   </si>
   <si>
+    <t>탑런토탈솔루션</t>
+  </si>
+  <si>
     <t>성우</t>
   </si>
   <si>
+    <t>케이뱅크(유가)</t>
+  </si>
+  <si>
     <t>웨이비스</t>
   </si>
   <si>
@@ -392,6 +386,9 @@
     <t>씨메스</t>
   </si>
   <si>
+    <t>에이치엔에스하이텍</t>
+  </si>
+  <si>
     <t>쓰리빌리언</t>
   </si>
   <si>
@@ -407,9 +404,6 @@
     <t>셀비온</t>
   </si>
   <si>
-    <t>탑런토탈솔루션</t>
-  </si>
-  <si>
     <t>인스피언</t>
   </si>
   <si>
@@ -419,24 +413,18 @@
     <t>토모큐브</t>
   </si>
   <si>
-    <t>에이치이엠파마(구.에이치이엠)</t>
-  </si>
-  <si>
-    <t>KB스팩30호</t>
-  </si>
-  <si>
-    <t>제닉스</t>
-  </si>
-  <si>
-    <t>아이언디바이스</t>
-  </si>
-  <si>
     <t>2024.10.28~11.01</t>
   </si>
   <si>
     <t>2024.10.15~10.21</t>
   </si>
   <si>
+    <t>2024.10.15~10.16</t>
+  </si>
+  <si>
+    <t>2024.10.11~10.17</t>
+  </si>
+  <si>
     <t>2024.10.10~10.16</t>
   </si>
   <si>
@@ -467,30 +455,30 @@
     <t>2024.09.20~09.26</t>
   </si>
   <si>
-    <t>2024.09.06~09.12</t>
-  </si>
-  <si>
-    <t>2024.09.05~09.06</t>
-  </si>
-  <si>
-    <t>2024.09.05~09.11</t>
-  </si>
-  <si>
-    <t>2024.08.30~09.05</t>
-  </si>
-  <si>
     <t>5,300~6,400</t>
   </si>
   <si>
     <t>23,000~28,000</t>
   </si>
   <si>
+    <t>2,000~2,000</t>
+  </si>
+  <si>
+    <t>27,200~30,200</t>
+  </si>
+  <si>
     <t>11,000~13,000</t>
   </si>
   <si>
+    <t>12,000~14,000</t>
+  </si>
+  <si>
     <t>25,000~29,000</t>
   </si>
   <si>
+    <t>9,500~12,000</t>
+  </si>
+  <si>
     <t>11,000~12,500</t>
   </si>
   <si>
@@ -500,24 +488,21 @@
     <t>20,000~24,000</t>
   </si>
   <si>
+    <t>22,000~26,000</t>
+  </si>
+  <si>
     <t>4,500~6,500</t>
   </si>
   <si>
     <t>16,500~20,500</t>
   </si>
   <si>
-    <t>2,000~2,000</t>
-  </si>
-  <si>
     <t>8,600~9,800</t>
   </si>
   <si>
     <t>10,000~12,200</t>
   </si>
   <si>
-    <t>12,000~14,000</t>
-  </si>
-  <si>
     <t>8,000~10,000</t>
   </si>
   <si>
@@ -527,36 +512,33 @@
     <t>10,900~13,400</t>
   </si>
   <si>
-    <t>16,400~19,000</t>
-  </si>
-  <si>
-    <t>28,000~34,000</t>
-  </si>
-  <si>
-    <t>4,900~5,700</t>
-  </si>
-  <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>7000</t>
-  </si>
-  <si>
     <t>15900</t>
   </si>
   <si>
     <t>69000</t>
   </si>
   <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>30736</t>
+  </si>
+  <si>
     <t>75000</t>
   </si>
   <si>
+    <t>779000</t>
+  </si>
+  <si>
     <t>28200</t>
   </si>
   <si>
     <t>52000</t>
   </si>
   <si>
+    <t>11000</t>
+  </si>
+  <si>
     <t>49500</t>
   </si>
   <si>
@@ -569,28 +551,28 @@
     <t>18000</t>
   </si>
   <si>
-    <t>11430</t>
-  </si>
-  <si>
-    <t>18480</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
     <t>신한투자증권</t>
   </si>
   <si>
     <t>한국투자증권,NH투자증권</t>
   </si>
   <si>
+    <t>유진증권</t>
+  </si>
+  <si>
+    <t>대신증권</t>
+  </si>
+  <si>
     <t>미래에셋증권</t>
   </si>
   <si>
+    <t>KB증권</t>
+  </si>
+  <si>
     <t>한국투자증권</t>
   </si>
   <si>
-    <t>대신증권</t>
+    <t>NH투자증권,KB증권,신한투자증권,키움증권</t>
   </si>
   <si>
     <t>미래에셋증권,신영증권</t>
@@ -602,13 +584,7 @@
     <t>NH투자증권</t>
   </si>
   <si>
-    <t>KB증권</t>
-  </si>
-  <si>
     <t>신영증권,유진증권</t>
-  </si>
-  <si>
-    <t>신영증권,KB증권</t>
   </si>
 </sst>
 </file>
@@ -966,7 +942,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y15"/>
+  <dimension ref="A1:Y14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1051,16 +1027,16 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F2">
         <v>7950000</v>
@@ -1087,10 +1063,10 @@
         <v>2000</v>
       </c>
       <c r="N2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="O2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -1120,7 +1096,7 @@
         <v>0</v>
       </c>
       <c r="Y2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1128,16 +1104,16 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F3">
         <v>1566800</v>
@@ -1164,10 +1140,10 @@
         <v>15300</v>
       </c>
       <c r="N3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="P3">
         <v>7367362</v>
@@ -1197,7 +1173,7 @@
         <v>-2903334</v>
       </c>
       <c r="Y3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1205,16 +1181,16 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F4">
         <v>1000000</v>
@@ -1241,10 +1217,10 @@
         <v>13000</v>
       </c>
       <c r="N4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="P4">
         <v>25588</v>
@@ -1274,7 +1250,7 @@
         <v>809</v>
       </c>
       <c r="Y4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1282,16 +1258,16 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F5">
         <v>6500000</v>
@@ -1318,10 +1294,10 @@
         <v>2000</v>
       </c>
       <c r="N5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="O5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1351,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="Y5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1362,13 +1338,13 @@
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F6">
         <v>1400000</v>
@@ -1395,10 +1371,10 @@
         <v>15500</v>
       </c>
       <c r="N6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="O6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="P6">
         <v>10740898602</v>
@@ -1428,7 +1404,7 @@
         <v>219774608</v>
       </c>
       <c r="Y6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1439,13 +1415,13 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F7">
         <v>1000000</v>
@@ -1472,10 +1448,10 @@
         <v>29000</v>
       </c>
       <c r="N7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="O7" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1505,7 +1481,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1516,13 +1492,13 @@
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F8">
         <v>751000</v>
@@ -1549,10 +1525,10 @@
         <v>21000</v>
       </c>
       <c r="N8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="O8" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1582,7 +1558,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1593,13 +1569,13 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F9">
         <v>5800000</v>
@@ -1626,10 +1602,10 @@
         <v>2000</v>
       </c>
       <c r="N9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="O9" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1659,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="Y9" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1670,13 +1646,13 @@
         <v>30</v>
       </c>
       <c r="C10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" t="s">
         <v>50</v>
       </c>
-      <c r="D10" t="s">
-        <v>52</v>
-      </c>
       <c r="E10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F10">
         <v>1400000</v>
@@ -1703,10 +1679,10 @@
         <v>16000</v>
       </c>
       <c r="N10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="O10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="P10">
         <v>72895458363</v>
@@ -1736,7 +1712,7 @@
         <v>-3801868433</v>
       </c>
       <c r="Y10" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1744,16 +1720,16 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F11">
         <v>2234000</v>
@@ -1780,10 +1756,10 @@
         <v>10000</v>
       </c>
       <c r="N11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O11" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="P11">
         <v>1337894447</v>
@@ -1813,7 +1789,7 @@
         <v>-1257080998</v>
       </c>
       <c r="Y11" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1821,16 +1797,16 @@
         <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F12">
         <v>1350000</v>
@@ -1857,10 +1833,10 @@
         <v>22000</v>
       </c>
       <c r="N12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="O12" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="P12">
         <v>5214628820</v>
@@ -1890,7 +1866,7 @@
         <v>24178632</v>
       </c>
       <c r="Y12" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1898,16 +1874,16 @@
         <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" t="s">
         <v>51</v>
       </c>
-      <c r="D13" t="s">
-        <v>53</v>
-      </c>
       <c r="E13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F13">
         <v>6000000</v>
@@ -1934,10 +1910,10 @@
         <v>2000</v>
       </c>
       <c r="N13" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="O13" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -1967,7 +1943,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1975,16 +1951,16 @@
         <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F14">
         <v>4000000</v>
@@ -2011,10 +1987,10 @@
         <v>2000</v>
       </c>
       <c r="N14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O14" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -2044,84 +2020,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25">
-      <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" t="s">
-        <v>55</v>
-      </c>
-      <c r="E15" t="s">
-        <v>74</v>
-      </c>
-      <c r="F15">
-        <v>1618000</v>
-      </c>
-      <c r="G15">
-        <v>1618000</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>6200</v>
-      </c>
-      <c r="J15">
-        <v>7700</v>
-      </c>
-      <c r="K15">
-        <v>10830212</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>10000</v>
-      </c>
-      <c r="N15" t="s">
-        <v>88</v>
-      </c>
-      <c r="O15" t="s">
-        <v>98</v>
-      </c>
-      <c r="P15">
-        <v>0</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>0</v>
-      </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
-      <c r="W15">
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -2136,422 +2035,422 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C2" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="F2" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B3" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C3" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="F3" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B4" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C4" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>89</v>
+        <v>167</v>
       </c>
       <c r="F4" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C5" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="F5" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B6" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C6" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F6" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B7" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C7" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>178</v>
+        <v>85</v>
       </c>
       <c r="F7" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B8" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C8" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="F8" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B9" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C9" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
-        <v>89</v>
+        <v>170</v>
       </c>
       <c r="F9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B10" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C10" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
-        <v>180</v>
+        <v>85</v>
       </c>
       <c r="F10" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B11" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C11" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E11" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="F11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B12" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C12" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E12" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="F12" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B13" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C13" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E13" t="s">
-        <v>89</v>
+        <v>173</v>
       </c>
       <c r="F13" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B14" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C14" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E14" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F14" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B15" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C15" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E15" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F15" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B16" t="s">
+        <v>141</v>
+      </c>
+      <c r="C16" t="s">
         <v>148</v>
       </c>
-      <c r="C16" t="s">
-        <v>168</v>
-      </c>
       <c r="D16" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E16" t="s">
-        <v>89</v>
+        <v>175</v>
       </c>
       <c r="F16" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B17" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C17" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E17" t="s">
-        <v>89</v>
+        <v>176</v>
       </c>
       <c r="F17" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B18" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C18" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="D18" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E18" t="s">
-        <v>184</v>
+        <v>85</v>
       </c>
       <c r="F18" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B19" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C19" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D19" t="s">
-        <v>173</v>
+        <v>85</v>
       </c>
       <c r="E19" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F19" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B20" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C20" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="D20" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E20" t="s">
-        <v>185</v>
+        <v>85</v>
       </c>
       <c r="F20" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B21" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C21" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="D21" t="s">
-        <v>174</v>
+        <v>85</v>
       </c>
       <c r="E21" t="s">
-        <v>186</v>
+        <v>85</v>
       </c>
       <c r="F21" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="184">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -116,9 +116,6 @@
     <t>2024-07-15</t>
   </si>
   <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
     <t>2024-07-09</t>
   </si>
   <si>
@@ -134,9 +131,6 @@
     <t>2024-07-19</t>
   </si>
   <si>
-    <t>2024-07-17</t>
-  </si>
-  <si>
     <t>2024-07-10</t>
   </si>
   <si>
@@ -224,9 +218,6 @@
     <t>아이빔테크놀로지</t>
   </si>
   <si>
-    <t>피앤에스미캐닉스</t>
-  </si>
-  <si>
     <t>엔에이치스팩31호</t>
   </si>
   <si>
@@ -263,9 +254,6 @@
     <t>1011.50:1</t>
   </si>
   <si>
-    <t>986.08:1</t>
-  </si>
-  <si>
     <t>1123.43 :1</t>
   </si>
   <si>
@@ -296,9 +284,6 @@
     <t>0.49%</t>
   </si>
   <si>
-    <t>5.60%</t>
-  </si>
-  <si>
     <t>기업인수합병</t>
   </si>
   <si>
@@ -324,9 +309,6 @@
   </si>
   <si>
     <t>생체현미경, CRO 서비스</t>
-  </si>
-  <si>
-    <t>보행재활로봇 시스템</t>
   </si>
   <si>
     <t>금융지원서비스업</t>
@@ -942,7 +924,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y14"/>
+  <dimension ref="A1:Y13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1027,16 +1009,16 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F2">
         <v>7950000</v>
@@ -1063,10 +1045,10 @@
         <v>2000</v>
       </c>
       <c r="N2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="O2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -1096,7 +1078,7 @@
         <v>0</v>
       </c>
       <c r="Y2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1104,16 +1086,16 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F3">
         <v>1566800</v>
@@ -1140,10 +1122,10 @@
         <v>15300</v>
       </c>
       <c r="N3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="O3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="P3">
         <v>7367362</v>
@@ -1173,7 +1155,7 @@
         <v>-2903334</v>
       </c>
       <c r="Y3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1181,16 +1163,16 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F4">
         <v>1000000</v>
@@ -1217,10 +1199,10 @@
         <v>13000</v>
       </c>
       <c r="N4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="O4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="P4">
         <v>25588</v>
@@ -1250,7 +1232,7 @@
         <v>809</v>
       </c>
       <c r="Y4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1258,16 +1240,16 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F5">
         <v>6500000</v>
@@ -1294,10 +1276,10 @@
         <v>2000</v>
       </c>
       <c r="N5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="O5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1327,7 +1309,7 @@
         <v>0</v>
       </c>
       <c r="Y5" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1338,13 +1320,13 @@
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F6">
         <v>1400000</v>
@@ -1371,10 +1353,10 @@
         <v>15500</v>
       </c>
       <c r="N6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="O6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="P6">
         <v>10740898602</v>
@@ -1404,7 +1386,7 @@
         <v>219774608</v>
       </c>
       <c r="Y6" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1415,13 +1397,13 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F7">
         <v>1000000</v>
@@ -1448,10 +1430,10 @@
         <v>29000</v>
       </c>
       <c r="N7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O7" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1481,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1492,13 +1474,13 @@
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F8">
         <v>751000</v>
@@ -1525,10 +1507,10 @@
         <v>21000</v>
       </c>
       <c r="N8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="O8" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1558,7 +1540,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1569,13 +1551,13 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F9">
         <v>5800000</v>
@@ -1602,10 +1584,10 @@
         <v>2000</v>
       </c>
       <c r="N9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="O9" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1635,7 +1617,7 @@
         <v>0</v>
       </c>
       <c r="Y9" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1646,13 +1628,13 @@
         <v>30</v>
       </c>
       <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
         <v>48</v>
       </c>
-      <c r="D10" t="s">
-        <v>50</v>
-      </c>
       <c r="E10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F10">
         <v>1400000</v>
@@ -1679,10 +1661,10 @@
         <v>16000</v>
       </c>
       <c r="N10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="O10" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="P10">
         <v>72895458363</v>
@@ -1712,7 +1694,7 @@
         <v>-3801868433</v>
       </c>
       <c r="Y10" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1720,16 +1702,16 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F11">
         <v>2234000</v>
@@ -1756,10 +1738,10 @@
         <v>10000</v>
       </c>
       <c r="N11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="O11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="P11">
         <v>1337894447</v>
@@ -1789,7 +1771,7 @@
         <v>-1257080998</v>
       </c>
       <c r="Y11" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1797,99 +1779,99 @@
         <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F12">
-        <v>1350000</v>
+        <v>6000000</v>
       </c>
       <c r="G12">
-        <v>1350000</v>
+        <v>6000000</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>14000</v>
+        <v>2000</v>
       </c>
       <c r="J12">
-        <v>17000</v>
+        <v>2000</v>
       </c>
       <c r="K12">
-        <v>6471740</v>
+        <v>6345000</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <v>22000</v>
+        <v>2000</v>
       </c>
       <c r="N12" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="O12" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P12">
-        <v>5214628820</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>6009352447</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>965797975</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>2015081728</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>1319755337</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>-44547594</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>1503069100</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>1410469786</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>24178632</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:25">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F13">
-        <v>6000000</v>
+        <v>4000000</v>
       </c>
       <c r="G13">
-        <v>6000000</v>
+        <v>4000000</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -1901,7 +1883,7 @@
         <v>2000</v>
       </c>
       <c r="K13">
-        <v>6345000</v>
+        <v>4420000</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1910,10 +1892,10 @@
         <v>2000</v>
       </c>
       <c r="N13" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="O13" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -1943,84 +1925,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25">
-      <c r="A14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" t="s">
-        <v>71</v>
-      </c>
-      <c r="F14">
-        <v>4000000</v>
-      </c>
-      <c r="G14">
-        <v>4000000</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>2000</v>
-      </c>
-      <c r="J14">
-        <v>2000</v>
-      </c>
-      <c r="K14">
-        <v>4420000</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>2000</v>
-      </c>
-      <c r="N14" t="s">
-        <v>84</v>
-      </c>
-      <c r="O14" t="s">
-        <v>85</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -2035,422 +1940,422 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="F2" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="F3" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C4" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="F4" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B5" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C5" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="F5" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C6" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F6" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B7" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C7" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F7" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B8" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C8" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="F8" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B9" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C9" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D9" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E9" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="F9" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B10" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C10" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F10" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B11" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C11" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E11" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="F11" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B12" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C12" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="F12" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B13" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C13" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D13" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E13" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F13" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B14" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C14" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D14" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E14" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F14" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B15" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C15" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D15" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E15" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="F15" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B16" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C16" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D16" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E16" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="F16" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B17" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C17" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D17" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E17" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="F17" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B18" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C18" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D18" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F18" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B19" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C19" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D19" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E19" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="F19" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B20" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C20" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D20" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F20" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B21" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C21" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D21" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E21" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F21" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="180">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -203,9 +203,6 @@
     <t>케이쓰리아이</t>
   </si>
   <si>
-    <t>넥스트바이오메디컬</t>
-  </si>
-  <si>
     <t>유라클</t>
   </si>
   <si>
@@ -239,9 +236,6 @@
     <t>239.23:1</t>
   </si>
   <si>
-    <t>356.95:1</t>
-  </si>
-  <si>
     <t>1065.86:1</t>
   </si>
   <si>
@@ -272,9 +266,6 @@
     <t>1.03%</t>
   </si>
   <si>
-    <t>2.18%</t>
-  </si>
-  <si>
     <t>0.55%</t>
   </si>
   <si>
@@ -297,9 +288,6 @@
   </si>
   <si>
     <t>XR 실감형콘텐츠</t>
-  </si>
-  <si>
-    <t>내시경용 지혈재, 혈관색전 미립구</t>
   </si>
   <si>
     <t>모바일 앱 개발 플랫폼</t>
@@ -924,7 +912,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y13"/>
+  <dimension ref="A1:Y12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1045,10 +1033,10 @@
         <v>2000</v>
       </c>
       <c r="N2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -1078,7 +1066,7 @@
         <v>0</v>
       </c>
       <c r="Y2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1122,10 +1110,10 @@
         <v>15300</v>
       </c>
       <c r="N3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P3">
         <v>7367362</v>
@@ -1155,7 +1143,7 @@
         <v>-2903334</v>
       </c>
       <c r="Y3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1199,10 +1187,10 @@
         <v>13000</v>
       </c>
       <c r="N4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="P4">
         <v>25588</v>
@@ -1232,7 +1220,7 @@
         <v>809</v>
       </c>
       <c r="Y4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1276,10 +1264,10 @@
         <v>2000</v>
       </c>
       <c r="N5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1309,7 +1297,7 @@
         <v>0</v>
       </c>
       <c r="Y5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1353,10 +1341,10 @@
         <v>15500</v>
       </c>
       <c r="N6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="P6">
         <v>10740898602</v>
@@ -1386,7 +1374,7 @@
         <v>219774608</v>
       </c>
       <c r="Y6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1397,43 +1385,43 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
         <v>62</v>
       </c>
       <c r="F7">
-        <v>1000000</v>
+        <v>751000</v>
       </c>
       <c r="G7">
-        <v>1000000</v>
+        <v>203700</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>547300</v>
       </c>
       <c r="I7">
-        <v>24000</v>
+        <v>18000</v>
       </c>
       <c r="J7">
-        <v>29000</v>
+        <v>21000</v>
       </c>
       <c r="K7">
-        <v>8008066</v>
+        <v>4330068</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>29000</v>
+        <v>21000</v>
       </c>
       <c r="N7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1463,7 +1451,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1471,307 +1459,307 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
         <v>63</v>
       </c>
       <c r="F8">
-        <v>751000</v>
+        <v>5800000</v>
       </c>
       <c r="G8">
-        <v>203700</v>
+        <v>5800000</v>
       </c>
       <c r="H8">
-        <v>547300</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>18000</v>
+        <v>2000</v>
       </c>
       <c r="J8">
-        <v>21000</v>
+        <v>2000</v>
       </c>
       <c r="K8">
-        <v>4330068</v>
+        <v>6100000</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>21000</v>
+        <v>2000</v>
       </c>
       <c r="N8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O8" t="s">
+        <v>79</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="s">
         <v>86</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:25">
       <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
         <v>30</v>
       </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
         <v>64</v>
       </c>
       <c r="F9">
-        <v>5800000</v>
+        <v>1400000</v>
       </c>
       <c r="G9">
-        <v>5800000</v>
+        <v>1400000</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>2000</v>
+        <v>16000</v>
       </c>
       <c r="J9">
-        <v>2000</v>
+        <v>19000</v>
       </c>
       <c r="K9">
-        <v>6100000</v>
+        <v>10000988</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>2000</v>
+        <v>16000</v>
       </c>
       <c r="N9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>72895458363</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>72913766913</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>11230711680</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>-6524077412</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>-4556157069</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>-3633759729</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>-11528915410</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>-7978634776</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>-3801868433</v>
       </c>
       <c r="Y9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:25">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E10" t="s">
         <v>65</v>
       </c>
       <c r="F10">
-        <v>1400000</v>
+        <v>2234000</v>
       </c>
       <c r="G10">
-        <v>1400000</v>
+        <v>2234000</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>16000</v>
+        <v>7300</v>
       </c>
       <c r="J10">
-        <v>19000</v>
+        <v>8500</v>
       </c>
       <c r="K10">
-        <v>10000988</v>
+        <v>14965620</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="N10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P10">
-        <v>72895458363</v>
+        <v>1337894447</v>
       </c>
       <c r="Q10">
-        <v>72913766913</v>
+        <v>4495088983</v>
       </c>
       <c r="R10">
-        <v>11230711680</v>
+        <v>99398351</v>
       </c>
       <c r="S10">
-        <v>-6524077412</v>
+        <v>-3330678562</v>
       </c>
       <c r="T10">
-        <v>-4556157069</v>
+        <v>-2905069801</v>
       </c>
       <c r="U10">
-        <v>-3633759729</v>
+        <v>-1314068310</v>
       </c>
       <c r="V10">
-        <v>-11528915410</v>
+        <v>-9735376868</v>
       </c>
       <c r="W10">
-        <v>-7978634776</v>
+        <v>-5043515600</v>
       </c>
       <c r="X10">
-        <v>-3801868433</v>
+        <v>-1257080998</v>
       </c>
       <c r="Y10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
         <v>66</v>
       </c>
       <c r="F11">
-        <v>2234000</v>
+        <v>6000000</v>
       </c>
       <c r="G11">
-        <v>2234000</v>
+        <v>6000000</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>7300</v>
+        <v>2000</v>
       </c>
       <c r="J11">
-        <v>8500</v>
+        <v>2000</v>
       </c>
       <c r="K11">
-        <v>14965620</v>
+        <v>6345000</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="N11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O11" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="P11">
-        <v>1337894447</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>4495088983</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>99398351</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>-3330678562</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>-2905069801</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>-1314068310</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>-9735376868</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>-5043515600</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>-1257080998</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1782,19 +1770,19 @@
         <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
         <v>67</v>
       </c>
       <c r="F12">
-        <v>6000000</v>
+        <v>4000000</v>
       </c>
       <c r="G12">
-        <v>6000000</v>
+        <v>4000000</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1806,7 +1794,7 @@
         <v>2000</v>
       </c>
       <c r="K12">
-        <v>6345000</v>
+        <v>4420000</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1815,10 +1803,10 @@
         <v>2000</v>
       </c>
       <c r="N12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1848,84 +1836,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25">
-      <c r="A13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13">
-        <v>4000000</v>
-      </c>
-      <c r="G13">
-        <v>4000000</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>2000</v>
-      </c>
-      <c r="J13">
-        <v>2000</v>
-      </c>
-      <c r="K13">
-        <v>4420000</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>2000</v>
-      </c>
-      <c r="N13" t="s">
-        <v>80</v>
-      </c>
-      <c r="O13" t="s">
-        <v>81</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1940,422 +1851,422 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="F4" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F5" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C6" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F6" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C7" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F7" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B8" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F8" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B9" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C9" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F9" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B10" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C10" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F10" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B11" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C11" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E11" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F11" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B12" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C12" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E12" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F12" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B13" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C13" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E13" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F13" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B14" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C14" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F14" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B15" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C15" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E15" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F15" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B16" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C16" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F16" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B17" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C17" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E17" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F17" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B18" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C18" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B19" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C19" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E19" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F19" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B20" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C20" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E20" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F20" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B21" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C21" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E21" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F21" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="181">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -326,6 +326,9 @@
     <t>위츠</t>
   </si>
   <si>
+    <t>동방메디컬</t>
+  </si>
+  <si>
     <t>더본코리아(유가)</t>
   </si>
   <si>
@@ -380,12 +383,12 @@
     <t>한켐</t>
   </si>
   <si>
-    <t>토모큐브</t>
-  </si>
-  <si>
     <t>2024.10.28~11.01</t>
   </si>
   <si>
+    <t>2024.10.16~10.22</t>
+  </si>
+  <si>
     <t>2024.10.15~10.21</t>
   </si>
   <si>
@@ -422,12 +425,12 @@
     <t>2024.09.23~09.27</t>
   </si>
   <si>
-    <t>2024.09.20~09.26</t>
-  </si>
-  <si>
     <t>5,300~6,400</t>
   </si>
   <si>
+    <t>9,000~10,500</t>
+  </si>
+  <si>
     <t>23,000~28,000</t>
   </si>
   <si>
@@ -479,12 +482,12 @@
     <t>12,500~14,500</t>
   </si>
   <si>
-    <t>10,900~13,400</t>
-  </si>
-  <si>
     <t>15900</t>
   </si>
   <si>
+    <t>30609</t>
+  </si>
+  <si>
     <t>69000</t>
   </si>
   <si>
@@ -524,6 +527,9 @@
     <t>신한투자증권</t>
   </si>
   <si>
+    <t>NH투자증권</t>
+  </si>
+  <si>
     <t>한국투자증권,NH투자증권</t>
   </si>
   <si>
@@ -549,9 +555,6 @@
   </si>
   <si>
     <t>삼성증권,유진투자증권,유안타증권</t>
-  </si>
-  <si>
-    <t>NH투자증권</t>
   </si>
   <si>
     <t>신영증권,유진증권</t>
@@ -1886,7 +1889,7 @@
         <v>155</v>
       </c>
       <c r="F2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1906,7 +1909,7 @@
         <v>156</v>
       </c>
       <c r="F3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1926,7 +1929,7 @@
         <v>157</v>
       </c>
       <c r="F4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1946,7 +1949,7 @@
         <v>158</v>
       </c>
       <c r="F5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1963,10 +1966,10 @@
         <v>79</v>
       </c>
       <c r="E6" t="s">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="F6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1974,7 +1977,7 @@
         <v>107</v>
       </c>
       <c r="B7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C7" t="s">
         <v>141</v>
@@ -1986,7 +1989,7 @@
         <v>79</v>
       </c>
       <c r="F7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1994,7 +1997,7 @@
         <v>108</v>
       </c>
       <c r="B8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C8" t="s">
         <v>142</v>
@@ -2003,10 +2006,10 @@
         <v>79</v>
       </c>
       <c r="E8" t="s">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="F8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2014,7 +2017,7 @@
         <v>109</v>
       </c>
       <c r="B9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C9" t="s">
         <v>143</v>
@@ -2026,7 +2029,7 @@
         <v>160</v>
       </c>
       <c r="F9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2043,10 +2046,10 @@
         <v>79</v>
       </c>
       <c r="E10" t="s">
-        <v>79</v>
+        <v>161</v>
       </c>
       <c r="F10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2054,7 +2057,7 @@
         <v>111</v>
       </c>
       <c r="B11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C11" t="s">
         <v>145</v>
@@ -2063,10 +2066,10 @@
         <v>79</v>
       </c>
       <c r="E11" t="s">
-        <v>161</v>
+        <v>79</v>
       </c>
       <c r="F11" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2086,7 +2089,7 @@
         <v>162</v>
       </c>
       <c r="F12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2094,7 +2097,7 @@
         <v>113</v>
       </c>
       <c r="B13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C13" t="s">
         <v>147</v>
@@ -2106,7 +2109,7 @@
         <v>163</v>
       </c>
       <c r="F13" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2123,7 +2126,7 @@
         <v>79</v>
       </c>
       <c r="E14" t="s">
-        <v>79</v>
+        <v>164</v>
       </c>
       <c r="F14" t="s">
         <v>174</v>
@@ -2143,10 +2146,10 @@
         <v>79</v>
       </c>
       <c r="E15" t="s">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="F15" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2157,7 +2160,7 @@
         <v>131</v>
       </c>
       <c r="C16" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="D16" t="s">
         <v>79</v>
@@ -2166,7 +2169,7 @@
         <v>165</v>
       </c>
       <c r="F16" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2177,7 +2180,7 @@
         <v>132</v>
       </c>
       <c r="C17" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="D17" t="s">
         <v>79</v>
@@ -2186,7 +2189,7 @@
         <v>166</v>
       </c>
       <c r="F17" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -2203,10 +2206,10 @@
         <v>79</v>
       </c>
       <c r="E18" t="s">
-        <v>79</v>
+        <v>167</v>
       </c>
       <c r="F18" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2223,10 +2226,10 @@
         <v>79</v>
       </c>
       <c r="E19" t="s">
-        <v>167</v>
+        <v>79</v>
       </c>
       <c r="F19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -2234,7 +2237,7 @@
         <v>120</v>
       </c>
       <c r="B20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C20" t="s">
         <v>153</v>
@@ -2243,10 +2246,10 @@
         <v>79</v>
       </c>
       <c r="E20" t="s">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="F20" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -2266,7 +2269,7 @@
         <v>79</v>
       </c>
       <c r="F21" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -326,6 +326,9 @@
     <t>위츠</t>
   </si>
   <si>
+    <t>엠오티</t>
+  </si>
+  <si>
     <t>동방메디컬</t>
   </si>
   <si>
@@ -335,15 +338,21 @@
     <t>유진스팩11호</t>
   </si>
   <si>
+    <t>에이치이엠파마(구.에이치이엠)</t>
+  </si>
+  <si>
+    <t>탑런토탈솔루션</t>
+  </si>
+  <si>
     <t>노머스</t>
   </si>
   <si>
+    <t>에이럭스</t>
+  </si>
+  <si>
     <t>닷밀</t>
   </si>
   <si>
-    <t>탑런토탈솔루션</t>
-  </si>
-  <si>
     <t>성우</t>
   </si>
   <si>
@@ -374,18 +383,12 @@
     <t>와이제이링크</t>
   </si>
   <si>
-    <t>셀비온</t>
-  </si>
-  <si>
-    <t>인스피언</t>
-  </si>
-  <si>
-    <t>한켐</t>
-  </si>
-  <si>
     <t>2024.10.28~11.01</t>
   </si>
   <si>
+    <t>2024.10.17~10.23</t>
+  </si>
+  <si>
     <t>2024.10.16~10.22</t>
   </si>
   <si>
@@ -395,6 +398,9 @@
     <t>2024.10.15~10.16</t>
   </si>
   <si>
+    <t>2024.10.14~10.18</t>
+  </si>
+  <si>
     <t>2024.10.11~10.17</t>
   </si>
   <si>
@@ -419,15 +425,12 @@
     <t>2024.09.25~10.02</t>
   </si>
   <si>
-    <t>2024.09.24~09.30</t>
-  </si>
-  <si>
-    <t>2024.09.23~09.27</t>
-  </si>
-  <si>
     <t>5,300~6,400</t>
   </si>
   <si>
+    <t>12,000~14,000</t>
+  </si>
+  <si>
     <t>9,000~10,500</t>
   </si>
   <si>
@@ -437,15 +440,18 @@
     <t>2,000~2,000</t>
   </si>
   <si>
+    <t>16,400~19,000</t>
+  </si>
+  <si>
     <t>27,200~30,200</t>
   </si>
   <si>
+    <t>11,500~13,500</t>
+  </si>
+  <si>
     <t>11,000~13,000</t>
   </si>
   <si>
-    <t>12,000~14,000</t>
-  </si>
-  <si>
     <t>25,000~29,000</t>
   </si>
   <si>
@@ -473,18 +479,12 @@
     <t>8,600~9,800</t>
   </si>
   <si>
-    <t>10,000~12,200</t>
-  </si>
-  <si>
-    <t>8,000~10,000</t>
-  </si>
-  <si>
-    <t>12,500~14,500</t>
-  </si>
-  <si>
     <t>15900</t>
   </si>
   <si>
+    <t>21000</t>
+  </si>
+  <si>
     <t>30609</t>
   </si>
   <si>
@@ -494,9 +494,15 @@
     <t>9000</t>
   </si>
   <si>
+    <t>11430</t>
+  </si>
+  <si>
     <t>30736</t>
   </si>
   <si>
+    <t>17250</t>
+  </si>
+  <si>
     <t>75000</t>
   </si>
   <si>
@@ -521,12 +527,12 @@
     <t>30616</t>
   </si>
   <si>
-    <t>18000</t>
-  </si>
-  <si>
     <t>신한투자증권</t>
   </si>
   <si>
+    <t>한국투자증권</t>
+  </si>
+  <si>
     <t>NH투자증권</t>
   </si>
   <si>
@@ -536,18 +542,15 @@
     <t>유진증권</t>
   </si>
   <si>
+    <t>KB증권</t>
+  </si>
+  <si>
     <t>대신증권</t>
   </si>
   <si>
     <t>미래에셋증권</t>
   </si>
   <si>
-    <t>KB증권</t>
-  </si>
-  <si>
-    <t>한국투자증권</t>
-  </si>
-  <si>
     <t>NH투자증권,KB증권,신한투자증권,키움증권</t>
   </si>
   <si>
@@ -555,9 +558,6 @@
   </si>
   <si>
     <t>삼성증권,유진투자증권,유안타증권</t>
-  </si>
-  <si>
-    <t>신영증권,유진증권</t>
   </si>
 </sst>
 </file>
@@ -1886,10 +1886,10 @@
         <v>79</v>
       </c>
       <c r="E2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1906,10 +1906,10 @@
         <v>79</v>
       </c>
       <c r="E3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1926,10 +1926,10 @@
         <v>79</v>
       </c>
       <c r="E4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1946,10 +1946,10 @@
         <v>79</v>
       </c>
       <c r="E5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1966,10 +1966,10 @@
         <v>79</v>
       </c>
       <c r="E6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1986,10 +1986,10 @@
         <v>79</v>
       </c>
       <c r="E7" t="s">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="F7" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2000,7 +2000,7 @@
         <v>127</v>
       </c>
       <c r="C8" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D8" t="s">
         <v>79</v>
@@ -2017,10 +2017,10 @@
         <v>109</v>
       </c>
       <c r="B9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D9" t="s">
         <v>79</v>
@@ -2037,10 +2037,10 @@
         <v>110</v>
       </c>
       <c r="B10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D10" t="s">
         <v>79</v>
@@ -2049,7 +2049,7 @@
         <v>161</v>
       </c>
       <c r="F10" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2057,10 +2057,10 @@
         <v>111</v>
       </c>
       <c r="B11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D11" t="s">
         <v>79</v>
@@ -2069,7 +2069,7 @@
         <v>79</v>
       </c>
       <c r="F11" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2077,10 +2077,10 @@
         <v>112</v>
       </c>
       <c r="B12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D12" t="s">
         <v>79</v>
@@ -2089,7 +2089,7 @@
         <v>162</v>
       </c>
       <c r="F12" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2100,7 +2100,7 @@
         <v>129</v>
       </c>
       <c r="C13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D13" t="s">
         <v>79</v>
@@ -2109,7 +2109,7 @@
         <v>163</v>
       </c>
       <c r="F13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2117,19 +2117,19 @@
         <v>114</v>
       </c>
       <c r="B14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D14" t="s">
         <v>79</v>
       </c>
       <c r="E14" t="s">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="F14" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2140,16 +2140,16 @@
         <v>130</v>
       </c>
       <c r="C15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D15" t="s">
         <v>79</v>
       </c>
       <c r="E15" t="s">
-        <v>79</v>
+        <v>164</v>
       </c>
       <c r="F15" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2160,7 +2160,7 @@
         <v>131</v>
       </c>
       <c r="C16" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D16" t="s">
         <v>79</v>
@@ -2169,7 +2169,7 @@
         <v>165</v>
       </c>
       <c r="F16" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2177,10 +2177,10 @@
         <v>117</v>
       </c>
       <c r="B17" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C17" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D17" t="s">
         <v>79</v>
@@ -2189,7 +2189,7 @@
         <v>166</v>
       </c>
       <c r="F17" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -2197,7 +2197,7 @@
         <v>118</v>
       </c>
       <c r="B18" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C18" t="s">
         <v>151</v>
@@ -2206,10 +2206,10 @@
         <v>79</v>
       </c>
       <c r="E18" t="s">
-        <v>167</v>
+        <v>79</v>
       </c>
       <c r="F18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2217,7 +2217,7 @@
         <v>119</v>
       </c>
       <c r="B19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C19" t="s">
         <v>152</v>
@@ -2226,10 +2226,10 @@
         <v>79</v>
       </c>
       <c r="E19" t="s">
-        <v>79</v>
+        <v>167</v>
       </c>
       <c r="F19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -2237,10 +2237,10 @@
         <v>120</v>
       </c>
       <c r="B20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C20" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="D20" t="s">
         <v>79</v>
@@ -2249,7 +2249,7 @@
         <v>168</v>
       </c>
       <c r="F20" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -2260,16 +2260,16 @@
         <v>135</v>
       </c>
       <c r="C21" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D21" t="s">
         <v>79</v>
       </c>
       <c r="E21" t="s">
-        <v>79</v>
+        <v>169</v>
       </c>
       <c r="F21" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="185">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -92,6 +92,9 @@
     <t>주요제품</t>
   </si>
   <si>
+    <t>2024-07-29</t>
+  </si>
+  <si>
     <t>2024-08-26</t>
   </si>
   <si>
@@ -107,9 +110,6 @@
     <t>2024-07-30</t>
   </si>
   <si>
-    <t>2024-07-29</t>
-  </si>
-  <si>
     <t>2024-07-23</t>
   </si>
   <si>
@@ -134,6 +134,9 @@
     <t>2024-07-10</t>
   </si>
   <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
     <t>2024-09-11</t>
   </si>
   <si>
@@ -149,9 +152,6 @@
     <t>2024-08-20</t>
   </si>
   <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
     <t>2024-08-13</t>
   </si>
   <si>
@@ -161,6 +161,9 @@
     <t>2024-07-26</t>
   </si>
   <si>
+    <t>대신</t>
+  </si>
+  <si>
     <t>미래</t>
   </si>
   <si>
@@ -170,9 +173,6 @@
     <t>한국</t>
   </si>
   <si>
-    <t>대신</t>
-  </si>
-  <si>
     <t>하나</t>
   </si>
   <si>
@@ -188,6 +188,9 @@
     <t>SK</t>
   </si>
   <si>
+    <t>아이언디바이스</t>
+  </si>
+  <si>
     <t>미래에셋비전스팩7호</t>
   </si>
   <si>
@@ -221,6 +224,9 @@
     <t>SK증권제13호스팩</t>
   </si>
   <si>
+    <t>1152.85:1</t>
+  </si>
+  <si>
     <t>1051.62 :1</t>
   </si>
   <si>
@@ -254,6 +260,9 @@
     <t>1197.45:1</t>
   </si>
   <si>
+    <t>3.34%</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
@@ -273,6 +282,9 @@
   </si>
   <si>
     <t>0.49%</t>
+  </si>
+  <si>
+    <t>스마트폰용 오디오 앰프 반도체 Soc</t>
   </si>
   <si>
     <t>기업인수합병</t>
@@ -915,7 +927,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:Y13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1000,7 +1012,7 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
         <v>39</v>
@@ -1012,64 +1024,64 @@
         <v>57</v>
       </c>
       <c r="F2">
-        <v>7950000</v>
+        <v>3000000</v>
       </c>
       <c r="G2">
-        <v>7950000</v>
+        <v>3000000</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>2000</v>
+        <v>4900</v>
       </c>
       <c r="J2">
-        <v>2000</v>
+        <v>5700</v>
       </c>
       <c r="K2">
-        <v>8215000</v>
+        <v>13653263</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="N2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>5436813</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>6232339</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2471281</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>-1510039</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>-3517400</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>-1015682</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>-3268622</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>-3926782</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>-801640</v>
       </c>
       <c r="Y2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1077,7 +1089,7 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
         <v>40</v>
@@ -1089,64 +1101,64 @@
         <v>58</v>
       </c>
       <c r="F3">
-        <v>1566800</v>
+        <v>7950000</v>
       </c>
       <c r="G3">
-        <v>1566800</v>
+        <v>7950000</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>13600</v>
+        <v>2000</v>
       </c>
       <c r="J3">
-        <v>15300</v>
+        <v>2000</v>
       </c>
       <c r="K3">
-        <v>9349954</v>
+        <v>8215000</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>15300</v>
+        <v>2000</v>
       </c>
       <c r="N3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="P3">
-        <v>7367362</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>10525887</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>1790340</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>-9315442</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>-11755057</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>-2929307</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>-45566953</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>-5053520</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>-2903334</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1154,7 +1166,7 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
         <v>41</v>
@@ -1166,64 +1178,64 @@
         <v>59</v>
       </c>
       <c r="F4">
-        <v>1000000</v>
+        <v>1566800</v>
       </c>
       <c r="G4">
-        <v>500000</v>
+        <v>1566800</v>
       </c>
       <c r="H4">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>9500</v>
+        <v>13600</v>
       </c>
       <c r="J4">
-        <v>10700</v>
+        <v>15300</v>
       </c>
       <c r="K4">
-        <v>5530000</v>
+        <v>9349954</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>13000</v>
+        <v>15300</v>
       </c>
       <c r="N4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="P4">
-        <v>25588</v>
+        <v>7367362</v>
       </c>
       <c r="Q4">
-        <v>30049</v>
+        <v>10525887</v>
       </c>
       <c r="R4">
-        <v>7363</v>
+        <v>1790340</v>
       </c>
       <c r="S4">
-        <v>3780</v>
+        <v>-9315442</v>
       </c>
       <c r="T4">
-        <v>5016</v>
+        <v>-11755057</v>
       </c>
       <c r="U4">
-        <v>938</v>
+        <v>-2929307</v>
       </c>
       <c r="V4">
-        <v>3456</v>
+        <v>-45566953</v>
       </c>
       <c r="W4">
-        <v>4688</v>
+        <v>-5053520</v>
       </c>
       <c r="X4">
-        <v>809</v>
+        <v>-2903334</v>
       </c>
       <c r="Y4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1243,64 +1255,64 @@
         <v>60</v>
       </c>
       <c r="F5">
-        <v>6500000</v>
+        <v>1000000</v>
       </c>
       <c r="G5">
-        <v>6500000</v>
+        <v>500000</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="I5">
-        <v>2000</v>
+        <v>9500</v>
       </c>
       <c r="J5">
-        <v>2000</v>
+        <v>10700</v>
       </c>
       <c r="K5">
-        <v>7910000</v>
+        <v>5530000</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="N5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O5" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>25588</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>30049</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>7363</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>3780</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>5016</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>938</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>3456</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>4688</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>809</v>
       </c>
       <c r="Y5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1308,76 +1320,76 @@
         <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
         <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
         <v>61</v>
       </c>
       <c r="F6">
-        <v>1400000</v>
+        <v>6500000</v>
       </c>
       <c r="G6">
-        <v>1400000</v>
+        <v>6500000</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>12500</v>
+        <v>2000</v>
       </c>
       <c r="J6">
-        <v>15500</v>
+        <v>2000</v>
       </c>
       <c r="K6">
-        <v>7486442</v>
+        <v>7910000</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>15500</v>
+        <v>2000</v>
       </c>
       <c r="N6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O6" t="s">
         <v>82</v>
       </c>
       <c r="P6">
-        <v>10740898602</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>13058877126</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>3506428302</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>1748628548</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>1115790858</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>191527654</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>1491084554</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>1185231988</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>219774608</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1385,123 +1397,123 @@
         <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
         <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
         <v>62</v>
       </c>
       <c r="F7">
-        <v>751000</v>
+        <v>1400000</v>
       </c>
       <c r="G7">
-        <v>203700</v>
+        <v>1400000</v>
       </c>
       <c r="H7">
-        <v>547300</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>18000</v>
+        <v>12500</v>
       </c>
       <c r="J7">
-        <v>21000</v>
+        <v>15500</v>
       </c>
       <c r="K7">
-        <v>4330068</v>
+        <v>7486442</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>21000</v>
+        <v>15500</v>
       </c>
       <c r="N7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>10740898602</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>13058877126</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>3506428302</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1748628548</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>1115790858</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>191527654</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1491084554</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1185231988</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>219774608</v>
       </c>
       <c r="Y7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E8" t="s">
         <v>63</v>
       </c>
       <c r="F8">
-        <v>5800000</v>
+        <v>751000</v>
       </c>
       <c r="G8">
-        <v>5800000</v>
+        <v>203700</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>547300</v>
       </c>
       <c r="I8">
-        <v>2000</v>
+        <v>18000</v>
       </c>
       <c r="J8">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="K8">
-        <v>6100000</v>
+        <v>4330068</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="N8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O8" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1531,238 +1543,238 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E9" t="s">
         <v>64</v>
       </c>
       <c r="F9">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="G9">
-        <v>1400000</v>
+        <v>5800000</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="J9">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="K9">
-        <v>10000988</v>
+        <v>6100000</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="N9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="P9">
-        <v>72895458363</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>72913766913</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>11230711680</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>-6524077412</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>-4556157069</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>-3633759729</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>-11528915410</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>-7978634776</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>-3801868433</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
         <v>65</v>
       </c>
       <c r="F10">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="G10">
-        <v>2234000</v>
+        <v>1400000</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>7300</v>
+        <v>16000</v>
       </c>
       <c r="J10">
-        <v>8500</v>
+        <v>19000</v>
       </c>
       <c r="K10">
-        <v>14965620</v>
+        <v>10000988</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="N10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="P10">
-        <v>1337894447</v>
+        <v>72895458363</v>
       </c>
       <c r="Q10">
-        <v>4495088983</v>
+        <v>72913766913</v>
       </c>
       <c r="R10">
-        <v>99398351</v>
+        <v>11230711680</v>
       </c>
       <c r="S10">
-        <v>-3330678562</v>
+        <v>-6524077412</v>
       </c>
       <c r="T10">
-        <v>-2905069801</v>
+        <v>-4556157069</v>
       </c>
       <c r="U10">
-        <v>-1314068310</v>
+        <v>-3633759729</v>
       </c>
       <c r="V10">
-        <v>-9735376868</v>
+        <v>-11528915410</v>
       </c>
       <c r="W10">
-        <v>-5043515600</v>
+        <v>-7978634776</v>
       </c>
       <c r="X10">
-        <v>-1257080998</v>
+        <v>-3801868433</v>
       </c>
       <c r="Y10" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:25">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
         <v>66</v>
       </c>
       <c r="F11">
-        <v>6000000</v>
+        <v>2234000</v>
       </c>
       <c r="G11">
-        <v>6000000</v>
+        <v>2234000</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>2000</v>
+        <v>7300</v>
       </c>
       <c r="J11">
-        <v>2000</v>
+        <v>8500</v>
       </c>
       <c r="K11">
-        <v>6345000</v>
+        <v>14965620</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="N11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O11" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>1337894447</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>4495088983</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>99398351</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>-3330678562</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>-2905069801</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>-1314068310</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>-9735376868</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>-5043515600</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>-1257080998</v>
       </c>
       <c r="Y11" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1773,19 +1785,19 @@
         <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s">
         <v>67</v>
       </c>
       <c r="F12">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="G12">
-        <v>4000000</v>
+        <v>6000000</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1797,7 +1809,7 @@
         <v>2000</v>
       </c>
       <c r="K12">
-        <v>4420000</v>
+        <v>6345000</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1806,10 +1818,10 @@
         <v>2000</v>
       </c>
       <c r="N12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1839,7 +1851,84 @@
         <v>0</v>
       </c>
       <c r="Y12" t="s">
-        <v>95</v>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13">
+        <v>4000000</v>
+      </c>
+      <c r="G13">
+        <v>4000000</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>2000</v>
+      </c>
+      <c r="J13">
+        <v>2000</v>
+      </c>
+      <c r="K13">
+        <v>4420000</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>2000</v>
+      </c>
+      <c r="N13" t="s">
+        <v>80</v>
+      </c>
+      <c r="O13" t="s">
+        <v>82</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -1854,422 +1943,422 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="F3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F4" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F5" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="F6" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C7" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F7" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B8" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C8" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F8" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B9" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C9" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F9" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B10" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C10" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E10" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="F10" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C11" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F11" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B12" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C12" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E12" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F12" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B13" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C13" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E13" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F13" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B14" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C14" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D14" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E14" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F14" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B15" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C15" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D15" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E15" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F15" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B16" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C16" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E16" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F16" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B17" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C17" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E17" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F17" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B18" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C18" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D18" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E18" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F18" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B19" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C19" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="F19" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B20" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C20" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D20" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E20" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F20" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B21" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C21" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D21" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F21" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="174">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -110,9 +110,6 @@
     <t>2024-07-30</t>
   </si>
   <si>
-    <t>2024-07-23</t>
-  </si>
-  <si>
     <t>2024-07-15</t>
   </si>
   <si>
@@ -155,9 +152,6 @@
     <t>2024-08-13</t>
   </si>
   <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
     <t>2024-07-26</t>
   </si>
   <si>
@@ -185,9 +179,6 @@
     <t>삼성</t>
   </si>
   <si>
-    <t>SK</t>
-  </si>
-  <si>
     <t>아이언디바이스</t>
   </si>
   <si>
@@ -212,18 +203,12 @@
     <t>교보16호스팩</t>
   </si>
   <si>
-    <t>뱅크웨어글로벌</t>
-  </si>
-  <si>
     <t>아이빔테크놀로지</t>
   </si>
   <si>
     <t>엔에이치스팩31호</t>
   </si>
   <si>
-    <t>SK증권제13호스팩</t>
-  </si>
-  <si>
     <t>1152.85:1</t>
   </si>
   <si>
@@ -248,18 +233,12 @@
     <t>1085.71:1</t>
   </si>
   <si>
-    <t>155.74:1</t>
-  </si>
-  <si>
     <t>1011.50:1</t>
   </si>
   <si>
     <t>1123.43 :1</t>
   </si>
   <si>
-    <t>1197.45:1</t>
-  </si>
-  <si>
     <t>3.34%</t>
   </si>
   <si>
@@ -278,9 +257,6 @@
     <t>0.55%</t>
   </si>
   <si>
-    <t>1.52%</t>
-  </si>
-  <si>
     <t>0.49%</t>
   </si>
   <si>
@@ -305,18 +281,12 @@
     <t>모바일 앱 개발 플랫폼</t>
   </si>
   <si>
-    <t>국내외 은행 및 금융기업 대상 코어뱅킹 소프트웨어</t>
-  </si>
-  <si>
     <t>생체현미경, CRO 서비스</t>
   </si>
   <si>
     <t>금융지원서비스업</t>
   </si>
   <si>
-    <t>기업인수목적 주식회사</t>
-  </si>
-  <si>
     <t>종목명</t>
   </si>
   <si>
@@ -350,6 +320,9 @@
     <t>유진스팩11호</t>
   </si>
   <si>
+    <t>미트박스글로벌</t>
+  </si>
+  <si>
     <t>에이치이엠파마(구.에이치이엠)</t>
   </si>
   <si>
@@ -392,9 +365,6 @@
     <t>신한스팩14호</t>
   </si>
   <si>
-    <t>와이제이링크</t>
-  </si>
-  <si>
     <t>2024.10.28~11.01</t>
   </si>
   <si>
@@ -434,9 +404,6 @@
     <t>2024.09.26~09.27</t>
   </si>
   <si>
-    <t>2024.09.25~10.02</t>
-  </si>
-  <si>
     <t>5,300~6,400</t>
   </si>
   <si>
@@ -452,6 +419,9 @@
     <t>2,000~2,000</t>
   </si>
   <si>
+    <t>23,000~28,500</t>
+  </si>
+  <si>
     <t>16,400~19,000</t>
   </si>
   <si>
@@ -488,9 +458,6 @@
     <t>16,500~20,500</t>
   </si>
   <si>
-    <t>8,600~9,800</t>
-  </si>
-  <si>
     <t>15900</t>
   </si>
   <si>
@@ -506,6 +473,9 @@
     <t>9000</t>
   </si>
   <si>
+    <t>23000</t>
+  </si>
+  <si>
     <t>11430</t>
   </si>
   <si>
@@ -536,9 +506,6 @@
     <t>10000</t>
   </si>
   <si>
-    <t>30616</t>
-  </si>
-  <si>
     <t>신한투자증권</t>
   </si>
   <si>
@@ -554,13 +521,13 @@
     <t>유진증권</t>
   </si>
   <si>
+    <t>미래에셋증권</t>
+  </si>
+  <si>
     <t>KB증권</t>
   </si>
   <si>
     <t>대신증권</t>
-  </si>
-  <si>
-    <t>미래에셋증권</t>
   </si>
   <si>
     <t>NH투자증권,KB증권,신한투자증권,키움증권</t>
@@ -927,7 +894,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y13"/>
+  <dimension ref="A1:Y11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1015,13 +982,13 @@
         <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F2">
         <v>3000000</v>
@@ -1048,10 +1015,10 @@
         <v>7000</v>
       </c>
       <c r="N2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="O2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="P2">
         <v>5436813</v>
@@ -1081,7 +1048,7 @@
         <v>-801640</v>
       </c>
       <c r="Y2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1089,16 +1056,16 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F3">
         <v>7950000</v>
@@ -1125,40 +1092,40 @@
         <v>2000</v>
       </c>
       <c r="N3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="O3" t="s">
+        <v>75</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="s">
         <v>82</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1166,16 +1133,16 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F4">
         <v>1566800</v>
@@ -1202,10 +1169,10 @@
         <v>15300</v>
       </c>
       <c r="N4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="O4" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="P4">
         <v>7367362</v>
@@ -1235,7 +1202,7 @@
         <v>-2903334</v>
       </c>
       <c r="Y4" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1243,16 +1210,16 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F5">
         <v>1000000</v>
@@ -1279,10 +1246,10 @@
         <v>13000</v>
       </c>
       <c r="N5" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="O5" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="P5">
         <v>25588</v>
@@ -1312,7 +1279,7 @@
         <v>809</v>
       </c>
       <c r="Y5" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1320,16 +1287,16 @@
         <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F6">
         <v>6500000</v>
@@ -1356,10 +1323,10 @@
         <v>2000</v>
       </c>
       <c r="N6" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="O6" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1389,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1400,13 +1367,13 @@
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F7">
         <v>1400000</v>
@@ -1433,40 +1400,40 @@
         <v>15500</v>
       </c>
       <c r="N7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="O7" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="P7">
-        <v>10740898602</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>13058877126</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>3506428302</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>1748628548</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>1115790858</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>191527654</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>1491084554</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>1185231988</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>219774608</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1477,13 +1444,13 @@
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F8">
         <v>751000</v>
@@ -1510,10 +1477,10 @@
         <v>21000</v>
       </c>
       <c r="N8" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="O8" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1543,7 +1510,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1554,13 +1521,13 @@
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F9">
         <v>5800000</v>
@@ -1587,40 +1554,40 @@
         <v>2000</v>
       </c>
       <c r="N9" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="O9" t="s">
+        <v>75</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="s">
         <v>82</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1628,76 +1595,76 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E10" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F10">
-        <v>1400000</v>
+        <v>2234000</v>
       </c>
       <c r="G10">
-        <v>1400000</v>
+        <v>2234000</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>16000</v>
+        <v>7300</v>
       </c>
       <c r="J10">
-        <v>19000</v>
+        <v>8500</v>
       </c>
       <c r="K10">
-        <v>10000988</v>
+        <v>14965620</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="N10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="O10" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="P10">
-        <v>72895458363</v>
+        <v>1337894447</v>
       </c>
       <c r="Q10">
-        <v>72913766913</v>
+        <v>4495088983</v>
       </c>
       <c r="R10">
-        <v>11230711680</v>
+        <v>99398351</v>
       </c>
       <c r="S10">
-        <v>-6524077412</v>
+        <v>-3330678562</v>
       </c>
       <c r="T10">
-        <v>-4556157069</v>
+        <v>-2905069801</v>
       </c>
       <c r="U10">
-        <v>-3633759729</v>
+        <v>-1314068310</v>
       </c>
       <c r="V10">
-        <v>-11528915410</v>
+        <v>-9735376868</v>
       </c>
       <c r="W10">
-        <v>-7978634776</v>
+        <v>-5043515600</v>
       </c>
       <c r="X10">
-        <v>-3801868433</v>
+        <v>-1257080998</v>
       </c>
       <c r="Y10" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1708,227 +1675,73 @@
         <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F11">
-        <v>2234000</v>
+        <v>6000000</v>
       </c>
       <c r="G11">
-        <v>2234000</v>
+        <v>6000000</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>7300</v>
+        <v>2000</v>
       </c>
       <c r="J11">
-        <v>8500</v>
+        <v>2000</v>
       </c>
       <c r="K11">
-        <v>14965620</v>
+        <v>6345000</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="N11" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="O11" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="P11">
-        <v>1337894447</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>4495088983</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>99398351</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>-3330678562</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>-2905069801</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>-1314068310</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>-9735376868</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>-5043515600</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>-1257080998</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25">
-      <c r="A12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" t="s">
-        <v>67</v>
-      </c>
-      <c r="F12">
-        <v>6000000</v>
-      </c>
-      <c r="G12">
-        <v>6000000</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>2000</v>
-      </c>
-      <c r="J12">
-        <v>2000</v>
-      </c>
-      <c r="K12">
-        <v>6345000</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>2000</v>
-      </c>
-      <c r="N12" t="s">
-        <v>79</v>
-      </c>
-      <c r="O12" t="s">
-        <v>82</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="X12">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25">
-      <c r="A13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13">
-        <v>4000000</v>
-      </c>
-      <c r="G13">
-        <v>4000000</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>2000</v>
-      </c>
-      <c r="J13">
-        <v>2000</v>
-      </c>
-      <c r="K13">
-        <v>4420000</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>2000</v>
-      </c>
-      <c r="N13" t="s">
-        <v>80</v>
-      </c>
-      <c r="O13" t="s">
-        <v>82</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1943,422 +1756,422 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C2" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="F2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="C3" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="F3" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C4" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="F4" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C5" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E5" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="F5" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B6" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C6" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="F6" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="B7" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C7" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="F7" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B8" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="C8" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E8" t="s">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="F8" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B9" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="C9" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E9" t="s">
-        <v>164</v>
+        <v>75</v>
       </c>
       <c r="F9" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B10" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C10" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E10" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="F10" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B11" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="C11" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E11" t="s">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="F11" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B12" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C12" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E12" t="s">
-        <v>166</v>
+        <v>75</v>
       </c>
       <c r="F12" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B13" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C13" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E13" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="F13" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B14" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="C14" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="D14" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E14" t="s">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="F14" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="B15" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C15" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="D15" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E15" t="s">
-        <v>168</v>
+        <v>75</v>
       </c>
       <c r="F15" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B16" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C16" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="D16" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E16" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="F16" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="B17" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C17" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="D17" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E17" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="F17" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B18" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="C18" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="D18" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E18" t="s">
-        <v>82</v>
+        <v>160</v>
       </c>
       <c r="F18" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B19" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="C19" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="D19" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E19" t="s">
-        <v>171</v>
+        <v>75</v>
       </c>
       <c r="F19" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="B20" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="C20" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D20" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E20" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="F20" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="B21" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="C21" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E21" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="F21" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="167">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -113,9 +113,6 @@
     <t>2024-07-15</t>
   </si>
   <si>
-    <t>2024-07-09</t>
-  </si>
-  <si>
     <t>2024-08-27</t>
   </si>
   <si>
@@ -128,9 +125,6 @@
     <t>2024-07-19</t>
   </si>
   <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
     <t>2024-08-16</t>
   </si>
   <si>
@@ -152,9 +146,6 @@
     <t>2024-08-13</t>
   </si>
   <si>
-    <t>2024-07-26</t>
-  </si>
-  <si>
     <t>대신</t>
   </si>
   <si>
@@ -206,9 +197,6 @@
     <t>아이빔테크놀로지</t>
   </si>
   <si>
-    <t>엔에이치스팩31호</t>
-  </si>
-  <si>
     <t>1152.85:1</t>
   </si>
   <si>
@@ -236,9 +224,6 @@
     <t>1011.50:1</t>
   </si>
   <si>
-    <t>1123.43 :1</t>
-  </si>
-  <si>
     <t>3.34%</t>
   </si>
   <si>
@@ -284,9 +269,6 @@
     <t>생체현미경, CRO 서비스</t>
   </si>
   <si>
-    <t>금융지원서비스업</t>
-  </si>
-  <si>
     <t>종목명</t>
   </si>
   <si>
@@ -308,6 +290,9 @@
     <t>위츠</t>
   </si>
   <si>
+    <t>토모큐브</t>
+  </si>
+  <si>
     <t>엠오티</t>
   </si>
   <si>
@@ -323,6 +308,9 @@
     <t>미트박스글로벌</t>
   </si>
   <si>
+    <t>에어레인</t>
+  </si>
+  <si>
     <t>에이치이엠파마(구.에이치이엠)</t>
   </si>
   <si>
@@ -359,12 +347,6 @@
     <t>쓰리빌리언</t>
   </si>
   <si>
-    <t>루미르</t>
-  </si>
-  <si>
-    <t>신한스팩14호</t>
-  </si>
-  <si>
     <t>2024.10.28~11.01</t>
   </si>
   <si>
@@ -398,15 +380,12 @@
     <t>2024.09.27~10.04</t>
   </si>
   <si>
-    <t>2024.09.26~10.04</t>
-  </si>
-  <si>
-    <t>2024.09.26~09.27</t>
-  </si>
-  <si>
     <t>5,300~6,400</t>
   </si>
   <si>
+    <t>10,900~13,400</t>
+  </si>
+  <si>
     <t>12,000~14,000</t>
   </si>
   <si>
@@ -422,6 +401,9 @@
     <t>23,000~28,500</t>
   </si>
   <si>
+    <t>16,000~18,500</t>
+  </si>
+  <si>
     <t>16,400~19,000</t>
   </si>
   <si>
@@ -455,9 +437,6 @@
     <t>4,500~6,500</t>
   </si>
   <si>
-    <t>16,500~20,500</t>
-  </si>
-  <si>
     <t>15900</t>
   </si>
   <si>
@@ -476,6 +455,9 @@
     <t>23000</t>
   </si>
   <si>
+    <t>19200</t>
+  </si>
+  <si>
     <t>11430</t>
   </si>
   <si>
@@ -500,15 +482,12 @@
     <t>11000</t>
   </si>
   <si>
-    <t>49500</t>
-  </si>
-  <si>
-    <t>10000</t>
-  </si>
-  <si>
     <t>신한투자증권</t>
   </si>
   <si>
+    <t>대신증권</t>
+  </si>
+  <si>
     <t>한국투자증권</t>
   </si>
   <si>
@@ -524,10 +503,10 @@
     <t>미래에셋증권</t>
   </si>
   <si>
+    <t>신영증권</t>
+  </si>
+  <si>
     <t>KB증권</t>
-  </si>
-  <si>
-    <t>대신증권</t>
   </si>
   <si>
     <t>NH투자증권,KB증권,신한투자증권,키움증권</t>
@@ -894,7 +873,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y11"/>
+  <dimension ref="A1:Y10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -982,13 +961,13 @@
         <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F2">
         <v>3000000</v>
@@ -1015,10 +994,10 @@
         <v>7000</v>
       </c>
       <c r="N2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="O2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="P2">
         <v>5436813</v>
@@ -1048,7 +1027,7 @@
         <v>-801640</v>
       </c>
       <c r="Y2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1056,16 +1035,16 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F3">
         <v>7950000</v>
@@ -1092,10 +1071,10 @@
         <v>2000</v>
       </c>
       <c r="N3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="O3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -1125,7 +1104,7 @@
         <v>0</v>
       </c>
       <c r="Y3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1133,16 +1112,16 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F4">
         <v>1566800</v>
@@ -1169,10 +1148,10 @@
         <v>15300</v>
       </c>
       <c r="N4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="O4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="P4">
         <v>7367362</v>
@@ -1202,7 +1181,7 @@
         <v>-2903334</v>
       </c>
       <c r="Y4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1210,16 +1189,16 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F5">
         <v>1000000</v>
@@ -1246,10 +1225,10 @@
         <v>13000</v>
       </c>
       <c r="N5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="P5">
         <v>25588</v>
@@ -1279,7 +1258,7 @@
         <v>809</v>
       </c>
       <c r="Y5" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1287,16 +1266,16 @@
         <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F6">
         <v>6500000</v>
@@ -1323,10 +1302,10 @@
         <v>2000</v>
       </c>
       <c r="N6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="O6" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1356,7 +1335,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1367,13 +1346,13 @@
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F7">
         <v>1400000</v>
@@ -1400,40 +1379,40 @@
         <v>15500</v>
       </c>
       <c r="N7" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="O7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>10740898602</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>13058877126</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>3506428302</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1748628548</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>1115790858</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>191527654</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1491084554</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1185231988</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>219774608</v>
       </c>
       <c r="Y7" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1444,13 +1423,13 @@
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F8">
         <v>751000</v>
@@ -1477,10 +1456,10 @@
         <v>21000</v>
       </c>
       <c r="N8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="O8" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1510,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1521,13 +1500,13 @@
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F9">
         <v>5800000</v>
@@ -1554,10 +1533,10 @@
         <v>2000</v>
       </c>
       <c r="N9" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="O9" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1587,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="Y9" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1595,16 +1574,16 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F10">
         <v>2234000</v>
@@ -1631,10 +1610,10 @@
         <v>10000</v>
       </c>
       <c r="N10" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O10" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="P10">
         <v>1337894447</v>
@@ -1664,84 +1643,7 @@
         <v>-1257080998</v>
       </c>
       <c r="Y10" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25">
-      <c r="A11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11">
-        <v>6000000</v>
-      </c>
-      <c r="G11">
-        <v>6000000</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>2000</v>
-      </c>
-      <c r="J11">
-        <v>2000</v>
-      </c>
-      <c r="K11">
-        <v>6345000</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>2000</v>
-      </c>
-      <c r="N11" t="s">
-        <v>73</v>
-      </c>
-      <c r="O11" t="s">
-        <v>75</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11">
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <v>0</v>
-      </c>
-      <c r="X11">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1756,422 +1658,422 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C2" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="F2" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C3" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
-        <v>148</v>
+        <v>70</v>
       </c>
       <c r="F3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C4" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="F4" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B5" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C5" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E5" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F5" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B6" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E6" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="F6" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B7" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C7" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="F7" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B8" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C8" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E8" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="F8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B9" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D9" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E9" t="s">
-        <v>75</v>
+        <v>146</v>
       </c>
       <c r="F9" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C10" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E10" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="F10" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C11" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="D11" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E11" t="s">
-        <v>155</v>
+        <v>70</v>
       </c>
       <c r="F11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B12" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C12" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E12" t="s">
-        <v>75</v>
+        <v>148</v>
       </c>
       <c r="F12" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B13" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C13" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D13" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E13" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="F13" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B14" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C14" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E14" t="s">
-        <v>157</v>
+        <v>70</v>
       </c>
       <c r="F14" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B15" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C15" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D15" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E15" t="s">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="F15" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B16" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C16" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="D16" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E16" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F16" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B17" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C17" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E17" t="s">
-        <v>159</v>
+        <v>70</v>
       </c>
       <c r="F17" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B18" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C18" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D18" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E18" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F18" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B19" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C19" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D19" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E19" t="s">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="F19" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B20" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C20" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="D20" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E20" t="s">
+        <v>154</v>
+      </c>
+      <c r="F20" t="s">
         <v>161</v>
-      </c>
-      <c r="F20" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B21" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C21" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D21" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E21" t="s">
-        <v>162</v>
+        <v>70</v>
       </c>
       <c r="F21" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/ib-strategy-data.xlsx
+++ b/datasets/ib-strategy-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="172">
   <si>
     <t>수요예측(시작일)</t>
   </si>
@@ -92,6 +92,9 @@
     <t>주요제품</t>
   </si>
   <si>
+    <t>2024-09-05</t>
+  </si>
+  <si>
     <t>2024-07-29</t>
   </si>
   <si>
@@ -113,6 +116,9 @@
     <t>2024-07-15</t>
   </si>
   <si>
+    <t>2024-09-06</t>
+  </si>
+  <si>
     <t>2024-08-27</t>
   </si>
   <si>
@@ -125,6 +131,9 @@
     <t>2024-07-19</t>
   </si>
   <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
     <t>2024-08-16</t>
   </si>
   <si>
@@ -146,6 +155,9 @@
     <t>2024-08-13</t>
   </si>
   <si>
+    <t>KB</t>
+  </si>
+  <si>
     <t>대신</t>
   </si>
   <si>
@@ -170,6 +182,9 @@
     <t>삼성</t>
   </si>
   <si>
+    <t>KB제30호스팩</t>
+  </si>
+  <si>
     <t>아이언디바이스</t>
   </si>
   <si>
@@ -197,6 +212,9 @@
     <t>아이빔테크놀로지</t>
   </si>
   <si>
+    <t>1217.75:1</t>
+  </si>
+  <si>
     <t>1152.85:1</t>
   </si>
   <si>
@@ -224,12 +242,12 @@
     <t>1011.50:1</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>3.34%</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>0.24%</t>
   </si>
   <si>
@@ -245,12 +263,12 @@
     <t>0.49%</t>
   </si>
   <si>
+    <t>기업인수합병</t>
+  </si>
+  <si>
     <t>스마트폰용 오디오 앰프 반도체 Soc</t>
   </si>
   <si>
-    <t>기업인수합병</t>
-  </si>
-  <si>
     <t>첨단바이오의약품 위탁개발생산(CDMO) 서비스 / 차세대 세포,유전자 치료제</t>
   </si>
   <si>
@@ -290,6 +308,9 @@
     <t>위츠</t>
   </si>
   <si>
+    <t>신한스팩15호</t>
+  </si>
+  <si>
     <t>토모큐브</t>
   </si>
   <si>
@@ -344,12 +365,12 @@
     <t>에이치엔에스하이텍</t>
   </si>
   <si>
-    <t>쓰리빌리언</t>
-  </si>
-  <si>
     <t>2024.10.28~11.01</t>
   </si>
   <si>
+    <t>2024.10.28~10.29</t>
+  </si>
+  <si>
     <t>2024.10.17~10.23</t>
   </si>
   <si>
@@ -377,12 +398,12 @@
     <t>2024.09.30~10.08</t>
   </si>
   <si>
-    <t>2024.09.27~10.04</t>
-  </si>
-  <si>
     <t>5,300~6,400</t>
   </si>
   <si>
+    <t>2,000~2,000</t>
+  </si>
+  <si>
     <t>10,900~13,400</t>
   </si>
   <si>
@@ -395,9 +416,6 @@
     <t>23,000~28,000</t>
   </si>
   <si>
-    <t>2,000~2,000</t>
-  </si>
-  <si>
     <t>23,000~28,500</t>
   </si>
   <si>
@@ -432,9 +450,6 @@
   </si>
   <si>
     <t>22,000~26,000</t>
-  </si>
-  <si>
-    <t>4,500~6,500</t>
   </si>
   <si>
     <t>15900</t>
@@ -873,7 +888,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y10"/>
+  <dimension ref="A1:Y11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -958,76 +973,76 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F2">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="G2">
-        <v>3000000</v>
+        <v>5000000</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>4900</v>
+        <v>2000</v>
       </c>
       <c r="J2">
-        <v>5700</v>
+        <v>2000</v>
       </c>
       <c r="K2">
-        <v>13653263</v>
+        <v>5310000</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>7000</v>
+        <v>2000</v>
       </c>
       <c r="N2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="O2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="P2">
-        <v>5436813</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>6232339</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>2471281</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>-1510039</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>-3517400</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>-1015682</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>-3268622</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>-3926782</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>-801640</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1035,76 +1050,76 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F3">
-        <v>7950000</v>
+        <v>3000000</v>
       </c>
       <c r="G3">
-        <v>7950000</v>
+        <v>3000000</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>2000</v>
+        <v>4900</v>
       </c>
       <c r="J3">
-        <v>2000</v>
+        <v>5700</v>
       </c>
       <c r="K3">
-        <v>8215000</v>
+        <v>13653263</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="N3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="O3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>5436813</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>6232339</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2471281</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>-1510039</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>-3517400</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>-1015682</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>-3268622</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>-3926782</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>-801640</v>
       </c>
       <c r="Y3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1112,76 +1127,76 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F4">
-        <v>1566800</v>
+        <v>7950000</v>
       </c>
       <c r="G4">
-        <v>1566800</v>
+        <v>7950000</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>13600</v>
+        <v>2000</v>
       </c>
       <c r="J4">
-        <v>15300</v>
+        <v>2000</v>
       </c>
       <c r="K4">
-        <v>9349954</v>
+        <v>8215000</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>15300</v>
+        <v>2000</v>
       </c>
       <c r="N4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="O4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="P4">
-        <v>7367362</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>10525887</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>1790340</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>-9315442</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>-11755057</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>-2929307</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>-45566953</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>-5053520</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>-2903334</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1189,76 +1204,76 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F5">
-        <v>1000000</v>
+        <v>1566800</v>
       </c>
       <c r="G5">
-        <v>500000</v>
+        <v>1566800</v>
       </c>
       <c r="H5">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>9500</v>
+        <v>13600</v>
       </c>
       <c r="J5">
-        <v>10700</v>
+        <v>15300</v>
       </c>
       <c r="K5">
-        <v>5530000</v>
+        <v>9349954</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>13000</v>
+        <v>15300</v>
       </c>
       <c r="N5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="O5" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="P5">
-        <v>25588</v>
+        <v>7367362</v>
       </c>
       <c r="Q5">
-        <v>30049</v>
+        <v>10525887</v>
       </c>
       <c r="R5">
-        <v>7363</v>
+        <v>1790340</v>
       </c>
       <c r="S5">
-        <v>3780</v>
+        <v>-9315442</v>
       </c>
       <c r="T5">
-        <v>5016</v>
+        <v>-11755057</v>
       </c>
       <c r="U5">
-        <v>938</v>
+        <v>-2929307</v>
       </c>
       <c r="V5">
-        <v>3456</v>
+        <v>-45566953</v>
       </c>
       <c r="W5">
-        <v>4688</v>
+        <v>-5053520</v>
       </c>
       <c r="X5">
-        <v>809</v>
+        <v>-2903334</v>
       </c>
       <c r="Y5" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1266,76 +1281,76 @@
         <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F6">
-        <v>6500000</v>
+        <v>1000000</v>
       </c>
       <c r="G6">
-        <v>6500000</v>
+        <v>500000</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="I6">
-        <v>2000</v>
+        <v>9500</v>
       </c>
       <c r="J6">
-        <v>2000</v>
+        <v>10700</v>
       </c>
       <c r="K6">
-        <v>7910000</v>
+        <v>5530000</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="N6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="O6" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>25588</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>30049</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>7363</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>3780</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>5016</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>938</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>3456</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>4688</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>809</v>
       </c>
       <c r="Y6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1343,200 +1358,200 @@
         <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
         <v>47</v>
       </c>
       <c r="E7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F7">
-        <v>1400000</v>
+        <v>6500000</v>
       </c>
       <c r="G7">
-        <v>1400000</v>
+        <v>6500000</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>12500</v>
+        <v>2000</v>
       </c>
       <c r="J7">
-        <v>15500</v>
+        <v>2000</v>
       </c>
       <c r="K7">
-        <v>7486442</v>
+        <v>7910000</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>15500</v>
+        <v>2000</v>
       </c>
       <c r="N7" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="O7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="P7">
-        <v>10740898602</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>13058877126</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>3506428302</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>1748628548</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>1115790858</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>191527654</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>1491084554</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>1185231988</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>219774608</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:25">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E8" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F8">
-        <v>751000</v>
+        <v>1400000</v>
       </c>
       <c r="G8">
-        <v>203700</v>
+        <v>1400000</v>
       </c>
       <c r="H8">
-        <v>547300</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>18000</v>
+        <v>12500</v>
       </c>
       <c r="J8">
-        <v>21000</v>
+        <v>15500</v>
       </c>
       <c r="K8">
-        <v>4330068</v>
+        <v>7486442</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>21000</v>
+        <v>15500</v>
       </c>
       <c r="N8" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="O8" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>10740898602</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>13058877126</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>3506428302</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1748628548</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1115790858</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>191527654</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1491084554</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1185231988</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>219774608</v>
       </c>
       <c r="Y8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:25">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F9">
-        <v>5800000</v>
+        <v>751000</v>
       </c>
       <c r="G9">
-        <v>5800000</v>
+        <v>203700</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>547300</v>
       </c>
       <c r="I9">
-        <v>2000</v>
+        <v>18000</v>
       </c>
       <c r="J9">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="K9">
-        <v>6100000</v>
+        <v>4330068</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>2000</v>
+        <v>21000</v>
       </c>
       <c r="N9" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="O9" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1566,84 +1581,161 @@
         <v>0</v>
       </c>
       <c r="Y9" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:25">
       <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
         <v>31</v>
       </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E10" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F10">
+        <v>5800000</v>
+      </c>
+      <c r="G10">
+        <v>5800000</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>2000</v>
+      </c>
+      <c r="J10">
+        <v>2000</v>
+      </c>
+      <c r="K10">
+        <v>6100000</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>2000</v>
+      </c>
+      <c r="N10" t="s">
+        <v>73</v>
+      </c>
+      <c r="O10" t="s">
+        <v>75</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11">
         <v>2234000</v>
       </c>
-      <c r="G10">
+      <c r="G11">
         <v>2234000</v>
       </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
         <v>7300</v>
       </c>
-      <c r="J10">
+      <c r="J11">
         <v>8500</v>
       </c>
-      <c r="K10">
+      <c r="K11">
         <v>14965620</v>
       </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
         <v>10000</v>
       </c>
-      <c r="N10" t="s">
-        <v>68</v>
-      </c>
-      <c r="O10" t="s">
-        <v>75</v>
-      </c>
-      <c r="P10">
+      <c r="N11" t="s">
+        <v>74</v>
+      </c>
+      <c r="O11" t="s">
+        <v>81</v>
+      </c>
+      <c r="P11">
         <v>1337894447</v>
       </c>
-      <c r="Q10">
+      <c r="Q11">
         <v>4495088983</v>
       </c>
-      <c r="R10">
+      <c r="R11">
         <v>99398351</v>
       </c>
-      <c r="S10">
+      <c r="S11">
         <v>-3330678562</v>
       </c>
-      <c r="T10">
+      <c r="T11">
         <v>-2905069801</v>
       </c>
-      <c r="U10">
+      <c r="U11">
         <v>-1314068310</v>
       </c>
-      <c r="V10">
+      <c r="V11">
         <v>-9735376868</v>
       </c>
-      <c r="W10">
+      <c r="W11">
         <v>-5043515600</v>
       </c>
-      <c r="X10">
+      <c r="X11">
         <v>-1257080998</v>
       </c>
-      <c r="Y10" t="s">
-        <v>83</v>
+      <c r="Y11" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1658,422 +1750,422 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C4" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
-        <v>141</v>
+        <v>75</v>
       </c>
       <c r="F4" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C5" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E5" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C6" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F6" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B7" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C7" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F7" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B8" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="C8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E8" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F8" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B9" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C9" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E9" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F9" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B10" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C10" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F10" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B11" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C11" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E11" t="s">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="F11" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B12" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C12" t="s">
         <v>130</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E12" t="s">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="F12" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B13" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C13" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E13" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F13" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B14" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C14" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D14" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E14" t="s">
-        <v>70</v>
+        <v>154</v>
       </c>
       <c r="F14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B15" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C15" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E15" t="s">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="F15" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B16" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C16" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E16" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F16" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B17" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C17" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E17" t="s">
-        <v>70</v>
+        <v>156</v>
       </c>
       <c r="F17" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B18" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C18" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E18" t="s">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="F18" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B19" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C19" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D19" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E19" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F19" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B20" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C20" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D20" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E20" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F20" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B21" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C21" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D21" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E21" t="s">
-        <v>70</v>
+        <v>159</v>
       </c>
       <c r="F21" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
